--- a/research/traditional_assets/database/data/chile/chile_retail_automotive.xlsx
+++ b/research/traditional_assets/database/data/chile/chile_retail_automotive.xlsx
@@ -650,10 +650,10 @@
         <v>0.08988066667770073</v>
       </c>
       <c r="X2">
-        <v>0.1190844167220945</v>
+        <v>0.1190544026818771</v>
       </c>
       <c r="Y2">
-        <v>-0.02920375004439374</v>
+        <v>-0.02917373600417636</v>
       </c>
       <c r="Z2">
         <v>1.36399103976106</v>
@@ -662,10 +662,10 @@
         <v>0.05739566545020543</v>
       </c>
       <c r="AB2">
-        <v>0.0802489929172169</v>
+        <v>0.08023544873121616</v>
       </c>
       <c r="AC2">
-        <v>-0.02285332746701147</v>
+        <v>-0.02283978328101072</v>
       </c>
       <c r="AD2">
         <v>9666.299999999999</v>
@@ -787,10 +787,10 @@
         <v>0.08988066667770073</v>
       </c>
       <c r="X3">
-        <v>0.1190844167220945</v>
+        <v>0.1190544026818771</v>
       </c>
       <c r="Y3">
-        <v>-0.02920375004439374</v>
+        <v>-0.02917373600417636</v>
       </c>
       <c r="Z3">
         <v>1.36399103976106</v>
@@ -799,10 +799,10 @@
         <v>0.05739566545020543</v>
       </c>
       <c r="AB3">
-        <v>0.0802489929172169</v>
+        <v>0.08023544873121616</v>
       </c>
       <c r="AC3">
-        <v>-0.02285332746701147</v>
+        <v>-0.02283978328101072</v>
       </c>
       <c r="AD3">
         <v>9666.299999999999</v>
@@ -1139,49 +1139,49 @@
         <v>2.85943906839429</v>
       </c>
       <c r="F2">
-        <v>3.04745237075288</v>
+        <v>3.01328133260794</v>
       </c>
       <c r="G2">
         <v>3.77206743151487</v>
       </c>
       <c r="H2">
-        <v>3.91822172793257</v>
+        <v>4.12444392413955</v>
       </c>
       <c r="I2">
         <v>0.548738327041526</v>
       </c>
       <c r="J2">
-        <v>0.57</v>
+        <v>0.6</v>
       </c>
       <c r="K2">
         <v>7949.2</v>
       </c>
       <c r="L2">
-        <v>7633.27731181556</v>
+        <v>7764.50911716249</v>
       </c>
       <c r="M2">
         <v>15735.4</v>
       </c>
       <c r="N2">
-        <v>15794.0123118156</v>
+        <v>16453.7091171625</v>
       </c>
       <c r="O2">
         <v>9666.299999999999</v>
       </c>
       <c r="P2">
-        <v>10040.835</v>
+        <v>10569.3</v>
       </c>
       <c r="Q2">
-        <v>0.0802489929172169</v>
+        <v>0.0802354487312162</v>
       </c>
       <c r="R2">
-        <v>0.080121151107629</v>
+        <v>0.0787321222410564</v>
       </c>
       <c r="S2">
         <v>0.0483122072898587</v>
       </c>
       <c r="T2">
-        <v>0.0483852072898587</v>
+        <v>0.0464872072898587</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -1194,16 +1194,16 @@
         </is>
       </c>
       <c r="W2">
-        <v>0.119084416722094</v>
+        <v>0.119054402681877</v>
       </c>
       <c r="X2">
-        <v>0.122189727796301</v>
+        <v>0.127099494667853</v>
       </c>
       <c r="Y2">
         <v>1.34168011100219</v>
       </c>
       <c r="Z2">
-        <v>1.39853168045027</v>
+        <v>1.48902879604494</v>
       </c>
       <c r="AA2">
         <v>9666.299999999999</v>
@@ -1236,7 +1236,7 @@
         <v>7949.2</v>
       </c>
       <c r="AK2">
-        <v>0.05462137816692637</v>
+        <v>0.05459900767788711</v>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
@@ -1424,13 +1424,13 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>0.08462234127456514</v>
+        <v>0.08460644136890352</v>
       </c>
       <c r="C2">
-        <v>15842.90248313403</v>
+        <v>15843.1314156912</v>
       </c>
       <c r="D2">
-        <v>13962.80248313403</v>
+        <v>13963.0314156912</v>
       </c>
       <c r="E2">
         <v>-9666.299999999999</v>
@@ -1475,19 +1475,19 @@
         <v>0</v>
       </c>
       <c r="S2">
-        <v>0.08462234127456514</v>
+        <v>0.08460644136890352</v>
       </c>
       <c r="T2">
         <v>0.7107536019307608</v>
       </c>
       <c r="U2">
-        <v>0.06008110587651873</v>
+        <v>0.05868110587651873</v>
       </c>
       <c r="V2">
         <v>0.27</v>
       </c>
       <c r="W2">
-        <v>0.04385920728985867</v>
+        <v>0.04283720728985867</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -1506,13 +1506,13 @@
         <v>0.01</v>
       </c>
       <c r="B3">
-        <v>0.08449811302602242</v>
+        <v>0.08447203605010607</v>
       </c>
       <c r="C3">
-        <v>15711.57071511077</v>
+        <v>15715.50516877711</v>
       </c>
       <c r="D3">
-        <v>14007.62571511077</v>
+        <v>14011.56016877711</v>
       </c>
       <c r="E3">
         <v>-9490.144999999999</v>
@@ -1539,37 +1539,37 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M3">
-        <v>10.58358720567816</v>
+        <v>10.33697020567816</v>
       </c>
       <c r="N3">
-        <v>2017.549746127655</v>
+        <v>2017.796363127655</v>
       </c>
       <c r="O3">
-        <v>544.7384314544669</v>
+        <v>544.8050180444669</v>
       </c>
       <c r="P3">
-        <v>1472.811314673188</v>
+        <v>1472.991345083188</v>
       </c>
       <c r="Q3">
-        <v>2292.011314673188</v>
+        <v>2292.191345083188</v>
       </c>
       <c r="R3">
         <v>0.0101010101010101</v>
       </c>
       <c r="S3">
-        <v>0.0849086070233574</v>
+        <v>0.08489258987596716</v>
       </c>
       <c r="T3">
         <v>0.7159945123288362</v>
       </c>
       <c r="U3">
-        <v>0.06008110587651873</v>
+        <v>0.05868110587651873</v>
       </c>
       <c r="V3">
         <v>0.27</v>
       </c>
       <c r="W3">
-        <v>0.04385920728985867</v>
+        <v>0.04283720728985867</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>191.6300488595424</v>
+        <v>196.20191342133</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1588,13 +1588,13 @@
         <v>0.02</v>
       </c>
       <c r="B4">
-        <v>0.08437388477747965</v>
+        <v>0.08433763073130862</v>
       </c>
       <c r="C4">
-        <v>15580.527655971</v>
+        <v>15588.21742334355</v>
       </c>
       <c r="D4">
-        <v>14052.737655971</v>
+        <v>14060.42742334354</v>
       </c>
       <c r="E4">
         <v>-9313.99</v>
@@ -1621,37 +1621,37 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M4">
-        <v>21.16717441135631</v>
+        <v>20.67394041135631</v>
       </c>
       <c r="N4">
-        <v>2006.966158921977</v>
+        <v>2007.459392921977</v>
       </c>
       <c r="O4">
-        <v>541.8808629089338</v>
+        <v>542.0140360889337</v>
       </c>
       <c r="P4">
-        <v>1465.085296013043</v>
+        <v>1465.445356833043</v>
       </c>
       <c r="Q4">
-        <v>2284.285296013043</v>
+        <v>2284.645356833043</v>
       </c>
       <c r="R4">
         <v>0.02040816326530612</v>
       </c>
       <c r="S4">
-        <v>0.08520071493028825</v>
+        <v>0.08518457814848107</v>
       </c>
       <c r="T4">
         <v>0.7213423800819742</v>
       </c>
       <c r="U4">
-        <v>0.06008110587651873</v>
+        <v>0.05868110587651873</v>
       </c>
       <c r="V4">
         <v>0.27</v>
       </c>
       <c r="W4">
-        <v>0.04385920728985867</v>
+        <v>0.04283720728985867</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>95.8150244297712</v>
+        <v>98.10095671066499</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1670,13 +1670,13 @@
         <v>0.03</v>
       </c>
       <c r="B5">
-        <v>0.08424965652893691</v>
+        <v>0.08420322541251116</v>
       </c>
       <c r="C5">
-        <v>15449.77610411151</v>
+        <v>15461.27173349819</v>
       </c>
       <c r="D5">
-        <v>14098.14110411151</v>
+        <v>14109.63673349819</v>
       </c>
       <c r="E5">
         <v>-9137.834999999999</v>
@@ -1703,37 +1703,37 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M5">
-        <v>31.75076161703447</v>
+        <v>31.01091061703447</v>
       </c>
       <c r="N5">
-        <v>1996.382571716299</v>
+        <v>1997.122422716299</v>
       </c>
       <c r="O5">
-        <v>539.0232943634007</v>
+        <v>539.2230541334008</v>
       </c>
       <c r="P5">
-        <v>1457.359277352898</v>
+        <v>1457.899368582898</v>
       </c>
       <c r="Q5">
-        <v>2276.559277352898</v>
+        <v>2277.099368582898</v>
       </c>
       <c r="R5">
         <v>0.03092783505154639</v>
       </c>
       <c r="S5">
-        <v>0.08549884568066099</v>
+        <v>0.08548258679774784</v>
       </c>
       <c r="T5">
         <v>0.7268005131496099</v>
       </c>
       <c r="U5">
-        <v>0.06008110587651873</v>
+        <v>0.05868110587651873</v>
       </c>
       <c r="V5">
         <v>0.27</v>
       </c>
       <c r="W5">
-        <v>0.04385920728985867</v>
+        <v>0.04283720728985867</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>63.87668295318081</v>
+        <v>65.40063780710999</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1752,13 +1752,13 @@
         <v>0.04</v>
       </c>
       <c r="B6">
-        <v>0.08412542828039418</v>
+        <v>0.08406882009371372</v>
       </c>
       <c r="C6">
-        <v>15319.31889421208</v>
+        <v>15334.67170327876</v>
       </c>
       <c r="D6">
-        <v>14143.83889421208</v>
+        <v>14159.19170327876</v>
       </c>
       <c r="E6">
         <v>-8961.679999999998</v>
@@ -1785,37 +1785,37 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M6">
-        <v>42.33434882271263</v>
+        <v>41.34788082271263</v>
       </c>
       <c r="N6">
-        <v>1985.798984510621</v>
+        <v>1986.785452510621</v>
       </c>
       <c r="O6">
-        <v>536.1657258178676</v>
+        <v>536.4320721778676</v>
       </c>
       <c r="P6">
-        <v>1449.633258692753</v>
+        <v>1450.353380332753</v>
       </c>
       <c r="Q6">
-        <v>2268.833258692753</v>
+        <v>2269.553380332753</v>
       </c>
       <c r="R6">
         <v>0.04166666666666667</v>
       </c>
       <c r="S6">
-        <v>0.08580318748833315</v>
+        <v>0.08578680396054102</v>
       </c>
       <c r="T6">
         <v>0.7323723573228215</v>
       </c>
       <c r="U6">
-        <v>0.06008110587651873</v>
+        <v>0.05868110587651873</v>
       </c>
       <c r="V6">
         <v>0.27</v>
       </c>
       <c r="W6">
-        <v>0.04385920728985867</v>
+        <v>0.04283720728985867</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>47.90751221488561</v>
+        <v>49.05047835533249</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1834,13 +1834,13 @@
         <v>0.05</v>
       </c>
       <c r="B7">
-        <v>0.08400120003185142</v>
+        <v>0.08393441477491626</v>
       </c>
       <c r="C7">
-        <v>15189.15889782542</v>
+        <v>15208.42098753292</v>
       </c>
       <c r="D7">
-        <v>14189.83389782542</v>
+        <v>14209.09598753292</v>
       </c>
       <c r="E7">
         <v>-8785.525</v>
@@ -1867,37 +1867,37 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M7">
-        <v>52.91793602839079</v>
+        <v>51.68485102839079</v>
       </c>
       <c r="N7">
-        <v>1975.215397304942</v>
+        <v>1976.448482304942</v>
       </c>
       <c r="O7">
-        <v>533.3081572723345</v>
+        <v>533.6410902223345</v>
       </c>
       <c r="P7">
-        <v>1441.907240032608</v>
+        <v>1442.807392082608</v>
       </c>
       <c r="Q7">
-        <v>2261.107240032607</v>
+        <v>2262.007392082608</v>
       </c>
       <c r="R7">
         <v>0.05263157894736843</v>
       </c>
       <c r="S7">
-        <v>0.08611393649195631</v>
+        <v>0.08609742569518244</v>
       </c>
       <c r="T7">
         <v>0.7380615034786268</v>
       </c>
       <c r="U7">
-        <v>0.06008110587651873</v>
+        <v>0.05868110587651873</v>
       </c>
       <c r="V7">
         <v>0.27</v>
       </c>
       <c r="W7">
-        <v>0.04385920728985867</v>
+        <v>0.04283720728985867</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>38.32600977190848</v>
+        <v>39.240382684266</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1916,13 +1916,13 @@
         <v>0.06</v>
       </c>
       <c r="B8">
-        <v>0.08387697178330869</v>
+        <v>0.0838000094561188</v>
       </c>
       <c r="C8">
-        <v>15059.2990239786</v>
+        <v>15082.52329281684</v>
       </c>
       <c r="D8">
-        <v>14236.1290239786</v>
+        <v>14259.35329281684</v>
       </c>
       <c r="E8">
         <v>-8609.369999999999</v>
@@ -1949,37 +1949,37 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M8">
-        <v>63.50152323406894</v>
+        <v>62.02182123406894</v>
       </c>
       <c r="N8">
-        <v>1964.631810099264</v>
+        <v>1966.111512099264</v>
       </c>
       <c r="O8">
-        <v>530.4505887268015</v>
+        <v>530.8501082668014</v>
       </c>
       <c r="P8">
-        <v>1434.181221372463</v>
+        <v>1435.261403832463</v>
       </c>
       <c r="Q8">
-        <v>2253.381221372463</v>
+        <v>2254.461403832463</v>
       </c>
       <c r="R8">
         <v>0.06382978723404255</v>
       </c>
       <c r="S8">
-        <v>0.08643129717650763</v>
+        <v>0.08641465640290137</v>
       </c>
       <c r="T8">
         <v>0.7438716952973218</v>
       </c>
       <c r="U8">
-        <v>0.06008110587651873</v>
+        <v>0.05868110587651873</v>
       </c>
       <c r="V8">
         <v>0.27</v>
       </c>
       <c r="W8">
-        <v>0.04385920728985867</v>
+        <v>0.04283720728985867</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>31.93834147659041</v>
+        <v>32.70031890355499</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1998,13 +1998,13 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="B9">
-        <v>0.08375274353476596</v>
+        <v>0.08366560413732135</v>
       </c>
       <c r="C9">
-        <v>14929.74221978642</v>
+        <v>14956.9823783129</v>
       </c>
       <c r="D9">
-        <v>14282.72721978642</v>
+        <v>14309.9673783129</v>
       </c>
       <c r="E9">
         <v>-8433.215</v>
@@ -2031,37 +2031,37 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M9">
-        <v>74.0851104397471</v>
+        <v>72.35879143974709</v>
       </c>
       <c r="N9">
-        <v>1954.048222893586</v>
+        <v>1955.774541893586</v>
       </c>
       <c r="O9">
-        <v>527.5930201812683</v>
+        <v>528.0591263112683</v>
       </c>
       <c r="P9">
-        <v>1426.455202712318</v>
+        <v>1427.715415582318</v>
       </c>
       <c r="Q9">
-        <v>2245.655202712318</v>
+        <v>2246.915415582318</v>
       </c>
       <c r="R9">
         <v>0.07526881720430109</v>
       </c>
       <c r="S9">
-        <v>0.08675548282201705</v>
+        <v>0.0867387092763777</v>
       </c>
       <c r="T9">
         <v>0.749806837477709</v>
       </c>
       <c r="U9">
-        <v>0.06008110587651873</v>
+        <v>0.05868110587651873</v>
       </c>
       <c r="V9">
         <v>0.27</v>
       </c>
       <c r="W9">
-        <v>0.04385920728985867</v>
+        <v>0.04283720728985867</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>27.37572126564892</v>
+        <v>28.02884477447571</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2080,13 +2080,13 @@
         <v>0.08</v>
       </c>
       <c r="B10">
-        <v>0.08362851528622323</v>
+        <v>0.08353119881852392</v>
       </c>
       <c r="C10">
-        <v>14800.49147107682</v>
+        <v>14831.80205676704</v>
       </c>
       <c r="D10">
-        <v>14329.63147107682</v>
+        <v>14360.94205676703</v>
       </c>
       <c r="E10">
         <v>-8257.059999999999</v>
@@ -2113,37 +2113,37 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M10">
-        <v>84.66869764542525</v>
+        <v>82.69576164542525</v>
       </c>
       <c r="N10">
-        <v>1943.464635687908</v>
+        <v>1945.437571687908</v>
       </c>
       <c r="O10">
-        <v>524.7354516357352</v>
+        <v>525.2681443557352</v>
       </c>
       <c r="P10">
-        <v>1418.729184052173</v>
+        <v>1420.169427332173</v>
       </c>
       <c r="Q10">
-        <v>2237.929184052173</v>
+        <v>2239.369427332173</v>
       </c>
       <c r="R10">
         <v>0.08695652173913043</v>
       </c>
       <c r="S10">
-        <v>0.08708671598155927</v>
+        <v>0.08706980677753828</v>
       </c>
       <c r="T10">
         <v>0.7558710044881047</v>
       </c>
       <c r="U10">
-        <v>0.06008110587651873</v>
+        <v>0.05868110587651873</v>
       </c>
       <c r="V10">
         <v>0.27</v>
       </c>
       <c r="W10">
-        <v>0.04385920728985867</v>
+        <v>0.04283720728985867</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>23.9537561074428</v>
+        <v>24.52523917766625</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2162,13 +2162,13 @@
         <v>0.09</v>
       </c>
       <c r="B11">
-        <v>0.08350428703768049</v>
+        <v>0.08339679349972645</v>
       </c>
       <c r="C11">
-        <v>14671.54980302859</v>
+        <v>14706.98619544613</v>
       </c>
       <c r="D11">
-        <v>14376.84480302859</v>
+        <v>14412.28119544613</v>
       </c>
       <c r="E11">
         <v>-8080.904999999999</v>
@@ -2195,37 +2195,37 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M11">
-        <v>95.25228485110341</v>
+        <v>93.03273185110341</v>
       </c>
       <c r="N11">
-        <v>1932.88104848223</v>
+        <v>1935.10060148223</v>
       </c>
       <c r="O11">
-        <v>521.8778830902021</v>
+        <v>522.4771624002021</v>
       </c>
       <c r="P11">
-        <v>1411.003165392028</v>
+        <v>1412.623439082028</v>
       </c>
       <c r="Q11">
-        <v>2230.203165392028</v>
+        <v>2231.823439082028</v>
       </c>
       <c r="R11">
         <v>0.0989010989010989</v>
       </c>
       <c r="S11">
-        <v>0.08742522899076177</v>
+        <v>0.08740818114685624</v>
       </c>
       <c r="T11">
         <v>0.7620684498943333</v>
       </c>
       <c r="U11">
-        <v>0.06008110587651873</v>
+        <v>0.05868110587651873</v>
       </c>
       <c r="V11">
         <v>0.27</v>
       </c>
       <c r="W11">
-        <v>0.04385920728985867</v>
+        <v>0.04283720728985867</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>21.29222765106027</v>
+        <v>21.80021260237</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2244,13 +2244,13 @@
         <v>0.1</v>
       </c>
       <c r="B12">
-        <v>0.08338005878913776</v>
+        <v>0.083262388180929</v>
       </c>
       <c r="C12">
-        <v>14542.9202808218</v>
+        <v>14582.53871711605</v>
       </c>
       <c r="D12">
-        <v>14424.3702808218</v>
+        <v>14463.98871711605</v>
       </c>
       <c r="E12">
         <v>-7904.749999999999</v>
@@ -2277,37 +2277,37 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M12">
-        <v>105.8358720567816</v>
+        <v>103.3697020567816</v>
       </c>
       <c r="N12">
-        <v>1922.297461276552</v>
+        <v>1924.763631276552</v>
       </c>
       <c r="O12">
-        <v>519.020314544669</v>
+        <v>519.6861804446689</v>
       </c>
       <c r="P12">
-        <v>1403.277146731883</v>
+        <v>1405.077450831883</v>
       </c>
       <c r="Q12">
-        <v>2222.477146731882</v>
+        <v>2224.277450831883</v>
       </c>
       <c r="R12">
         <v>0.1111111111111111</v>
       </c>
       <c r="S12">
-        <v>0.08777126451127987</v>
+        <v>0.08775407494660348</v>
       </c>
       <c r="T12">
         <v>0.7684036163095892</v>
       </c>
       <c r="U12">
-        <v>0.06008110587651873</v>
+        <v>0.05868110587651873</v>
       </c>
       <c r="V12">
         <v>0.27</v>
       </c>
       <c r="W12">
-        <v>0.04385920728985867</v>
+        <v>0.04283720728985867</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>19.16300488595424</v>
+        <v>19.620191342133</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2326,13 +2326,13 @@
         <v>0.11</v>
       </c>
       <c r="B13">
-        <v>0.083255830540595</v>
+        <v>0.08312798286213155</v>
       </c>
       <c r="C13">
-        <v>14414.6060103012</v>
+        <v>14458.46360104085</v>
       </c>
       <c r="D13">
-        <v>14472.2110103012</v>
+        <v>14516.06860104085</v>
       </c>
       <c r="E13">
         <v>-7728.594999999999</v>
@@ -2359,37 +2359,37 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M13">
-        <v>116.4194592624597</v>
+        <v>113.7066722624597</v>
       </c>
       <c r="N13">
-        <v>1911.713874070874</v>
+        <v>1914.426661070873</v>
       </c>
       <c r="O13">
-        <v>516.1627459991358</v>
+        <v>516.8951984891359</v>
       </c>
       <c r="P13">
-        <v>1395.551128071738</v>
+        <v>1397.531462581738</v>
       </c>
       <c r="Q13">
-        <v>2214.751128071738</v>
+        <v>2216.731462581738</v>
       </c>
       <c r="R13">
         <v>0.1235955056179775</v>
       </c>
       <c r="S13">
-        <v>0.08812507611091074</v>
+        <v>0.08810774164072707</v>
       </c>
       <c r="T13">
         <v>0.7748811460150755</v>
       </c>
       <c r="U13">
-        <v>0.06008110587651873</v>
+        <v>0.05868110587651873</v>
       </c>
       <c r="V13">
         <v>0.27</v>
       </c>
       <c r="W13">
-        <v>0.04385920728985867</v>
+        <v>0.04283720728985867</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>17.42091353268567</v>
+        <v>17.83653758375727</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2408,13 +2408,13 @@
         <v>0.12</v>
       </c>
       <c r="B14">
-        <v>0.08313160229205227</v>
+        <v>0.08299357754333408</v>
       </c>
       <c r="C14">
-        <v>14286.61013865271</v>
+        <v>14334.76488400356</v>
       </c>
       <c r="D14">
-        <v>14520.37013865271</v>
+        <v>14568.52488400356</v>
       </c>
       <c r="E14">
         <v>-7552.439999999999</v>
@@ -2441,37 +2441,37 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M14">
-        <v>127.0030464681379</v>
+        <v>124.0436424681379</v>
       </c>
       <c r="N14">
-        <v>1901.130286865195</v>
+        <v>1904.089690865195</v>
       </c>
       <c r="O14">
-        <v>513.3051774536028</v>
+        <v>514.1042165336028</v>
       </c>
       <c r="P14">
-        <v>1387.825109411593</v>
+        <v>1389.985474331593</v>
       </c>
       <c r="Q14">
-        <v>2207.025109411592</v>
+        <v>2209.185474331593</v>
       </c>
       <c r="R14">
         <v>0.1363636363636364</v>
       </c>
       <c r="S14">
-        <v>0.08848692888326049</v>
+        <v>0.08846944621426256</v>
       </c>
       <c r="T14">
         <v>0.7815058923047774</v>
       </c>
       <c r="U14">
-        <v>0.06008110587651873</v>
+        <v>0.05868110587651873</v>
       </c>
       <c r="V14">
         <v>0.27</v>
       </c>
       <c r="W14">
-        <v>0.04385920728985867</v>
+        <v>0.04283720728985867</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2479,7 +2479,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>15.9691707382952</v>
+        <v>16.3501594517775</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2490,13 +2490,13 @@
         <v>0.13</v>
       </c>
       <c r="B15">
-        <v>0.08300737404350952</v>
+        <v>0.08285917222453663</v>
       </c>
       <c r="C15">
-        <v>14158.9358550937</v>
+        <v>14211.44666134924</v>
       </c>
       <c r="D15">
-        <v>14568.8508550937</v>
+        <v>14621.36166134924</v>
       </c>
       <c r="E15">
         <v>-7376.285</v>
@@ -2523,37 +2523,37 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M15">
-        <v>137.586633673816</v>
+        <v>134.380612673816</v>
       </c>
       <c r="N15">
-        <v>1890.546699659517</v>
+        <v>1893.752720659517</v>
       </c>
       <c r="O15">
-        <v>510.4476089080696</v>
+        <v>511.3132345780696</v>
       </c>
       <c r="P15">
-        <v>1380.099090751447</v>
+        <v>1382.439486081448</v>
       </c>
       <c r="Q15">
-        <v>2199.299090751447</v>
+        <v>2201.639486081447</v>
       </c>
       <c r="R15">
         <v>0.1494252873563219</v>
       </c>
       <c r="S15">
-        <v>0.08885710011014701</v>
+        <v>0.08883946583546554</v>
       </c>
       <c r="T15">
         <v>0.7882829316126334</v>
       </c>
       <c r="U15">
-        <v>0.06008110587651873</v>
+        <v>0.05868110587651873</v>
       </c>
       <c r="V15">
         <v>0.27</v>
       </c>
       <c r="W15">
-        <v>0.04385920728985867</v>
+        <v>0.04283720728985867</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2561,7 +2561,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>14.74077298919557</v>
+        <v>15.09245487856384</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2572,13 +2572,13 @@
         <v>0.14</v>
       </c>
       <c r="B16">
-        <v>0.08288314579496679</v>
+        <v>0.08272476690573918</v>
       </c>
       <c r="C16">
-        <v>14031.58639157691</v>
+        <v>14088.51308805082</v>
       </c>
       <c r="D16">
-        <v>14617.65639157691</v>
+        <v>14674.58308805082</v>
       </c>
       <c r="E16">
         <v>-7200.129999999999</v>
@@ -2605,37 +2605,37 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M16">
-        <v>148.1702208794942</v>
+        <v>144.7175828794942</v>
       </c>
       <c r="N16">
-        <v>1879.963112453839</v>
+        <v>1883.415750453839</v>
       </c>
       <c r="O16">
-        <v>507.5900403625366</v>
+        <v>508.5222526225366</v>
       </c>
       <c r="P16">
-        <v>1372.373072091302</v>
+        <v>1374.893497831303</v>
       </c>
       <c r="Q16">
-        <v>2191.573072091302</v>
+        <v>2194.093497831303</v>
       </c>
       <c r="R16">
         <v>0.1627906976744186</v>
       </c>
       <c r="S16">
-        <v>0.08923587997021695</v>
+        <v>0.08921809056413835</v>
       </c>
       <c r="T16">
         <v>0.7952175764857884</v>
       </c>
       <c r="U16">
-        <v>0.06008110587651873</v>
+        <v>0.05868110587651873</v>
       </c>
       <c r="V16">
         <v>0.27</v>
       </c>
       <c r="W16">
-        <v>0.04385920728985867</v>
+        <v>0.04283720728985867</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>13.68786063282446</v>
+        <v>14.01442238723786</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2654,13 +2654,13 @@
         <v>0.15</v>
       </c>
       <c r="B17">
-        <v>0.08275891754642406</v>
+        <v>0.08259036158694175</v>
       </c>
       <c r="C17">
-        <v>13904.56502350875</v>
+        <v>13965.96837979823</v>
       </c>
       <c r="D17">
-        <v>14666.79002350875</v>
+        <v>14728.19337979823</v>
       </c>
       <c r="E17">
         <v>-7023.974999999999</v>
@@ -2687,37 +2687,37 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M17">
-        <v>158.7538080851724</v>
+        <v>155.0545530851723</v>
       </c>
       <c r="N17">
-        <v>1869.379525248161</v>
+        <v>1873.078780248161</v>
       </c>
       <c r="O17">
-        <v>504.7324718170035</v>
+        <v>505.7312706670035</v>
       </c>
       <c r="P17">
-        <v>1364.647053431157</v>
+        <v>1367.347509581158</v>
       </c>
       <c r="Q17">
-        <v>2183.847053431157</v>
+        <v>2186.547509581157</v>
       </c>
       <c r="R17">
         <v>0.1764705882352941</v>
       </c>
       <c r="S17">
-        <v>0.08962357229758265</v>
+        <v>0.0896056241099564</v>
       </c>
       <c r="T17">
         <v>0.8023153894736059</v>
       </c>
       <c r="U17">
-        <v>0.06008110587651873</v>
+        <v>0.05868110587651873</v>
       </c>
       <c r="V17">
         <v>0.27</v>
       </c>
       <c r="W17">
-        <v>0.04385920728985867</v>
+        <v>0.04283720728985867</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>12.77533659063616</v>
+        <v>13.080127561422</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2736,13 +2736,13 @@
         <v>0.16</v>
       </c>
       <c r="B18">
-        <v>0.08263468929788131</v>
+        <v>0.08245595626814428</v>
       </c>
       <c r="C18">
-        <v>13777.875070482</v>
+        <v>13843.81681411166</v>
       </c>
       <c r="D18">
-        <v>14716.255070482</v>
+        <v>14782.19681411166</v>
       </c>
       <c r="E18">
         <v>-6847.82</v>
@@ -2769,37 +2769,37 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M18">
-        <v>169.3373952908505</v>
+        <v>165.3915232908505</v>
       </c>
       <c r="N18">
-        <v>1858.795938042483</v>
+        <v>1862.741810042483</v>
       </c>
       <c r="O18">
-        <v>501.8749032714704</v>
+        <v>502.9402887114704</v>
       </c>
       <c r="P18">
-        <v>1356.921034771012</v>
+        <v>1359.801521331012</v>
       </c>
       <c r="Q18">
-        <v>2176.121034771012</v>
+        <v>2179.001521331012</v>
       </c>
       <c r="R18">
         <v>0.1904761904761905</v>
       </c>
       <c r="S18">
-        <v>0.09002049539464753</v>
+        <v>0.09000238464496059</v>
       </c>
       <c r="T18">
         <v>0.8095821980087523</v>
       </c>
       <c r="U18">
-        <v>0.06008110587651873</v>
+        <v>0.05868110587651873</v>
       </c>
       <c r="V18">
         <v>0.27</v>
       </c>
       <c r="W18">
-        <v>0.04385920728985867</v>
+        <v>0.04283720728985867</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>11.9768780537214</v>
+        <v>12.26261958883312</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2818,13 +2818,13 @@
         <v>0.17</v>
       </c>
       <c r="B19">
-        <v>0.08251046104933857</v>
+        <v>0.08232155094934683</v>
       </c>
       <c r="C19">
-        <v>13651.51989702346</v>
+        <v>13722.06273147913</v>
       </c>
       <c r="D19">
-        <v>14766.05489702346</v>
+        <v>14836.59773147913</v>
       </c>
       <c r="E19">
         <v>-6671.664999999999</v>
@@ -2851,37 +2851,37 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M19">
-        <v>179.9209824965287</v>
+        <v>175.7284934965287</v>
       </c>
       <c r="N19">
-        <v>1848.212350836804</v>
+        <v>1852.404839836805</v>
       </c>
       <c r="O19">
-        <v>499.0173347259372</v>
+        <v>500.1493067559372</v>
       </c>
       <c r="P19">
-        <v>1349.195016110867</v>
+        <v>1352.255533080867</v>
       </c>
       <c r="Q19">
-        <v>2168.395016110867</v>
+        <v>2171.455533080867</v>
       </c>
       <c r="R19">
         <v>0.2048192771084338</v>
       </c>
       <c r="S19">
-        <v>0.09042698290368988</v>
+        <v>0.09040870567478416</v>
       </c>
       <c r="T19">
         <v>0.8170241103640228</v>
       </c>
       <c r="U19">
-        <v>0.06008110587651873</v>
+        <v>0.05868110587651873</v>
       </c>
       <c r="V19">
         <v>0.27</v>
       </c>
       <c r="W19">
-        <v>0.04385920728985867</v>
+        <v>0.04283720728985867</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>11.2723558152672</v>
+        <v>11.54128902478412</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2900,13 +2900,13 @@
         <v>0.18</v>
       </c>
       <c r="B20">
-        <v>0.08238623280079584</v>
+        <v>0.08218714563054939</v>
       </c>
       <c r="C20">
-        <v>13525.50291335684</v>
+        <v>13600.71053651956</v>
       </c>
       <c r="D20">
-        <v>14816.19291335684</v>
+        <v>14891.40053651956</v>
       </c>
       <c r="E20">
         <v>-6495.509999999999</v>
@@ -2933,37 +2933,37 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M20">
-        <v>190.5045697022068</v>
+        <v>186.0654637022068</v>
       </c>
       <c r="N20">
-        <v>1837.628763631126</v>
+        <v>1842.067869631126</v>
       </c>
       <c r="O20">
-        <v>496.1597661804041</v>
+        <v>497.3583248004041</v>
       </c>
       <c r="P20">
-        <v>1341.468997450722</v>
+        <v>1344.709544830722</v>
       </c>
       <c r="Q20">
-        <v>2160.668997450722</v>
+        <v>2163.909544830722</v>
       </c>
       <c r="R20">
         <v>0.2195121951219512</v>
       </c>
       <c r="S20">
-        <v>0.09084338474222106</v>
+        <v>0.09082493697362783</v>
       </c>
       <c r="T20">
         <v>0.8246475327767387</v>
       </c>
       <c r="U20">
-        <v>0.06008110587651873</v>
+        <v>0.05868110587651873</v>
       </c>
       <c r="V20">
         <v>0.27</v>
       </c>
       <c r="W20">
-        <v>0.04385920728985867</v>
+        <v>0.04283720728985867</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>10.64611382553013</v>
+        <v>10.900106301185</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2982,13 +2982,13 @@
         <v>0.19</v>
       </c>
       <c r="B21">
-        <v>0.0822620045522531</v>
+        <v>0.08205274031175194</v>
       </c>
       <c r="C21">
-        <v>13399.82757618119</v>
+        <v>13479.76469917154</v>
       </c>
       <c r="D21">
-        <v>14866.67257618119</v>
+        <v>14946.60969917154</v>
       </c>
       <c r="E21">
         <v>-6319.355</v>
@@ -3015,37 +3015,37 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M21">
-        <v>201.088156907885</v>
+        <v>196.402433907885</v>
       </c>
       <c r="N21">
-        <v>1827.045176425448</v>
+        <v>1831.730899425448</v>
       </c>
       <c r="O21">
-        <v>493.302197634871</v>
+        <v>494.567342844871</v>
       </c>
       <c r="P21">
-        <v>1333.742978790577</v>
+        <v>1337.163556580577</v>
       </c>
       <c r="Q21">
-        <v>2152.942978790577</v>
+        <v>2156.363556580577</v>
       </c>
       <c r="R21">
         <v>0.2345679012345679</v>
       </c>
       <c r="S21">
-        <v>0.09127006810762955</v>
+        <v>0.09125144558849232</v>
       </c>
       <c r="T21">
         <v>0.8324591878416207</v>
       </c>
       <c r="U21">
-        <v>0.06008110587651873</v>
+        <v>0.05868110587651873</v>
       </c>
       <c r="V21">
         <v>0.27</v>
       </c>
       <c r="W21">
-        <v>0.04385920728985867</v>
+        <v>0.04283720728985867</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>10.08579204523907</v>
+        <v>10.32641649585947</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3064,13 +3064,13 @@
         <v>0.2</v>
       </c>
       <c r="B22">
-        <v>0.08213777630371036</v>
+        <v>0.08191833499295448</v>
       </c>
       <c r="C22">
-        <v>13274.49738946534</v>
+        <v>13359.22975590866</v>
       </c>
       <c r="D22">
-        <v>14917.49738946534</v>
+        <v>15002.22975590866</v>
       </c>
       <c r="E22">
         <v>-6143.199999999999</v>
@@ -3097,37 +3097,37 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M22">
-        <v>211.6717441135632</v>
+        <v>206.7394041135632</v>
       </c>
       <c r="N22">
-        <v>1816.46158921977</v>
+        <v>1821.39392921977</v>
       </c>
       <c r="O22">
-        <v>490.444629089338</v>
+        <v>491.776360889338</v>
       </c>
       <c r="P22">
-        <v>1326.016960130432</v>
+        <v>1329.617568330432</v>
       </c>
       <c r="Q22">
-        <v>2145.216960130432</v>
+        <v>2148.817568330432</v>
       </c>
       <c r="R22">
         <v>0.25</v>
       </c>
       <c r="S22">
-        <v>0.09170741855717328</v>
+        <v>0.09168861691872843</v>
       </c>
       <c r="T22">
         <v>0.8404661342831247</v>
       </c>
       <c r="U22">
-        <v>0.06008110587651873</v>
+        <v>0.05868110587651873</v>
       </c>
       <c r="V22">
         <v>0.27</v>
       </c>
       <c r="W22">
-        <v>0.04385920728985867</v>
+        <v>0.04283720728985867</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>9.58150244297712</v>
+        <v>9.810095671066499</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3146,13 +3146,13 @@
         <v>0.21</v>
       </c>
       <c r="B23">
-        <v>0.08201354805516763</v>
+        <v>0.08178392967415703</v>
       </c>
       <c r="C23">
-        <v>13149.51590525868</v>
+        <v>13239.11031098211</v>
       </c>
       <c r="D23">
-        <v>14968.67090525868</v>
+        <v>15058.26531098211</v>
       </c>
       <c r="E23">
         <v>-5967.045</v>
@@ -3179,37 +3179,37 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M23">
-        <v>222.2553313192413</v>
+        <v>217.0763743192413</v>
       </c>
       <c r="N23">
-        <v>1805.878002014092</v>
+        <v>1811.056959014092</v>
       </c>
       <c r="O23">
-        <v>487.5870605438049</v>
+        <v>488.9853789338048</v>
       </c>
       <c r="P23">
-        <v>1318.290941470287</v>
+        <v>1322.071580080287</v>
       </c>
       <c r="Q23">
-        <v>2137.490941470287</v>
+        <v>2141.271580080287</v>
       </c>
       <c r="R23">
         <v>0.2658227848101266</v>
       </c>
       <c r="S23">
-        <v>0.09215584116999657</v>
+        <v>0.0921368558775781</v>
       </c>
       <c r="T23">
         <v>0.8486757882294768</v>
       </c>
       <c r="U23">
-        <v>0.06008110587651873</v>
+        <v>0.05868110587651873</v>
       </c>
       <c r="V23">
         <v>0.27</v>
       </c>
       <c r="W23">
-        <v>0.04385920728985867</v>
+        <v>0.04283720728985867</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3217,7 +3217,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>9.125240421882973</v>
+        <v>9.342948258158572</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3228,13 +3228,13 @@
         <v>0.22</v>
       </c>
       <c r="B24">
-        <v>0.08188931980662487</v>
+        <v>0.08164952435535958</v>
       </c>
       <c r="C24">
-        <v>13024.88672451871</v>
+        <v>13119.41103769126</v>
       </c>
       <c r="D24">
-        <v>15020.19672451871</v>
+        <v>15114.72103769126</v>
       </c>
       <c r="E24">
         <v>-5790.889999999999</v>
@@ -3261,37 +3261,37 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M24">
-        <v>232.8389185249194</v>
+        <v>227.4133445249194</v>
       </c>
       <c r="N24">
-        <v>1795.294414808414</v>
+        <v>1800.719988808414</v>
       </c>
       <c r="O24">
-        <v>484.7294919982718</v>
+        <v>486.1943969782718</v>
       </c>
       <c r="P24">
-        <v>1310.564922810142</v>
+        <v>1314.525591830142</v>
       </c>
       <c r="Q24">
-        <v>2129.764922810142</v>
+        <v>2133.725591830142</v>
       </c>
       <c r="R24">
         <v>0.282051282051282</v>
       </c>
       <c r="S24">
-        <v>0.09261576179853329</v>
+        <v>0.09259658814306496</v>
       </c>
       <c r="T24">
         <v>0.8570959461231713</v>
       </c>
       <c r="U24">
-        <v>0.06008110587651873</v>
+        <v>0.05868110587651873</v>
       </c>
       <c r="V24">
         <v>0.27</v>
       </c>
       <c r="W24">
-        <v>0.04385920728985867</v>
+        <v>0.04283720728985867</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>8.710456766342837</v>
+        <v>8.918268791878635</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3310,13 +3310,13 @@
         <v>0.23</v>
       </c>
       <c r="B25">
-        <v>0.08194978155808214</v>
+        <v>0.08176696903656212</v>
       </c>
       <c r="C25">
-        <v>12823.60992952976</v>
+        <v>12893.90120904466</v>
       </c>
       <c r="D25">
-        <v>14995.07492952976</v>
+        <v>15065.36620904466</v>
       </c>
       <c r="E25">
         <v>-5614.734999999999</v>
@@ -3343,37 +3343,37 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M25">
-        <v>247.8792272305976</v>
+        <v>243.8276622305976</v>
       </c>
       <c r="N25">
-        <v>1780.254106102736</v>
+        <v>1784.305671102736</v>
       </c>
       <c r="O25">
-        <v>480.6686086477387</v>
+        <v>481.7625311977387</v>
       </c>
       <c r="P25">
-        <v>1299.585497454997</v>
+        <v>1302.543139904997</v>
       </c>
       <c r="Q25">
-        <v>2118.785497454997</v>
+        <v>2121.743139904997</v>
       </c>
       <c r="R25">
         <v>0.2987012987012987</v>
       </c>
       <c r="S25">
-        <v>0.0930876284174216</v>
+        <v>0.09306826150635665</v>
       </c>
       <c r="T25">
         <v>0.865734809416702</v>
       </c>
       <c r="U25">
-        <v>0.06118110587651873</v>
+        <v>0.06018110587651872</v>
       </c>
       <c r="V25">
         <v>0.27</v>
       </c>
       <c r="W25">
-        <v>0.04466220728985867</v>
+        <v>0.04393220728985867</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3381,7 +3381,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>8.181941488169144</v>
+        <v>8.317896807849662</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3392,13 +3392,13 @@
         <v>0.24</v>
       </c>
       <c r="B26">
-        <v>0.0818335833095394</v>
+        <v>0.08164351371776465</v>
       </c>
       <c r="C26">
-        <v>12695.8098607785</v>
+        <v>12769.6356416149</v>
       </c>
       <c r="D26">
-        <v>15043.42986077851</v>
+        <v>15117.2556416149</v>
       </c>
       <c r="E26">
         <v>-5438.579999999999</v>
@@ -3425,37 +3425,37 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M26">
-        <v>258.6565849362757</v>
+        <v>254.4288649362757</v>
       </c>
       <c r="N26">
-        <v>1769.476748397057</v>
+        <v>1773.704468397058</v>
       </c>
       <c r="O26">
-        <v>477.7587220672056</v>
+        <v>478.9002064672056</v>
       </c>
       <c r="P26">
-        <v>1291.718026329852</v>
+        <v>1294.804261929852</v>
       </c>
       <c r="Q26">
-        <v>2110.918026329852</v>
+        <v>2114.004261929852</v>
       </c>
       <c r="R26">
         <v>0.3157894736842105</v>
       </c>
       <c r="S26">
-        <v>0.09357191257891226</v>
+        <v>0.09355234732657708</v>
       </c>
       <c r="T26">
         <v>0.8746010112179572</v>
       </c>
       <c r="U26">
-        <v>0.06118110587651873</v>
+        <v>0.06018110587651872</v>
       </c>
       <c r="V26">
         <v>0.27</v>
       </c>
       <c r="W26">
-        <v>0.04466220728985867</v>
+        <v>0.04393220728985867</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>7.84102725949543</v>
+        <v>7.971317774189259</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3474,13 +3474,13 @@
         <v>0.25</v>
       </c>
       <c r="B27">
-        <v>0.08171738506099666</v>
+        <v>0.0815200583989672</v>
       </c>
       <c r="C27">
-        <v>12568.32266326272</v>
+        <v>12645.72875369055</v>
       </c>
       <c r="D27">
-        <v>15092.09766326272</v>
+        <v>15169.50375369055</v>
       </c>
       <c r="E27">
         <v>-5262.424999999999</v>
@@ -3507,37 +3507,37 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M27">
-        <v>269.4339426419539</v>
+        <v>265.0300676419539</v>
       </c>
       <c r="N27">
-        <v>1758.699390691379</v>
+        <v>1763.103265691379</v>
       </c>
       <c r="O27">
-        <v>474.8488354866725</v>
+        <v>476.0378817366725</v>
       </c>
       <c r="P27">
-        <v>1283.850555204707</v>
+        <v>1287.065383954707</v>
       </c>
       <c r="Q27">
-        <v>2103.050555204707</v>
+        <v>2106.265383954707</v>
       </c>
       <c r="R27">
         <v>0.3333333333333333</v>
       </c>
       <c r="S27">
-        <v>0.09406911098470933</v>
+        <v>0.09404934210200339</v>
       </c>
       <c r="T27">
         <v>0.883703645067246</v>
       </c>
       <c r="U27">
-        <v>0.06118110587651873</v>
+        <v>0.06018110587651872</v>
       </c>
       <c r="V27">
         <v>0.27</v>
       </c>
       <c r="W27">
-        <v>0.04466220728985867</v>
+        <v>0.04393220728985867</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3545,7 +3545,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>7.527386169115614</v>
+        <v>7.652465063221689</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3556,13 +3556,13 @@
         <v>0.26</v>
       </c>
       <c r="B28">
-        <v>0.08160118681245392</v>
+        <v>0.08139660308016976</v>
       </c>
       <c r="C28">
-        <v>12441.1513833973</v>
+        <v>12522.18427716363</v>
       </c>
       <c r="D28">
-        <v>15141.0813833973</v>
+        <v>15222.11427716362</v>
       </c>
       <c r="E28">
         <v>-5086.27</v>
@@ -3589,37 +3589,37 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M28">
-        <v>280.2113003476321</v>
+        <v>275.631270347632</v>
       </c>
       <c r="N28">
-        <v>1747.922032985701</v>
+        <v>1752.502062985701</v>
       </c>
       <c r="O28">
-        <v>471.9389489061393</v>
+        <v>473.1755570061394</v>
       </c>
       <c r="P28">
-        <v>1275.983084079562</v>
+        <v>1279.326505979562</v>
       </c>
       <c r="Q28">
-        <v>2095.183084079562</v>
+        <v>2098.526505979562</v>
       </c>
       <c r="R28">
         <v>0.3513513513513514</v>
       </c>
       <c r="S28">
-        <v>0.09457974718525765</v>
+        <v>0.09455976916865744</v>
       </c>
       <c r="T28">
         <v>0.8930522960475964</v>
       </c>
       <c r="U28">
-        <v>0.06118110587651873</v>
+        <v>0.06018110587651872</v>
       </c>
       <c r="V28">
         <v>0.27</v>
       </c>
       <c r="W28">
-        <v>0.04466220728985867</v>
+        <v>0.04393220728985867</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3627,7 +3627,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>7.23787131645732</v>
+        <v>7.358139483867009</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3638,13 +3638,13 @@
         <v>0.27</v>
       </c>
       <c r="B29">
-        <v>0.08148498856391118</v>
+        <v>0.08127314776137229</v>
       </c>
       <c r="C29">
-        <v>12314.29910727635</v>
+        <v>12399.00599587775</v>
       </c>
       <c r="D29">
-        <v>15190.38410727636</v>
+        <v>15275.09099587775</v>
       </c>
       <c r="E29">
         <v>-4910.114999999999</v>
@@ -3671,37 +3671,37 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M29">
-        <v>290.9886580533102</v>
+        <v>286.2324730533102</v>
       </c>
       <c r="N29">
-        <v>1737.144675280023</v>
+        <v>1741.900860280023</v>
       </c>
       <c r="O29">
-        <v>469.0290623256062</v>
+        <v>470.3132322756062</v>
       </c>
       <c r="P29">
-        <v>1268.115612954417</v>
+        <v>1271.587628004417</v>
       </c>
       <c r="Q29">
-        <v>2087.315612954417</v>
+        <v>2090.787628004417</v>
       </c>
       <c r="R29">
         <v>0.3698630136986302</v>
       </c>
       <c r="S29">
-        <v>0.09510437341869772</v>
+        <v>0.09508418053850748</v>
       </c>
       <c r="T29">
         <v>0.9026570744520662</v>
       </c>
       <c r="U29">
-        <v>0.06118110587651873</v>
+        <v>0.06018110587651872</v>
       </c>
       <c r="V29">
         <v>0.27</v>
       </c>
       <c r="W29">
-        <v>0.04466220728985867</v>
+        <v>0.04393220728985867</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3709,7 +3709,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>6.969802008440381</v>
+        <v>7.085615799279341</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3720,13 +3720,13 @@
         <v>0.28</v>
       </c>
       <c r="B30">
-        <v>0.08181847031536844</v>
+        <v>0.08114969244257485</v>
       </c>
       <c r="C30">
-        <v>11997.50193527268</v>
+        <v>12276.19774653532</v>
       </c>
       <c r="D30">
-        <v>15049.74193527269</v>
+        <v>15328.43774653532</v>
       </c>
       <c r="E30">
         <v>-4733.959999999999</v>
@@ -3753,45 +3753,45 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M30">
-        <v>312.6171637589884</v>
+        <v>296.8336757589884</v>
       </c>
       <c r="N30">
-        <v>1715.516169574345</v>
+        <v>1731.299657574345</v>
       </c>
       <c r="O30">
-        <v>463.1893657850731</v>
+        <v>467.4509075450731</v>
       </c>
       <c r="P30">
-        <v>1252.326803789272</v>
+        <v>1263.848750029272</v>
       </c>
       <c r="Q30">
-        <v>2071.526803789272</v>
+        <v>2083.048750029272</v>
       </c>
       <c r="R30">
         <v>0.388888888888889</v>
       </c>
       <c r="S30">
-        <v>0.09564357260306668</v>
+        <v>0.09562315889085336</v>
       </c>
       <c r="T30">
         <v>0.91252865225666</v>
       </c>
       <c r="U30">
-        <v>0.06338110587651873</v>
+        <v>0.06018110587651872</v>
       </c>
       <c r="V30">
         <v>0.27</v>
       </c>
       <c r="W30">
-        <v>0.04626820728985867</v>
+        <v>0.04393220728985867</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y30">
-        <v>6.487594311670356</v>
+        <v>6.832558092162222</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3802,13 +3802,13 @@
         <v>0.29</v>
       </c>
       <c r="B31">
-        <v>0.0817183320668257</v>
+        <v>0.08138612712377739</v>
       </c>
       <c r="C31">
-        <v>11863.30475212272</v>
+        <v>11998.20041119691</v>
       </c>
       <c r="D31">
-        <v>15091.69975212272</v>
+        <v>15226.59541119691</v>
       </c>
       <c r="E31">
         <v>-4557.804999999999</v>
@@ -3835,37 +3835,37 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M31">
-        <v>323.7820624646665</v>
+        <v>316.1193199646665</v>
       </c>
       <c r="N31">
-        <v>1704.351270868667</v>
+        <v>1712.014013368667</v>
       </c>
       <c r="O31">
-        <v>460.17484313454</v>
+        <v>462.2437836095401</v>
       </c>
       <c r="P31">
-        <v>1244.176427734127</v>
+        <v>1249.770229759127</v>
       </c>
       <c r="Q31">
-        <v>2063.376427734127</v>
+        <v>2068.970229759127</v>
       </c>
       <c r="R31">
         <v>0.4084507042253521</v>
       </c>
       <c r="S31">
-        <v>0.09619796049685449</v>
+        <v>0.09617731973199772</v>
       </c>
       <c r="T31">
         <v>0.9226783026754679</v>
       </c>
       <c r="U31">
-        <v>0.06338110587651873</v>
+        <v>0.06188110587651872</v>
       </c>
       <c r="V31">
         <v>0.27</v>
       </c>
       <c r="W31">
-        <v>0.04626820728985867</v>
+        <v>0.04517320728985866</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3873,7 +3873,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>6.263884162992068</v>
+        <v>6.415720916899427</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3884,13 +3884,13 @@
         <v>0.3</v>
       </c>
       <c r="B32">
-        <v>0.08161819381828295</v>
+        <v>0.08127508180497994</v>
       </c>
       <c r="C32">
-        <v>11729.34217501198</v>
+        <v>11869.70822282709</v>
       </c>
       <c r="D32">
-        <v>15133.89217501198</v>
+        <v>15274.25822282709</v>
       </c>
       <c r="E32">
         <v>-4381.65</v>
@@ -3917,37 +3917,37 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M32">
-        <v>334.9469611703447</v>
+        <v>327.0199861703447</v>
       </c>
       <c r="N32">
-        <v>1693.186372162989</v>
+        <v>1701.113347162988</v>
       </c>
       <c r="O32">
-        <v>457.1603204840069</v>
+        <v>459.3006037340069</v>
       </c>
       <c r="P32">
-        <v>1236.026051678982</v>
+        <v>1241.812743428982</v>
       </c>
       <c r="Q32">
-        <v>2055.226051678982</v>
+        <v>2061.012743428982</v>
       </c>
       <c r="R32">
         <v>0.4285714285714286</v>
       </c>
       <c r="S32">
-        <v>0.09676818804475051</v>
+        <v>0.09674731374003193</v>
       </c>
       <c r="T32">
         <v>0.9331179431062416</v>
       </c>
       <c r="U32">
-        <v>0.06338110587651873</v>
+        <v>0.06188110587651872</v>
       </c>
       <c r="V32">
         <v>0.27</v>
       </c>
       <c r="W32">
-        <v>0.04626820728985867</v>
+        <v>0.04517320728985866</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>6.055088024225666</v>
+        <v>6.201863553002778</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3966,13 +3966,13 @@
         <v>0.31</v>
       </c>
       <c r="B33">
-        <v>0.08151805556974021</v>
+        <v>0.08116403648618248</v>
       </c>
       <c r="C33">
-        <v>11595.61617714737</v>
+        <v>11741.51536296376</v>
       </c>
       <c r="D33">
-        <v>15176.32117714737</v>
+        <v>15322.22036296377</v>
       </c>
       <c r="E33">
         <v>-4205.494999999999</v>
@@ -3999,37 +3999,37 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M33">
-        <v>346.1118598760228</v>
+        <v>337.9206523760229</v>
       </c>
       <c r="N33">
-        <v>1682.02147345731</v>
+        <v>1690.21268095731</v>
       </c>
       <c r="O33">
-        <v>454.1457978334738</v>
+        <v>456.3574238584738</v>
       </c>
       <c r="P33">
-        <v>1227.875675623837</v>
+        <v>1233.855257098837</v>
       </c>
       <c r="Q33">
-        <v>2047.075675623836</v>
+        <v>2053.055257098837</v>
       </c>
       <c r="R33">
         <v>0.4492753623188406</v>
       </c>
       <c r="S33">
-        <v>0.09735494392736815</v>
+        <v>0.09733382931351638</v>
       </c>
       <c r="T33">
         <v>0.9438601818103711</v>
       </c>
       <c r="U33">
-        <v>0.06338110587651873</v>
+        <v>0.06188110587651872</v>
       </c>
       <c r="V33">
         <v>0.27</v>
       </c>
       <c r="W33">
-        <v>0.04626820728985867</v>
+        <v>0.04517320728985866</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4037,7 +4037,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>5.859762604089354</v>
+        <v>6.001803438389785</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4048,13 +4048,13 @@
         <v>0.32</v>
       </c>
       <c r="B34">
-        <v>0.08141791732119746</v>
+        <v>0.08105299116738504</v>
       </c>
       <c r="C34">
-        <v>11462.12875392613</v>
+        <v>11613.62466022045</v>
       </c>
       <c r="D34">
-        <v>15218.98875392613</v>
+        <v>15370.48466022045</v>
       </c>
       <c r="E34">
         <v>-4029.339999999999</v>
@@ -4081,37 +4081,37 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M34">
-        <v>357.276758581701</v>
+        <v>348.821318581701</v>
       </c>
       <c r="N34">
-        <v>1670.856574751632</v>
+        <v>1679.312014751632</v>
       </c>
       <c r="O34">
-        <v>451.1312751829407</v>
+        <v>453.4142439829407</v>
       </c>
       <c r="P34">
-        <v>1219.725299568692</v>
+        <v>1225.897770768692</v>
       </c>
       <c r="Q34">
-        <v>2038.925299568691</v>
+        <v>2045.097770768691</v>
       </c>
       <c r="R34">
         <v>0.4705882352941177</v>
       </c>
       <c r="S34">
-        <v>0.09795895733594515</v>
+        <v>0.09793759534504451</v>
       </c>
       <c r="T34">
         <v>0.9549183687116809</v>
       </c>
       <c r="U34">
-        <v>0.06338110587651873</v>
+        <v>0.06188110587651872</v>
       </c>
       <c r="V34">
         <v>0.27</v>
       </c>
       <c r="W34">
-        <v>0.04626820728985867</v>
+        <v>0.04517320728985866</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>5.676645022711561</v>
+        <v>5.814247080940104</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4130,13 +4130,13 @@
         <v>0.33</v>
       </c>
       <c r="B35">
-        <v>0.08167912907265473</v>
+        <v>0.08094194584858759</v>
       </c>
       <c r="C35">
-        <v>11175.17455643804</v>
+        <v>11486.03897896334</v>
       </c>
       <c r="D35">
-        <v>15108.18955643805</v>
+        <v>15419.05397896334</v>
       </c>
       <c r="E35">
         <v>-3853.184999999999</v>
@@ -4163,45 +4163,45 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M35">
-        <v>377.1613297873792</v>
+        <v>359.7219847873792</v>
       </c>
       <c r="N35">
-        <v>1650.972003545954</v>
+        <v>1668.411348545954</v>
       </c>
       <c r="O35">
-        <v>445.7624409574076</v>
+        <v>450.4710641074076</v>
       </c>
       <c r="P35">
-        <v>1205.209562588546</v>
+        <v>1217.940284438546</v>
       </c>
       <c r="Q35">
-        <v>2024.409562588546</v>
+        <v>2037.140284438546</v>
       </c>
       <c r="R35">
         <v>0.4925373134328359</v>
       </c>
       <c r="S35">
-        <v>0.09858100099552446</v>
+        <v>0.09855938424318542</v>
       </c>
       <c r="T35">
         <v>0.9663066507443732</v>
       </c>
       <c r="U35">
-        <v>0.06488110587651873</v>
+        <v>0.06188110587651872</v>
       </c>
       <c r="V35">
         <v>0.27</v>
       </c>
       <c r="W35">
-        <v>0.04736320728985867</v>
+        <v>0.04517320728985866</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y35">
-        <v>5.377362876720878</v>
+        <v>5.63805777545707</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4212,13 +4212,13 @@
         <v>0.34</v>
       </c>
       <c r="B36">
-        <v>0.08158994082411199</v>
+        <v>0.08102946052979013</v>
       </c>
       <c r="C36">
-        <v>11036.66904493015</v>
+        <v>11271.58099126154</v>
       </c>
       <c r="D36">
-        <v>15145.83904493015</v>
+        <v>15380.75099126154</v>
       </c>
       <c r="E36">
         <v>-3677.029999999999</v>
@@ -4245,37 +4245,37 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M36">
-        <v>388.5904609930573</v>
+        <v>375.4140669930574</v>
       </c>
       <c r="N36">
-        <v>1639.542872340276</v>
+        <v>1652.719266340276</v>
       </c>
       <c r="O36">
-        <v>442.6765755318745</v>
+        <v>446.2342019118745</v>
       </c>
       <c r="P36">
-        <v>1196.866296808401</v>
+        <v>1206.485064428401</v>
       </c>
       <c r="Q36">
-        <v>2016.066296808401</v>
+        <v>2025.685064428401</v>
       </c>
       <c r="R36">
         <v>0.5151515151515152</v>
       </c>
       <c r="S36">
-        <v>0.09922189446296978</v>
+        <v>0.09920001522914876</v>
       </c>
       <c r="T36">
         <v>0.9780400322326014</v>
       </c>
       <c r="U36">
-        <v>0.06488110587651873</v>
+        <v>0.06268110587651873</v>
       </c>
       <c r="V36">
         <v>0.27</v>
       </c>
       <c r="W36">
-        <v>0.04736320728985867</v>
+        <v>0.04575720728985867</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4283,7 +4283,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>5.219205145052618</v>
+        <v>5.402390351480463</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4294,13 +4294,13 @@
         <v>0.35</v>
       </c>
       <c r="B37">
-        <v>0.08150075257556925</v>
+        <v>0.08092425521099268</v>
       </c>
       <c r="C37">
-        <v>10898.35164665208</v>
+        <v>11141.49492003055</v>
       </c>
       <c r="D37">
-        <v>15183.67664665208</v>
+        <v>15426.81992003055</v>
       </c>
       <c r="E37">
         <v>-3500.874999999999</v>
@@ -4327,37 +4327,37 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M37">
-        <v>400.0195921987355</v>
+        <v>386.4556571987355</v>
       </c>
       <c r="N37">
-        <v>1628.113741134598</v>
+        <v>1641.677676134598</v>
       </c>
       <c r="O37">
-        <v>439.5907101063414</v>
+        <v>443.2529725563414</v>
       </c>
       <c r="P37">
-        <v>1188.523031028256</v>
+        <v>1198.424703578256</v>
       </c>
       <c r="Q37">
-        <v>2007.723031028256</v>
+        <v>2017.624703578256</v>
       </c>
       <c r="R37">
         <v>0.5384615384615385</v>
       </c>
       <c r="S37">
-        <v>0.09988250772941343</v>
+        <v>0.09986035793775715</v>
       </c>
       <c r="T37">
         <v>0.9901344408435444</v>
       </c>
       <c r="U37">
-        <v>0.06488110587651873</v>
+        <v>0.06268110587651873</v>
       </c>
       <c r="V37">
         <v>0.27</v>
       </c>
       <c r="W37">
-        <v>0.04736320728985867</v>
+        <v>0.04575720728985867</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4365,7 +4365,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>5.070084998051113</v>
+        <v>5.248036341438164</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4376,13 +4376,13 @@
         <v>0.36</v>
       </c>
       <c r="B38">
-        <v>0.08141156432702652</v>
+        <v>0.08081904989219522</v>
       </c>
       <c r="C38">
-        <v>10760.22377497809</v>
+        <v>11011.68565221672</v>
       </c>
       <c r="D38">
-        <v>15221.70377497809</v>
+        <v>15473.16565221672</v>
       </c>
       <c r="E38">
         <v>-3324.719999999999</v>
@@ -4409,37 +4409,37 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M38">
-        <v>411.4487234044136</v>
+        <v>397.4972474044137</v>
       </c>
       <c r="N38">
-        <v>1616.68460992892</v>
+        <v>1630.63608592892</v>
       </c>
       <c r="O38">
-        <v>436.5048446808083</v>
+        <v>440.2717432008083</v>
       </c>
       <c r="P38">
-        <v>1180.179765248111</v>
+        <v>1190.364342728111</v>
       </c>
       <c r="Q38">
-        <v>1999.379765248111</v>
+        <v>2009.564342728111</v>
       </c>
       <c r="R38">
         <v>0.5625</v>
       </c>
       <c r="S38">
-        <v>0.1005637651604334</v>
+        <v>0.1005413363560095</v>
       </c>
       <c r="T38">
         <v>1.002606799723579</v>
       </c>
       <c r="U38">
-        <v>0.06488110587651873</v>
+        <v>0.06268110587651873</v>
       </c>
       <c r="V38">
         <v>0.27</v>
       </c>
       <c r="W38">
-        <v>0.04736320728985867</v>
+        <v>0.04575720728985867</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4447,7 +4447,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>4.929249303660805</v>
+        <v>5.102257554175993</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4458,13 +4458,13 @@
         <v>0.37</v>
       </c>
       <c r="B39">
-        <v>0.08132237607848379</v>
+        <v>0.08071384457339775</v>
       </c>
       <c r="C39">
-        <v>10622.28685747705</v>
+        <v>10882.15569008172</v>
       </c>
       <c r="D39">
-        <v>15259.92185747705</v>
+        <v>15519.79069008172</v>
       </c>
       <c r="E39">
         <v>-3148.565</v>
@@ -4491,37 +4491,37 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M39">
-        <v>422.8778546100918</v>
+        <v>408.5388376100918</v>
       </c>
       <c r="N39">
-        <v>1605.255478723241</v>
+        <v>1619.594495723241</v>
       </c>
       <c r="O39">
-        <v>433.4189792552752</v>
+        <v>437.2905138452752</v>
       </c>
       <c r="P39">
-        <v>1171.836499467966</v>
+        <v>1182.303981877966</v>
       </c>
       <c r="Q39">
-        <v>1991.036499467966</v>
+        <v>2001.503981877966</v>
       </c>
       <c r="R39">
         <v>0.5873015873015873</v>
       </c>
       <c r="S39">
-        <v>0.1012666498114858</v>
+        <v>0.1012439331367461</v>
       </c>
       <c r="T39">
         <v>1.015475106504568</v>
       </c>
       <c r="U39">
-        <v>0.06488110587651873</v>
+        <v>0.06268110587651873</v>
       </c>
       <c r="V39">
         <v>0.27</v>
       </c>
       <c r="W39">
-        <v>0.04736320728985867</v>
+        <v>0.04575720728985867</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4529,7 +4529,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>4.796026349507811</v>
+        <v>4.964358701360426</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4540,13 +4540,13 @@
         <v>0.38</v>
       </c>
       <c r="B40">
-        <v>0.08123318782994104</v>
+        <v>0.08060863925460031</v>
       </c>
       <c r="C40">
-        <v>10484.54233609105</v>
+        <v>10752.90756613847</v>
       </c>
       <c r="D40">
-        <v>15298.33233609105</v>
+        <v>15566.69756613847</v>
       </c>
       <c r="E40">
         <v>-2972.409999999999</v>
@@ -4573,37 +4573,37 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M40">
-        <v>434.30698581577</v>
+        <v>419.58042781577</v>
       </c>
       <c r="N40">
-        <v>1593.826347517563</v>
+        <v>1608.552905517563</v>
       </c>
       <c r="O40">
-        <v>430.333113829742</v>
+        <v>434.3092844897421</v>
       </c>
       <c r="P40">
-        <v>1163.493233687821</v>
+        <v>1174.243621027821</v>
       </c>
       <c r="Q40">
-        <v>1982.693233687821</v>
+        <v>1993.443621027821</v>
       </c>
       <c r="R40">
         <v>0.6129032258064516</v>
       </c>
       <c r="S40">
-        <v>0.1019922081609593</v>
+        <v>0.1019691943297645</v>
       </c>
       <c r="T40">
         <v>1.028758519955911</v>
       </c>
       <c r="U40">
-        <v>0.06488110587651873</v>
+        <v>0.06268110587651873</v>
       </c>
       <c r="V40">
         <v>0.27</v>
       </c>
       <c r="W40">
-        <v>0.04736320728985867</v>
+        <v>0.04575720728985867</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>4.66981512978392</v>
+        <v>4.833717682903572</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4622,13 +4622,13 @@
         <v>0.39</v>
       </c>
       <c r="B41">
-        <v>0.08114399958139831</v>
+        <v>0.08050343393580288</v>
       </c>
       <c r="C41">
-        <v>10346.99166731673</v>
+        <v>10623.9438436097</v>
       </c>
       <c r="D41">
-        <v>15336.93666731673</v>
+        <v>15613.8888436097</v>
       </c>
       <c r="E41">
         <v>-2796.254999999999</v>
@@ -4655,37 +4655,37 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M41">
-        <v>445.7361170214481</v>
+        <v>430.6220180214481</v>
       </c>
       <c r="N41">
-        <v>1582.397216311885</v>
+        <v>1597.511315311885</v>
       </c>
       <c r="O41">
-        <v>427.247248404209</v>
+        <v>431.328055134209</v>
       </c>
       <c r="P41">
-        <v>1155.149967907676</v>
+        <v>1166.183260177676</v>
       </c>
       <c r="Q41">
-        <v>1974.349967907676</v>
+        <v>1985.383260177676</v>
       </c>
       <c r="R41">
         <v>0.639344262295082</v>
       </c>
       <c r="S41">
-        <v>0.1027415553087761</v>
+        <v>0.1027182345782918</v>
       </c>
       <c r="T41">
         <v>1.042477455159757</v>
       </c>
       <c r="U41">
-        <v>0.06488110587651873</v>
+        <v>0.06268110587651873</v>
       </c>
       <c r="V41">
         <v>0.27</v>
       </c>
       <c r="W41">
-        <v>0.04736320728985867</v>
+        <v>0.04575720728985867</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4693,7 +4693,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>4.550076280302282</v>
+        <v>4.709776203854762</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4704,13 +4704,13 @@
         <v>0.4</v>
       </c>
       <c r="B42">
-        <v>0.08105481133285558</v>
+        <v>0.08039822861700542</v>
       </c>
       <c r="C42">
-        <v>10209.63632238945</v>
+        <v>10495.26711689484</v>
       </c>
       <c r="D42">
-        <v>15375.73632238945</v>
+        <v>15661.36711689484</v>
       </c>
       <c r="E42">
         <v>-2620.099999999999</v>
@@ -4737,37 +4737,37 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M42">
-        <v>457.1652482271263</v>
+        <v>441.6636082271264</v>
       </c>
       <c r="N42">
-        <v>1570.968085106207</v>
+        <v>1586.469725106207</v>
       </c>
       <c r="O42">
-        <v>424.1613829786759</v>
+        <v>428.3468257786758</v>
       </c>
       <c r="P42">
-        <v>1146.806702127531</v>
+        <v>1158.122899327531</v>
       </c>
       <c r="Q42">
-        <v>1966.006702127531</v>
+        <v>1977.322899327531</v>
       </c>
       <c r="R42">
         <v>0.6666666666666667</v>
       </c>
       <c r="S42">
-        <v>0.1035158806948535</v>
+        <v>0.1034922428351032</v>
       </c>
       <c r="T42">
         <v>1.056653688203731</v>
       </c>
       <c r="U42">
-        <v>0.06488110587651873</v>
+        <v>0.06268110587651873</v>
       </c>
       <c r="V42">
         <v>0.27</v>
       </c>
       <c r="W42">
-        <v>0.04736320728985867</v>
+        <v>0.04575720728985867</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4775,7 +4775,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>4.436324373294724</v>
+        <v>4.592031798758393</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4786,13 +4786,13 @@
         <v>0.41</v>
       </c>
       <c r="B43">
-        <v>0.08096562308431282</v>
+        <v>0.08029302329820796</v>
       </c>
       <c r="C43">
-        <v>10072.47778747017</v>
+        <v>10366.88001204547</v>
       </c>
       <c r="D43">
-        <v>15414.73278747017</v>
+        <v>15709.13501204547</v>
       </c>
       <c r="E43">
         <v>-2443.944999999999</v>
@@ -4819,37 +4819,37 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M43">
-        <v>468.5943794328044</v>
+        <v>452.7051984328045</v>
       </c>
       <c r="N43">
-        <v>1559.538953900529</v>
+        <v>1575.428134900529</v>
       </c>
       <c r="O43">
-        <v>421.0755175531428</v>
+        <v>425.3655964231428</v>
       </c>
       <c r="P43">
-        <v>1138.463436347386</v>
+        <v>1150.062538477386</v>
       </c>
       <c r="Q43">
-        <v>1957.663436347386</v>
+        <v>1969.262538477386</v>
       </c>
       <c r="R43">
         <v>0.6949152542372882</v>
       </c>
       <c r="S43">
-        <v>0.104316454399103</v>
+        <v>0.1042924886599422</v>
       </c>
       <c r="T43">
         <v>1.071310471520382</v>
       </c>
       <c r="U43">
-        <v>0.06488110587651873</v>
+        <v>0.06268110587651873</v>
       </c>
       <c r="V43">
         <v>0.27</v>
       </c>
       <c r="W43">
-        <v>0.04736320728985867</v>
+        <v>0.04575720728985867</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4857,7 +4857,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>4.328121339799731</v>
+        <v>4.48003102317892</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4868,13 +4868,13 @@
         <v>0.42</v>
       </c>
       <c r="B44">
-        <v>0.0813056748357701</v>
+        <v>0.08018781797941051</v>
       </c>
       <c r="C44">
-        <v>9748.689855358029</v>
+        <v>10238.78518724949</v>
       </c>
       <c r="D44">
-        <v>15267.09985535803</v>
+        <v>15757.19518724949</v>
       </c>
       <c r="E44">
         <v>-2267.79</v>
@@ -4901,45 +4901,45 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M44">
-        <v>490.3814246384825</v>
+        <v>463.7467886384826</v>
       </c>
       <c r="N44">
-        <v>1537.751908694851</v>
+        <v>1564.386544694851</v>
       </c>
       <c r="O44">
-        <v>415.1930153476097</v>
+        <v>422.3843670676097</v>
       </c>
       <c r="P44">
-        <v>1122.558893347241</v>
+        <v>1142.002177627241</v>
       </c>
       <c r="Q44">
-        <v>1941.758893347241</v>
+        <v>1961.202177627241</v>
       </c>
       <c r="R44">
         <v>0.7241379310344827</v>
       </c>
       <c r="S44">
-        <v>0.1051446340931542</v>
+        <v>0.1051203291683963</v>
       </c>
       <c r="T44">
         <v>1.086472661158297</v>
       </c>
       <c r="U44">
-        <v>0.06628110587651873</v>
+        <v>0.06268110587651873</v>
       </c>
       <c r="V44">
         <v>0.27</v>
       </c>
       <c r="W44">
-        <v>0.04838520728985867</v>
+        <v>0.04575720728985867</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y44">
-        <v>4.13582821745034</v>
+        <v>4.373363617865137</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4950,13 +4950,13 @@
         <v>0.43</v>
       </c>
       <c r="B45">
-        <v>0.08122670658722736</v>
+        <v>0.08008261266061306</v>
       </c>
       <c r="C45">
-        <v>9606.566134357567</v>
+        <v>10110.98533332424</v>
       </c>
       <c r="D45">
-        <v>15301.13113435757</v>
+        <v>15805.55033332425</v>
       </c>
       <c r="E45">
         <v>-2091.634999999999</v>
@@ -4983,45 +4983,45 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M45">
-        <v>502.0571728441607</v>
+        <v>474.7883788441608</v>
       </c>
       <c r="N45">
-        <v>1526.076160489172</v>
+        <v>1553.344954489172</v>
       </c>
       <c r="O45">
-        <v>412.0405633320766</v>
+        <v>419.4031377120766</v>
       </c>
       <c r="P45">
-        <v>1114.035597157096</v>
+        <v>1133.941816777096</v>
       </c>
       <c r="Q45">
-        <v>1933.235597157096</v>
+        <v>1953.141816777096</v>
       </c>
       <c r="R45">
         <v>0.7543859649122806</v>
       </c>
       <c r="S45">
-        <v>0.1060018727238388</v>
+        <v>0.1059772167122348</v>
       </c>
       <c r="T45">
         <v>1.102166857450174</v>
       </c>
       <c r="U45">
-        <v>0.06628110587651873</v>
+        <v>0.06268110587651873</v>
       </c>
       <c r="V45">
         <v>0.27</v>
       </c>
       <c r="W45">
-        <v>0.04838520728985867</v>
+        <v>0.04575720728985867</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y45">
-        <v>4.039646165881726</v>
+        <v>4.27165748721711</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5032,13 +5032,13 @@
         <v>0.44</v>
       </c>
       <c r="B46">
-        <v>0.08114773833868461</v>
+        <v>0.0802986073418156</v>
       </c>
       <c r="C46">
-        <v>9464.594467809507</v>
+        <v>9835.872286361606</v>
       </c>
       <c r="D46">
-        <v>15335.31446780951</v>
+        <v>15706.59228636161</v>
       </c>
       <c r="E46">
         <v>-1915.48</v>
@@ -5065,37 +5065,37 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M46">
-        <v>513.7329210498389</v>
+        <v>493.5807890498389</v>
       </c>
       <c r="N46">
-        <v>1514.400412283494</v>
+        <v>1534.552544283494</v>
       </c>
       <c r="O46">
-        <v>408.8881113165435</v>
+        <v>414.3291869565435</v>
       </c>
       <c r="P46">
-        <v>1105.512300966951</v>
+        <v>1120.223357326951</v>
       </c>
       <c r="Q46">
-        <v>1924.712300966951</v>
+        <v>1939.423357326951</v>
       </c>
       <c r="R46">
         <v>0.7857142857142857</v>
       </c>
       <c r="S46">
-        <v>0.106889727019905</v>
+        <v>0.1068647073826389</v>
       </c>
       <c r="T46">
         <v>1.118421560752475</v>
       </c>
       <c r="U46">
-        <v>0.06628110587651873</v>
+        <v>0.06368110587651873</v>
       </c>
       <c r="V46">
         <v>0.27</v>
       </c>
       <c r="W46">
-        <v>0.04838520728985867</v>
+        <v>0.04648720728985867</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5103,7 +5103,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>3.947836025748051</v>
+        <v>4.109019999010829</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5114,13 +5114,13 @@
         <v>0.45</v>
       </c>
       <c r="B47">
-        <v>0.08106877009014188</v>
+        <v>0.08020070202301816</v>
       </c>
       <c r="C47">
-        <v>9322.775877082631</v>
+        <v>9704.418668443535</v>
       </c>
       <c r="D47">
-        <v>15369.65087708263</v>
+        <v>15751.29366844354</v>
       </c>
       <c r="E47">
         <v>-1739.324999999999</v>
@@ -5147,37 +5147,37 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M47">
-        <v>525.408669255517</v>
+        <v>504.7985342555171</v>
       </c>
       <c r="N47">
-        <v>1502.724664077816</v>
+        <v>1523.334799077816</v>
       </c>
       <c r="O47">
-        <v>405.7356593010104</v>
+        <v>411.3003957510104</v>
       </c>
       <c r="P47">
-        <v>1096.989004776806</v>
+        <v>1112.034403326806</v>
       </c>
       <c r="Q47">
-        <v>1916.189004776806</v>
+        <v>1931.234403326805</v>
       </c>
       <c r="R47">
         <v>0.8181818181818181</v>
       </c>
       <c r="S47">
-        <v>0.1078098669267372</v>
+        <v>0.1077844704410577</v>
       </c>
       <c r="T47">
         <v>1.13526734417486</v>
       </c>
       <c r="U47">
-        <v>0.06628110587651873</v>
+        <v>0.06368110587651873</v>
       </c>
       <c r="V47">
         <v>0.27</v>
       </c>
       <c r="W47">
-        <v>0.04838520728985867</v>
+        <v>0.04648720728985867</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5185,7 +5185,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>3.860106336286984</v>
+        <v>4.017708443477255</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5196,13 +5196,13 @@
         <v>0.46</v>
       </c>
       <c r="B48">
-        <v>0.08098980184159914</v>
+        <v>0.08010279670422071</v>
       </c>
       <c r="C48">
-        <v>9181.111392713836</v>
+        <v>9573.220219402872</v>
       </c>
       <c r="D48">
-        <v>15404.14139271384</v>
+        <v>15796.25021940287</v>
       </c>
       <c r="E48">
         <v>-1563.169999999999</v>
@@ -5229,37 +5229,37 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M48">
-        <v>537.0844174611952</v>
+        <v>516.0162794611953</v>
       </c>
       <c r="N48">
-        <v>1491.048915872138</v>
+        <v>1512.117053872138</v>
       </c>
       <c r="O48">
-        <v>402.5832072854773</v>
+        <v>408.2716045454773</v>
       </c>
       <c r="P48">
-        <v>1088.465708586661</v>
+        <v>1103.845449326661</v>
       </c>
       <c r="Q48">
-        <v>1907.66570858666</v>
+        <v>1923.045449326661</v>
       </c>
       <c r="R48">
         <v>0.8518518518518519</v>
       </c>
       <c r="S48">
-        <v>0.108764086089378</v>
+        <v>0.1087382987979365</v>
       </c>
       <c r="T48">
         <v>1.152737045501778</v>
       </c>
       <c r="U48">
-        <v>0.06628110587651873</v>
+        <v>0.06368110587651873</v>
       </c>
       <c r="V48">
         <v>0.27</v>
       </c>
       <c r="W48">
-        <v>0.04838520728985867</v>
+        <v>0.04648720728985867</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5267,7 +5267,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>3.776190981150309</v>
+        <v>3.930366955575575</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5278,13 +5278,13 @@
         <v>0.47</v>
       </c>
       <c r="B49">
-        <v>0.0809108335930564</v>
+        <v>0.08000489138542326</v>
       </c>
       <c r="C49">
-        <v>9039.602054511164</v>
+        <v>9442.27913036399</v>
       </c>
       <c r="D49">
-        <v>15438.78705451117</v>
+        <v>15841.46413036399</v>
       </c>
       <c r="E49">
         <v>-1387.014999999999</v>
@@ -5311,37 +5311,37 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M49">
-        <v>548.7601656668734</v>
+        <v>527.2340246668734</v>
       </c>
       <c r="N49">
-        <v>1479.37316766646</v>
+        <v>1500.89930866646</v>
       </c>
       <c r="O49">
-        <v>399.4307552699441</v>
+        <v>405.2428133399442</v>
       </c>
       <c r="P49">
-        <v>1079.942412396515</v>
+        <v>1095.656495326516</v>
       </c>
       <c r="Q49">
-        <v>1899.142412396515</v>
+        <v>1914.856495326515</v>
       </c>
       <c r="R49">
         <v>0.8867924528301887</v>
       </c>
       <c r="S49">
-        <v>0.1097543135223072</v>
+        <v>0.1097281206777164</v>
       </c>
       <c r="T49">
         <v>1.170865980841032</v>
       </c>
       <c r="U49">
-        <v>0.06628110587651873</v>
+        <v>0.06368110587651873</v>
       </c>
       <c r="V49">
         <v>0.27</v>
       </c>
       <c r="W49">
-        <v>0.04838520728985867</v>
+        <v>0.04648720728985867</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5349,7 +5349,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>3.695846492189665</v>
+        <v>3.846742126733541</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5360,13 +5360,13 @@
         <v>0.48</v>
       </c>
       <c r="B50">
-        <v>0.08083186534451366</v>
+        <v>0.07990698606662579</v>
       </c>
       <c r="C50">
-        <v>8898.248911658347</v>
+        <v>9311.597617610039</v>
       </c>
       <c r="D50">
-        <v>15473.58891165835</v>
+        <v>15886.93761761004</v>
       </c>
       <c r="E50">
         <v>-1210.859999999999</v>
@@ -5393,37 +5393,37 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M50">
-        <v>560.4359138725515</v>
+        <v>538.4517698725516</v>
       </c>
       <c r="N50">
-        <v>1467.697419460782</v>
+        <v>1489.681563460781</v>
       </c>
       <c r="O50">
-        <v>396.2783032544111</v>
+        <v>402.214022134411</v>
       </c>
       <c r="P50">
-        <v>1071.419116206371</v>
+        <v>1087.46754132637</v>
       </c>
       <c r="Q50">
-        <v>1890.619116206371</v>
+        <v>1906.66754132637</v>
       </c>
       <c r="R50">
         <v>0.923076923076923</v>
       </c>
       <c r="S50">
-        <v>0.1107826266257336</v>
+        <v>0.1107560126297954</v>
       </c>
       <c r="T50">
         <v>1.189692182924104</v>
       </c>
       <c r="U50">
-        <v>0.06628110587651873</v>
+        <v>0.06368110587651873</v>
       </c>
       <c r="V50">
         <v>0.27</v>
       </c>
       <c r="W50">
-        <v>0.04838520728985867</v>
+        <v>0.04648720728985867</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5431,7 +5431,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>3.618849690269047</v>
+        <v>3.766601665759926</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5442,13 +5442,13 @@
         <v>0.49</v>
       </c>
       <c r="B51">
-        <v>0.08075289709597092</v>
+        <v>0.07980908074782835</v>
       </c>
       <c r="C51">
-        <v>8757.053022820694</v>
+        <v>9181.177922945115</v>
       </c>
       <c r="D51">
-        <v>15508.54802282069</v>
+        <v>15932.67292294512</v>
       </c>
       <c r="E51">
         <v>-1034.705</v>
@@ -5475,37 +5475,37 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M51">
-        <v>572.1116620782296</v>
+        <v>549.6695150782297</v>
       </c>
       <c r="N51">
-        <v>1456.021671255104</v>
+        <v>1478.463818255103</v>
       </c>
       <c r="O51">
-        <v>393.125851238878</v>
+        <v>399.185230928878</v>
       </c>
       <c r="P51">
-        <v>1062.895820016226</v>
+        <v>1079.278587326226</v>
       </c>
       <c r="Q51">
-        <v>1882.095820016225</v>
+        <v>1898.478587326225</v>
       </c>
       <c r="R51">
         <v>0.9607843137254901</v>
       </c>
       <c r="S51">
-        <v>0.111851265733216</v>
+        <v>0.1118242140701914</v>
       </c>
       <c r="T51">
         <v>1.209256667441806</v>
       </c>
       <c r="U51">
-        <v>0.06628110587651873</v>
+        <v>0.06368110587651873</v>
       </c>
       <c r="V51">
         <v>0.27</v>
       </c>
       <c r="W51">
-        <v>0.04838520728985867</v>
+        <v>0.04648720728985867</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5513,7 +5513,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>3.544995614957434</v>
+        <v>3.689732244009724</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5524,13 +5524,13 @@
         <v>0.5</v>
       </c>
       <c r="B52">
-        <v>0.08067392884742819</v>
+        <v>0.07971117542903089</v>
       </c>
       <c r="C52">
-        <v>8616.015456252437</v>
+        <v>9051.022314062684</v>
       </c>
       <c r="D52">
-        <v>15543.66545625244</v>
+        <v>15978.67231406269</v>
       </c>
       <c r="E52">
         <v>-858.5499999999993</v>
@@ -5557,37 +5557,37 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M52">
-        <v>583.7874102839078</v>
+        <v>560.8872602839078</v>
       </c>
       <c r="N52">
-        <v>1444.345923049425</v>
+        <v>1467.246073049425</v>
       </c>
       <c r="O52">
-        <v>389.9733992233449</v>
+        <v>396.1564397233449</v>
       </c>
       <c r="P52">
-        <v>1054.372523826081</v>
+        <v>1071.089633326081</v>
       </c>
       <c r="Q52">
-        <v>1873.57252382608</v>
+        <v>1890.28963332608</v>
       </c>
       <c r="R52">
         <v>1</v>
       </c>
       <c r="S52">
-        <v>0.1129626504049977</v>
+        <v>0.1129351435682031</v>
       </c>
       <c r="T52">
         <v>1.229603731340216</v>
       </c>
       <c r="U52">
-        <v>0.06628110587651873</v>
+        <v>0.06368110587651873</v>
       </c>
       <c r="V52">
         <v>0.27</v>
       </c>
       <c r="W52">
-        <v>0.04838520728985867</v>
+        <v>0.04648720728985867</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>3.474095702658285</v>
+        <v>3.61593759912953</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5606,13 +5606,13 @@
         <v>0.51</v>
       </c>
       <c r="B53">
-        <v>0.08059496059888543</v>
+        <v>0.07961327011023343</v>
       </c>
       <c r="C53">
-        <v>8475.137289905584</v>
+        <v>8921.13308492035</v>
       </c>
       <c r="D53">
-        <v>15578.94228990559</v>
+        <v>16024.93808492035</v>
       </c>
       <c r="E53">
         <v>-682.3949999999986</v>
@@ -5639,37 +5639,37 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M53">
-        <v>595.463158489586</v>
+        <v>572.1050054895861</v>
       </c>
       <c r="N53">
-        <v>1432.670174843747</v>
+        <v>1456.028327843747</v>
       </c>
       <c r="O53">
-        <v>386.8209472078117</v>
+        <v>393.1276485178117</v>
       </c>
       <c r="P53">
-        <v>1045.849227635935</v>
+        <v>1062.900679325935</v>
       </c>
       <c r="Q53">
-        <v>1865.049227635935</v>
+        <v>1882.100679325935</v>
       </c>
       <c r="R53">
         <v>1.040816326530612</v>
       </c>
       <c r="S53">
-        <v>0.1141193977164439</v>
+        <v>0.1140914171273582</v>
       </c>
       <c r="T53">
         <v>1.250781287642643</v>
       </c>
       <c r="U53">
-        <v>0.06628110587651873</v>
+        <v>0.06368110587651873</v>
       </c>
       <c r="V53">
         <v>0.27</v>
       </c>
       <c r="W53">
-        <v>0.04838520728985867</v>
+        <v>0.04648720728985867</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5677,7 +5677,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>3.40597617907675</v>
+        <v>3.545036861891695</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5688,13 +5688,13 @@
         <v>0.52</v>
       </c>
       <c r="B54">
-        <v>0.08051599235034269</v>
+        <v>0.07951536479143598</v>
       </c>
       <c r="C54">
-        <v>8334.419611540152</v>
+        <v>8791.512556121213</v>
       </c>
       <c r="D54">
-        <v>15614.37961154015</v>
+        <v>16071.47255612121</v>
       </c>
       <c r="E54">
         <v>-506.2399999999998</v>
@@ -5721,37 +5721,37 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M54">
-        <v>607.138906695264</v>
+        <v>583.3227506952642</v>
       </c>
       <c r="N54">
-        <v>1420.994426638069</v>
+        <v>1444.810582638069</v>
       </c>
       <c r="O54">
-        <v>383.6684951922787</v>
+        <v>390.0988573122787</v>
       </c>
       <c r="P54">
-        <v>1037.325931445791</v>
+        <v>1054.71172532579</v>
       </c>
       <c r="Q54">
-        <v>1856.52593144579</v>
+        <v>1873.91172532579</v>
       </c>
       <c r="R54">
         <v>1.083333333333333</v>
       </c>
       <c r="S54">
-        <v>0.1153243428325337</v>
+        <v>0.1152958687514781</v>
       </c>
       <c r="T54">
         <v>1.272841242124338</v>
       </c>
       <c r="U54">
-        <v>0.06628110587651873</v>
+        <v>0.06368110587651873</v>
       </c>
       <c r="V54">
         <v>0.27</v>
       </c>
       <c r="W54">
-        <v>0.04838520728985867</v>
+        <v>0.04648720728985867</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5759,7 +5759,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>3.340476637171428</v>
+        <v>3.476863076086086</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5770,13 +5770,13 @@
         <v>0.53</v>
       </c>
       <c r="B55">
-        <v>0.08043702410179995</v>
+        <v>0.07941745947263854</v>
       </c>
       <c r="C55">
-        <v>8193.86351883602</v>
+        <v>8662.163075301865</v>
       </c>
       <c r="D55">
-        <v>15649.97851883602</v>
+        <v>16118.27807530187</v>
       </c>
       <c r="E55">
         <v>-330.0849999999991</v>
@@ -5803,37 +5803,37 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M55">
-        <v>618.8146549009423</v>
+        <v>594.5404959009423</v>
       </c>
       <c r="N55">
-        <v>1409.318678432391</v>
+        <v>1433.592837432391</v>
       </c>
       <c r="O55">
-        <v>380.5160431767456</v>
+        <v>387.0700661067455</v>
       </c>
       <c r="P55">
-        <v>1028.802635255645</v>
+        <v>1046.522771325645</v>
       </c>
       <c r="Q55">
-        <v>1848.002635255645</v>
+        <v>1865.722771325645</v>
       </c>
       <c r="R55">
         <v>1.127659574468085</v>
       </c>
       <c r="S55">
-        <v>0.1165805622088827</v>
+        <v>0.1165515736361988</v>
       </c>
       <c r="T55">
         <v>1.295839918073338</v>
       </c>
       <c r="U55">
-        <v>0.06628110587651873</v>
+        <v>0.06368110587651873</v>
       </c>
       <c r="V55">
         <v>0.27</v>
       </c>
       <c r="W55">
-        <v>0.04838520728985867</v>
+        <v>0.04648720728985867</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5841,7 +5841,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>3.277448776092722</v>
+        <v>3.411261885971254</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5852,13 +5852,13 @@
         <v>0.54</v>
       </c>
       <c r="B56">
-        <v>0.08035805585325721</v>
+        <v>0.07931955415384107</v>
       </c>
       <c r="C56">
-        <v>8053.470119506261</v>
+        <v>8533.08701752723</v>
       </c>
       <c r="D56">
-        <v>15685.74011950626</v>
+        <v>16165.35701752723</v>
       </c>
       <c r="E56">
         <v>-153.9299999999985</v>
@@ -5885,37 +5885,37 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M56">
-        <v>630.4904031066205</v>
+        <v>605.7582411066205</v>
       </c>
       <c r="N56">
-        <v>1397.642930226713</v>
+        <v>1422.375092226713</v>
       </c>
       <c r="O56">
-        <v>377.3635911612125</v>
+        <v>384.0412749012124</v>
       </c>
       <c r="P56">
-        <v>1020.2793390655</v>
+        <v>1038.3338173255</v>
       </c>
       <c r="Q56">
-        <v>1839.4793390655</v>
+        <v>1857.5338173255</v>
       </c>
       <c r="R56">
         <v>1.173913043478261</v>
       </c>
       <c r="S56">
-        <v>0.1178913998189859</v>
+        <v>0.1178618743854726</v>
       </c>
       <c r="T56">
         <v>1.319838536454904</v>
       </c>
       <c r="U56">
-        <v>0.06628110587651873</v>
+        <v>0.06368110587651873</v>
       </c>
       <c r="V56">
         <v>0.27</v>
       </c>
       <c r="W56">
-        <v>0.04838520728985867</v>
+        <v>0.04648720728985867</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5923,7 +5923,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>3.216755280239152</v>
+        <v>3.348090369564379</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5934,13 +5934,13 @@
         <v>0.55</v>
       </c>
       <c r="B57">
-        <v>0.08027908760471449</v>
+        <v>0.07922164883504362</v>
       </c>
       <c r="C57">
-        <v>7913.240531412008</v>
+        <v>8404.286785692228</v>
       </c>
       <c r="D57">
-        <v>15721.66553141201</v>
+        <v>16212.71178569223</v>
       </c>
       <c r="E57">
         <v>22.22500000000218</v>
@@ -5967,37 +5967,37 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M57">
-        <v>642.1661513122987</v>
+        <v>616.9759863122988</v>
       </c>
       <c r="N57">
-        <v>1385.967182021035</v>
+        <v>1411.157347021034</v>
       </c>
       <c r="O57">
-        <v>374.2111391456794</v>
+        <v>381.0124836956793</v>
       </c>
       <c r="P57">
-        <v>1011.756042875355</v>
+        <v>1030.144863325355</v>
       </c>
       <c r="Q57">
-        <v>1830.956042875355</v>
+        <v>1849.344863325355</v>
       </c>
       <c r="R57">
         <v>1.222222222222223</v>
       </c>
       <c r="S57">
-        <v>0.1192604968784272</v>
+        <v>0.119230410723603</v>
       </c>
       <c r="T57">
         <v>1.344903760097873</v>
       </c>
       <c r="U57">
-        <v>0.06628110587651873</v>
+        <v>0.06368110587651873</v>
       </c>
       <c r="V57">
         <v>0.27</v>
       </c>
       <c r="W57">
-        <v>0.04838520728985867</v>
+        <v>0.04648720728985867</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6005,7 +6005,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>3.158268820598441</v>
+        <v>3.287215999208662</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6016,13 +6016,13 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="B58">
-        <v>0.08020011935617175</v>
+        <v>0.07912374351624617</v>
       </c>
       <c r="C58">
-        <v>7773.175882678992</v>
+        <v>8275.76481093069</v>
       </c>
       <c r="D58">
-        <v>15757.75588267899</v>
+        <v>16260.34481093069</v>
       </c>
       <c r="E58">
         <v>198.380000000001</v>
@@ -6049,37 +6049,37 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M58">
-        <v>653.8418995179768</v>
+        <v>628.1937315179769</v>
       </c>
       <c r="N58">
-        <v>1374.291433815356</v>
+        <v>1399.939601815356</v>
       </c>
       <c r="O58">
-        <v>371.0586871301463</v>
+        <v>377.9836924901463</v>
       </c>
       <c r="P58">
-        <v>1003.23274668521</v>
+        <v>1021.95590932521</v>
       </c>
       <c r="Q58">
-        <v>1822.43274668521</v>
+        <v>1841.15590932521</v>
       </c>
       <c r="R58">
         <v>1.272727272727273</v>
       </c>
       <c r="S58">
-        <v>0.1206918256223884</v>
+        <v>0.1206611532589212</v>
       </c>
       <c r="T58">
         <v>1.371108312088249</v>
       </c>
       <c r="U58">
-        <v>0.06628110587651873</v>
+        <v>0.06368110587651873</v>
       </c>
       <c r="V58">
         <v>0.27</v>
       </c>
       <c r="W58">
-        <v>0.04838520728985867</v>
+        <v>0.04648720728985867</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6087,7 +6087,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>3.101871163087754</v>
+        <v>3.228515713508508</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6098,13 +6098,13 @@
         <v>0.5700000000000001</v>
       </c>
       <c r="B59">
-        <v>0.08012115110762902</v>
+        <v>0.07902583819744873</v>
       </c>
       <c r="C59">
-        <v>7633.277311815558</v>
+        <v>8147.523553031342</v>
       </c>
       <c r="D59">
-        <v>15794.01231181556</v>
+        <v>16308.25855303134</v>
       </c>
       <c r="E59">
         <v>374.5350000000017</v>
@@ -6131,37 +6131,37 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M59">
-        <v>665.5176477236549</v>
+        <v>639.411476723655</v>
       </c>
       <c r="N59">
-        <v>1362.615685609678</v>
+        <v>1388.721856609678</v>
       </c>
       <c r="O59">
-        <v>367.9062351146131</v>
+        <v>374.9549012846131</v>
       </c>
       <c r="P59">
-        <v>994.7094504950651</v>
+        <v>1013.766955325065</v>
       </c>
       <c r="Q59">
-        <v>1813.909450495065</v>
+        <v>1832.966955325065</v>
       </c>
       <c r="R59">
         <v>1.325581395348838</v>
       </c>
       <c r="S59">
-        <v>0.1221897277963013</v>
+        <v>0.1221584419586728</v>
       </c>
       <c r="T59">
         <v>1.398531680450272</v>
       </c>
       <c r="U59">
-        <v>0.06628110587651873</v>
+        <v>0.06368110587651873</v>
       </c>
       <c r="V59">
         <v>0.27</v>
       </c>
       <c r="W59">
-        <v>0.04838520728985867</v>
+        <v>0.04648720728985867</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6169,7 +6169,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>3.047452370752881</v>
+        <v>3.171875086955727</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6180,13 +6180,13 @@
         <v>0.58</v>
       </c>
       <c r="B60">
-        <v>0.08114302285908626</v>
+        <v>0.07892793287865127</v>
       </c>
       <c r="C60">
-        <v>7000.470511318452</v>
+        <v>8019.565500861276</v>
       </c>
       <c r="D60">
-        <v>15337.36051131845</v>
+        <v>16356.45550086128</v>
       </c>
       <c r="E60">
         <v>550.6900000000005</v>
@@ -6213,45 +6213,45 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M60">
-        <v>703.7575699293329</v>
+        <v>650.6292219293331</v>
       </c>
       <c r="N60">
-        <v>1324.375763404</v>
+        <v>1377.504111404</v>
       </c>
       <c r="O60">
-        <v>357.5814561190801</v>
+        <v>371.92611007908</v>
       </c>
       <c r="P60">
-        <v>966.7943072849203</v>
+        <v>1005.57800132492</v>
       </c>
       <c r="Q60">
-        <v>1785.99430728492</v>
+        <v>1824.77800132492</v>
       </c>
       <c r="R60">
         <v>1.380952380952381</v>
       </c>
       <c r="S60">
-        <v>0.1237589586451625</v>
+        <v>0.1237270301203172</v>
       </c>
       <c r="T60">
         <v>1.427260923496199</v>
       </c>
       <c r="U60">
-        <v>0.06888110587651872</v>
+        <v>0.06368110587651873</v>
       </c>
       <c r="V60">
         <v>0.27</v>
       </c>
       <c r="W60">
-        <v>0.05028320728985866</v>
+        <v>0.04648720728985867</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y60">
-        <v>2.881863613256744</v>
+        <v>3.117187585456491</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6262,13 +6262,13 @@
         <v>0.59</v>
       </c>
       <c r="B61">
-        <v>0.08108303461054352</v>
+        <v>0.07883002755985381</v>
       </c>
       <c r="C61">
-        <v>6850.392106047284</v>
+        <v>7891.893172796879</v>
       </c>
       <c r="D61">
-        <v>15363.43710604728</v>
+        <v>16404.93817279688</v>
       </c>
       <c r="E61">
         <v>726.8449999999993</v>
@@ -6295,45 +6295,45 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M61">
-        <v>715.891321135011</v>
+        <v>661.8469671350113</v>
       </c>
       <c r="N61">
-        <v>1312.242012198322</v>
+        <v>1366.286366198322</v>
       </c>
       <c r="O61">
-        <v>354.305343293547</v>
+        <v>368.897318873547</v>
       </c>
       <c r="P61">
-        <v>957.9366689047753</v>
+        <v>997.389047324775</v>
       </c>
       <c r="Q61">
-        <v>1777.136668904775</v>
+        <v>1816.589047324775</v>
       </c>
       <c r="R61">
         <v>1.439024390243902</v>
       </c>
       <c r="S61">
-        <v>0.1254047373403095</v>
+        <v>0.1253721347776517</v>
       </c>
       <c r="T61">
         <v>1.457391593032172</v>
       </c>
       <c r="U61">
-        <v>0.06888110587651872</v>
+        <v>0.06368110587651873</v>
       </c>
       <c r="V61">
         <v>0.27</v>
       </c>
       <c r="W61">
-        <v>0.05028320728985866</v>
+        <v>0.04648720728985867</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y61">
-        <v>2.833018467269342</v>
+        <v>3.064353897567398</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6344,13 +6344,13 @@
         <v>0.6</v>
       </c>
       <c r="B62">
-        <v>0.08102304636200078</v>
+        <v>0.07873212224105636</v>
       </c>
       <c r="C62">
-        <v>6700.402522692864</v>
+        <v>7764.509117162492</v>
       </c>
       <c r="D62">
-        <v>15389.60252269286</v>
+        <v>16453.70911716249</v>
       </c>
       <c r="E62">
         <v>903</v>
@@ -6377,45 +6377,45 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M62">
-        <v>728.0250723406892</v>
+        <v>673.0647123406894</v>
       </c>
       <c r="N62">
-        <v>1300.108260992644</v>
+        <v>1355.068620992644</v>
       </c>
       <c r="O62">
-        <v>351.0292304680138</v>
+        <v>365.8685276680139</v>
       </c>
       <c r="P62">
-        <v>949.0790305246301</v>
+        <v>989.20009332463</v>
       </c>
       <c r="Q62">
-        <v>1768.27903052463</v>
+        <v>1808.40009332463</v>
       </c>
       <c r="R62">
         <v>1.5</v>
       </c>
       <c r="S62">
-        <v>0.127132804970214</v>
+        <v>0.1270994946678529</v>
       </c>
       <c r="T62">
         <v>1.489028796044944</v>
       </c>
       <c r="U62">
-        <v>0.06888110587651872</v>
+        <v>0.06368110587651873</v>
       </c>
       <c r="V62">
         <v>0.27</v>
       </c>
       <c r="W62">
-        <v>0.05028320728985866</v>
+        <v>0.04648720728985867</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y62">
-        <v>2.785801492814852</v>
+        <v>3.013281332607941</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6426,13 +6426,13 @@
         <v>0.61</v>
       </c>
       <c r="B63">
-        <v>0.08096305811345805</v>
+        <v>0.07974746692225891</v>
       </c>
       <c r="C63">
-        <v>6550.502215846294</v>
+        <v>7096.235336211243</v>
       </c>
       <c r="D63">
-        <v>15415.85721584629</v>
+        <v>15961.59033621124</v>
       </c>
       <c r="E63">
         <v>1079.155000000001</v>
@@ -6459,37 +6459,37 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M63">
-        <v>740.1588235463674</v>
+        <v>711.1460950463675</v>
       </c>
       <c r="N63">
-        <v>1287.974509786966</v>
+        <v>1316.987238286966</v>
       </c>
       <c r="O63">
-        <v>347.7531176424808</v>
+        <v>355.5865543374808</v>
       </c>
       <c r="P63">
-        <v>940.2213921444851</v>
+        <v>961.400683949485</v>
       </c>
       <c r="Q63">
-        <v>1759.421392144485</v>
+        <v>1780.600683949485</v>
       </c>
       <c r="R63">
         <v>1.564102564102564</v>
       </c>
       <c r="S63">
-        <v>0.128949491452934</v>
+        <v>0.1289154371165259</v>
       </c>
       <c r="T63">
         <v>1.522288419725037</v>
       </c>
       <c r="U63">
-        <v>0.06888110587651872</v>
+        <v>0.06618110587651872</v>
       </c>
       <c r="V63">
         <v>0.27</v>
       </c>
       <c r="W63">
-        <v>0.05028320728985866</v>
+        <v>0.04831220728985867</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6497,7 +6497,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>2.740132615883462</v>
+        <v>2.851922196382302</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6508,13 +6508,13 @@
         <v>0.62</v>
       </c>
       <c r="B64">
-        <v>0.08090306986491531</v>
+        <v>0.07966781160346145</v>
       </c>
       <c r="C64">
-        <v>6400.69164320613</v>
+        <v>6957.621160567767</v>
       </c>
       <c r="D64">
-        <v>15442.20164320613</v>
+        <v>15999.13116056777</v>
       </c>
       <c r="E64">
         <v>1255.310000000001</v>
@@ -6541,37 +6541,37 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M64">
-        <v>752.2925747520457</v>
+        <v>722.8042277520457</v>
       </c>
       <c r="N64">
-        <v>1275.840758581287</v>
+        <v>1305.329105581287</v>
       </c>
       <c r="O64">
-        <v>344.4770048169476</v>
+        <v>352.4388585069476</v>
       </c>
       <c r="P64">
-        <v>931.3637537643399</v>
+        <v>952.8902470743399</v>
       </c>
       <c r="Q64">
-        <v>1750.56375376434</v>
+        <v>1772.09024707434</v>
       </c>
       <c r="R64">
         <v>1.631578947368421</v>
       </c>
       <c r="S64">
-        <v>0.1308617930136919</v>
+        <v>0.1308269554835502</v>
       </c>
       <c r="T64">
         <v>1.557298549914609</v>
       </c>
       <c r="U64">
-        <v>0.06888110587651872</v>
+        <v>0.06618110587651872</v>
       </c>
       <c r="V64">
         <v>0.27</v>
       </c>
       <c r="W64">
-        <v>0.05028320728985866</v>
+        <v>0.04831220728985867</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6579,7 +6579,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>2.695936928530502</v>
+        <v>2.80592345127936</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6590,13 +6590,13 @@
         <v>0.63</v>
       </c>
       <c r="B65">
-        <v>0.08084308161637258</v>
+        <v>0.07958815628466399</v>
       </c>
       <c r="C65">
-        <v>6250.971265604949</v>
+        <v>6819.183989334171</v>
       </c>
       <c r="D65">
-        <v>15468.63626560495</v>
+        <v>16036.84898933417</v>
       </c>
       <c r="E65">
         <v>1431.465</v>
@@ -6623,37 +6623,37 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M65">
-        <v>764.4263259577237</v>
+        <v>734.4623604577238</v>
       </c>
       <c r="N65">
-        <v>1263.707007375609</v>
+        <v>1293.67097287561</v>
       </c>
       <c r="O65">
-        <v>341.2008919914146</v>
+        <v>349.2911626764146</v>
       </c>
       <c r="P65">
-        <v>922.5061153841949</v>
+        <v>944.3798101991949</v>
       </c>
       <c r="Q65">
-        <v>1741.706115384195</v>
+        <v>1763.579810199195</v>
       </c>
       <c r="R65">
         <v>1.702702702702703</v>
       </c>
       <c r="S65">
-        <v>0.1328774622263827</v>
+        <v>0.1328417991677109</v>
       </c>
       <c r="T65">
         <v>1.594201119573887</v>
       </c>
       <c r="U65">
-        <v>0.06888110587651872</v>
+        <v>0.06618110587651872</v>
       </c>
       <c r="V65">
         <v>0.27</v>
       </c>
       <c r="W65">
-        <v>0.05028320728985866</v>
+        <v>0.04831220728985867</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6661,7 +6661,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>2.653144278871288</v>
+        <v>2.761384983798736</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6672,13 +6672,13 @@
         <v>0.64</v>
       </c>
       <c r="B66">
-        <v>0.08078309336782982</v>
+        <v>0.07950850096586655</v>
       </c>
       <c r="C66">
-        <v>6101.341547036232</v>
+        <v>6680.925077328275</v>
       </c>
       <c r="D66">
-        <v>15495.16154703623</v>
+        <v>16074.74507732827</v>
       </c>
       <c r="E66">
         <v>1607.620000000001</v>
@@ -6705,37 +6705,37 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M66">
-        <v>776.5600771634018</v>
+        <v>746.120493163402</v>
       </c>
       <c r="N66">
-        <v>1251.573256169931</v>
+        <v>1282.012840169931</v>
       </c>
       <c r="O66">
-        <v>337.9247791658815</v>
+        <v>346.1434668458814</v>
       </c>
       <c r="P66">
-        <v>913.6484770040499</v>
+        <v>935.8693733240498</v>
       </c>
       <c r="Q66">
-        <v>1732.84847700405</v>
+        <v>1755.06937332405</v>
       </c>
       <c r="R66">
         <v>1.777777777777778</v>
       </c>
       <c r="S66">
-        <v>0.1350051130620008</v>
+        <v>0.1349685786121028</v>
       </c>
       <c r="T66">
         <v>1.633153831992015</v>
       </c>
       <c r="U66">
-        <v>0.06888110587651872</v>
+        <v>0.06618110587651872</v>
       </c>
       <c r="V66">
         <v>0.27</v>
       </c>
       <c r="W66">
-        <v>0.05028320728985866</v>
+        <v>0.04831220728985867</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6743,7 +6743,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>2.611688899513925</v>
+        <v>2.718238343426881</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6754,13 +6754,13 @@
         <v>0.65</v>
       </c>
       <c r="B67">
-        <v>0.08072310511928708</v>
+        <v>0.07942884564706909</v>
       </c>
       <c r="C67">
-        <v>5951.802954681498</v>
+        <v>6542.84569125688</v>
       </c>
       <c r="D67">
-        <v>15521.7779546815</v>
+        <v>16112.82069125688</v>
       </c>
       <c r="E67">
         <v>1783.775000000001</v>
@@ -6787,37 +6787,37 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M67">
-        <v>788.6938283690801</v>
+        <v>757.7786258690802</v>
       </c>
       <c r="N67">
-        <v>1239.439504964253</v>
+        <v>1270.354707464253</v>
       </c>
       <c r="O67">
-        <v>334.6486663403484</v>
+        <v>342.9957710153483</v>
       </c>
       <c r="P67">
-        <v>904.7908386239046</v>
+        <v>927.3589364489046</v>
       </c>
       <c r="Q67">
-        <v>1723.990838623904</v>
+        <v>1746.558936448904</v>
       </c>
       <c r="R67">
         <v>1.857142857142857</v>
       </c>
       <c r="S67">
-        <v>0.1372543439453685</v>
+        <v>0.1372168883104599</v>
       </c>
       <c r="T67">
         <v>1.674332413691178</v>
       </c>
       <c r="U67">
-        <v>0.06888110587651872</v>
+        <v>0.06618110587651872</v>
       </c>
       <c r="V67">
         <v>0.27</v>
       </c>
       <c r="W67">
-        <v>0.05028320728985866</v>
+        <v>0.04831220728985867</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6825,7 +6825,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>2.571509070290633</v>
+        <v>2.676419291989544</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6836,13 +6836,13 @@
         <v>0.66</v>
       </c>
       <c r="B68">
-        <v>0.08066311687074434</v>
+        <v>0.07934919032827163</v>
       </c>
       <c r="C68">
-        <v>5802.355958937767</v>
+        <v>6404.947109856845</v>
       </c>
       <c r="D68">
-        <v>15548.48595893777</v>
+        <v>16151.07710985685</v>
       </c>
       <c r="E68">
         <v>1959.930000000002</v>
@@ -6869,37 +6869,37 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M68">
-        <v>800.8275795747583</v>
+        <v>769.4367585747584</v>
       </c>
       <c r="N68">
-        <v>1227.305753758575</v>
+        <v>1258.696574758575</v>
       </c>
       <c r="O68">
-        <v>331.3725535148153</v>
+        <v>339.8480751848152</v>
       </c>
       <c r="P68">
-        <v>895.9332002437598</v>
+        <v>918.8484995737596</v>
       </c>
       <c r="Q68">
-        <v>1715.13320024376</v>
+        <v>1738.048499573759</v>
       </c>
       <c r="R68">
         <v>1.941176470588236</v>
       </c>
       <c r="S68">
-        <v>0.1396358825277577</v>
+        <v>0.1395974515204851</v>
       </c>
       <c r="T68">
         <v>1.717933264902056</v>
       </c>
       <c r="U68">
-        <v>0.06888110587651872</v>
+        <v>0.06618110587651872</v>
       </c>
       <c r="V68">
         <v>0.27</v>
       </c>
       <c r="W68">
-        <v>0.05028320728985866</v>
+        <v>0.04831220728985867</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>2.532546811649866</v>
+        <v>2.635867484535157</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6918,13 +6918,13 @@
         <v>0.67</v>
       </c>
       <c r="B69">
-        <v>0.08192369862220161</v>
+        <v>0.07926953500947419</v>
       </c>
       <c r="C69">
-        <v>5083.617048369424</v>
+        <v>6267.230624038284</v>
       </c>
       <c r="D69">
-        <v>15005.90204836942</v>
+        <v>16189.51562403828</v>
       </c>
       <c r="E69">
         <v>2136.085000000001</v>
@@ -6951,45 +6951,45 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M69">
-        <v>844.8277702804364</v>
+        <v>781.0948912804364</v>
       </c>
       <c r="N69">
-        <v>1183.305563052897</v>
+        <v>1247.038442052897</v>
       </c>
       <c r="O69">
-        <v>319.4925020242821</v>
+        <v>336.7003793542821</v>
       </c>
       <c r="P69">
-        <v>863.8130610286146</v>
+        <v>910.3380626986145</v>
       </c>
       <c r="Q69">
-        <v>1683.013061028614</v>
+        <v>1729.538062698614</v>
       </c>
       <c r="R69">
         <v>2.030303030303031</v>
       </c>
       <c r="S69">
-        <v>0.142161756781807</v>
+        <v>0.1421222912886936</v>
       </c>
       <c r="T69">
         <v>1.764176591943898</v>
       </c>
       <c r="U69">
-        <v>0.07158110587651872</v>
+        <v>0.06618110587651872</v>
       </c>
       <c r="V69">
         <v>0.27</v>
       </c>
       <c r="W69">
-        <v>0.05225420728985867</v>
+        <v>0.04831220728985867</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y69">
-        <v>2.400647095987511</v>
+        <v>2.596526178795826</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7000,13 +7000,13 @@
         <v>0.68</v>
       </c>
       <c r="B70">
-        <v>0.08188342037365887</v>
+        <v>0.07918987969067673</v>
       </c>
       <c r="C70">
-        <v>4924.212440822615</v>
+        <v>6129.697537029759</v>
       </c>
       <c r="D70">
-        <v>15022.65244082262</v>
+        <v>16228.13753702976</v>
       </c>
       <c r="E70">
         <v>2312.240000000002</v>
@@ -7033,45 +7033,45 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M70">
-        <v>857.4371399861146</v>
+        <v>792.7530239861146</v>
       </c>
       <c r="N70">
-        <v>1170.696193347218</v>
+        <v>1235.380309347219</v>
       </c>
       <c r="O70">
-        <v>316.087972203749</v>
+        <v>333.5526835237491</v>
       </c>
       <c r="P70">
-        <v>854.6082211434694</v>
+        <v>901.8276258234696</v>
       </c>
       <c r="Q70">
-        <v>1673.808221143469</v>
+        <v>1721.027625823469</v>
       </c>
       <c r="R70">
         <v>2.125</v>
       </c>
       <c r="S70">
-        <v>0.1448454981767343</v>
+        <v>0.1448049335424151</v>
       </c>
       <c r="T70">
         <v>1.813310126925854</v>
       </c>
       <c r="U70">
-        <v>0.07158110587651872</v>
+        <v>0.06618110587651872</v>
       </c>
       <c r="V70">
         <v>0.27</v>
       </c>
       <c r="W70">
-        <v>0.05225420728985867</v>
+        <v>0.04831220728985867</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y70">
-        <v>2.365343462222988</v>
+        <v>2.558341970284123</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7082,13 +7082,13 @@
         <v>0.6900000000000001</v>
       </c>
       <c r="B71">
-        <v>0.08184314212511612</v>
+        <v>0.07911022437187928</v>
       </c>
       <c r="C71">
-        <v>4764.845270437532</v>
+        <v>5992.349164525558</v>
       </c>
       <c r="D71">
-        <v>15039.44027043754</v>
+        <v>16266.94416452556</v>
       </c>
       <c r="E71">
         <v>2488.395000000002</v>
@@ -7115,45 +7115,45 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M71">
-        <v>870.0465096917928</v>
+        <v>804.4111566917928</v>
       </c>
       <c r="N71">
-        <v>1158.08682364154</v>
+        <v>1223.72217664154</v>
       </c>
       <c r="O71">
-        <v>312.6834423832159</v>
+        <v>330.404987693216</v>
       </c>
       <c r="P71">
-        <v>845.4033812583244</v>
+        <v>893.3171889483245</v>
       </c>
       <c r="Q71">
-        <v>1664.603381258324</v>
+        <v>1712.517188948324</v>
       </c>
       <c r="R71">
         <v>2.225806451612904</v>
       </c>
       <c r="S71">
-        <v>0.147702384177786</v>
+        <v>0.1476606494899252</v>
       </c>
       <c r="T71">
         <v>1.865613567390516</v>
       </c>
       <c r="U71">
-        <v>0.07158110587651872</v>
+        <v>0.06618110587651872</v>
       </c>
       <c r="V71">
         <v>0.27</v>
       </c>
       <c r="W71">
-        <v>0.05225420728985867</v>
+        <v>0.04831220728985867</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y71">
-        <v>2.331063122190771</v>
+        <v>2.521264550424933</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7164,13 +7164,13 @@
         <v>0.7000000000000001</v>
       </c>
       <c r="B72">
-        <v>0.0818028638765734</v>
+        <v>0.08081906905308184</v>
       </c>
       <c r="C72">
-        <v>4605.515662862779</v>
+        <v>5022.407185984443</v>
       </c>
       <c r="D72">
-        <v>15056.26566286278</v>
+        <v>15473.15718598444</v>
       </c>
       <c r="E72">
         <v>2664.550000000001</v>
@@ -7197,37 +7197,37 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M72">
-        <v>882.6558793974709</v>
+        <v>859.227264397471</v>
       </c>
       <c r="N72">
-        <v>1145.477453935862</v>
+        <v>1168.906068935862</v>
       </c>
       <c r="O72">
-        <v>309.2789125626828</v>
+        <v>315.6046386126828</v>
       </c>
       <c r="P72">
-        <v>836.1985413731795</v>
+        <v>853.3014303231794</v>
       </c>
       <c r="Q72">
-        <v>1655.398541373179</v>
+        <v>1672.501430323179</v>
       </c>
       <c r="R72">
         <v>2.333333333333334</v>
       </c>
       <c r="S72">
-        <v>0.1507497292455744</v>
+        <v>0.1507067465006026</v>
       </c>
       <c r="T72">
         <v>1.921403903886157</v>
       </c>
       <c r="U72">
-        <v>0.07158110587651872</v>
+        <v>0.06968110587651873</v>
       </c>
       <c r="V72">
         <v>0.27</v>
       </c>
       <c r="W72">
-        <v>0.05225420728985867</v>
+        <v>0.05086720728985867</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7235,7 +7235,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>2.297762220445188</v>
+        <v>2.360415477220164</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7246,13 +7246,13 @@
         <v>0.71</v>
       </c>
       <c r="B73">
-        <v>0.08176258562803065</v>
+        <v>0.08076496373428438</v>
       </c>
       <c r="C73">
-        <v>4446.223744309898</v>
+        <v>4870.19558568916</v>
       </c>
       <c r="D73">
-        <v>15073.1287443099</v>
+        <v>15497.10058568916</v>
       </c>
       <c r="E73">
         <v>2840.705</v>
@@ -7279,37 +7279,37 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M73">
-        <v>895.265249103149</v>
+        <v>871.501939603149</v>
       </c>
       <c r="N73">
-        <v>1132.868084230184</v>
+        <v>1156.631393730184</v>
       </c>
       <c r="O73">
-        <v>305.8743827421497</v>
+        <v>312.2904763071498</v>
       </c>
       <c r="P73">
-        <v>826.9937014880345</v>
+        <v>844.3409174230345</v>
       </c>
       <c r="Q73">
-        <v>1646.193701488034</v>
+        <v>1663.540917423034</v>
       </c>
       <c r="R73">
         <v>2.448275862068965</v>
       </c>
       <c r="S73">
-        <v>0.1540072360421759</v>
+        <v>0.1539629191671887</v>
       </c>
       <c r="T73">
         <v>1.981041849795289</v>
       </c>
       <c r="U73">
-        <v>0.07158110587651872</v>
+        <v>0.06968110587651873</v>
       </c>
       <c r="V73">
         <v>0.27</v>
       </c>
       <c r="W73">
-        <v>0.05225420728985867</v>
+        <v>0.05086720728985867</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7317,7 +7317,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>2.265399372269904</v>
+        <v>2.327170188808614</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7328,13 +7328,13 @@
         <v>0.72</v>
       </c>
       <c r="B74">
-        <v>0.08419262737948793</v>
+        <v>0.08071085841548693</v>
       </c>
       <c r="C74">
-        <v>3316.022754914202</v>
+        <v>4718.058201000873</v>
       </c>
       <c r="D74">
-        <v>14119.0827549142</v>
+        <v>15521.11820100087</v>
       </c>
       <c r="E74">
         <v>3016.860000000001</v>
@@ -7361,45 +7361,45 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M74">
-        <v>967.4854708088274</v>
+        <v>883.7766148088273</v>
       </c>
       <c r="N74">
-        <v>1060.647862524506</v>
+        <v>1144.356718524506</v>
       </c>
       <c r="O74">
-        <v>286.3749228816166</v>
+        <v>308.9763140016166</v>
       </c>
       <c r="P74">
-        <v>774.2729396428892</v>
+        <v>835.3804045228894</v>
       </c>
       <c r="Q74">
-        <v>1593.472939642889</v>
+        <v>1654.580404522889</v>
       </c>
       <c r="R74">
         <v>2.571428571428571</v>
       </c>
       <c r="S74">
-        <v>0.1574974218956774</v>
+        <v>0.1574516755956739</v>
       </c>
       <c r="T74">
         <v>2.044939648983646</v>
       </c>
       <c r="U74">
-        <v>0.07628110587651873</v>
+        <v>0.06968110587651873</v>
       </c>
       <c r="V74">
         <v>0.27</v>
       </c>
       <c r="W74">
-        <v>0.05568520728985867</v>
+        <v>0.05086720728985867</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y74">
-        <v>2.096293323803399</v>
+        <v>2.294848380630716</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7410,13 +7410,13 @@
         <v>0.73</v>
       </c>
       <c r="B75">
-        <v>0.08418665913094517</v>
+        <v>0.08065675309668946</v>
       </c>
       <c r="C75">
-        <v>3142.062949728883</v>
+        <v>4565.995377516252</v>
       </c>
       <c r="D75">
-        <v>14121.27794972888</v>
+        <v>15545.21037751625</v>
       </c>
       <c r="E75">
         <v>3193.015000000001</v>
@@ -7443,45 +7443,45 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M75">
-        <v>980.9227690145055</v>
+        <v>896.0512900145054</v>
       </c>
       <c r="N75">
-        <v>1047.210564318828</v>
+        <v>1132.082043318828</v>
       </c>
       <c r="O75">
-        <v>282.7468523660835</v>
+        <v>305.6621516960835</v>
       </c>
       <c r="P75">
-        <v>764.4637119527442</v>
+        <v>826.4198916227442</v>
       </c>
       <c r="Q75">
-        <v>1583.663711952744</v>
+        <v>1645.619891622744</v>
       </c>
       <c r="R75">
         <v>2.703703703703703</v>
       </c>
       <c r="S75">
-        <v>0.1612461400346235</v>
+        <v>0.161198858426269</v>
       </c>
       <c r="T75">
         <v>2.113570618482251</v>
       </c>
       <c r="U75">
-        <v>0.07628110587651873</v>
+        <v>0.06968110587651873</v>
       </c>
       <c r="V75">
         <v>0.27</v>
       </c>
       <c r="W75">
-        <v>0.05568520728985867</v>
+        <v>0.05086720728985867</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y75">
-        <v>2.067576976901983</v>
+        <v>2.263412101443994</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7492,13 +7492,13 @@
         <v>0.74</v>
       </c>
       <c r="B76">
-        <v>0.08418069088240243</v>
+        <v>0.08211520777789202</v>
       </c>
       <c r="C76">
-        <v>2968.103827254989</v>
+        <v>3765.529345509172</v>
       </c>
       <c r="D76">
-        <v>14123.47382725499</v>
+        <v>14920.89934550917</v>
       </c>
       <c r="E76">
         <v>3369.17</v>
@@ -7525,37 +7525,37 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M76">
-        <v>994.3600672201836</v>
+        <v>944.8252812201835</v>
       </c>
       <c r="N76">
-        <v>1033.773266113149</v>
+        <v>1083.30805211315</v>
       </c>
       <c r="O76">
-        <v>279.1187818505504</v>
+        <v>292.4931740705504</v>
       </c>
       <c r="P76">
-        <v>754.6544842625991</v>
+        <v>790.8148780425993</v>
       </c>
       <c r="Q76">
-        <v>1573.854484262599</v>
+        <v>1610.014878042599</v>
       </c>
       <c r="R76">
         <v>2.846153846153846</v>
       </c>
       <c r="S76">
-        <v>0.1652832211073347</v>
+        <v>0.1652342860899869</v>
       </c>
       <c r="T76">
         <v>2.187480893326903</v>
       </c>
       <c r="U76">
-        <v>0.07628110587651873</v>
+        <v>0.07248110587651872</v>
       </c>
       <c r="V76">
         <v>0.27</v>
       </c>
       <c r="W76">
-        <v>0.05568520728985867</v>
+        <v>0.05291120728985867</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>2.039636747484388</v>
+        <v>2.146569713623798</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7574,13 +7574,13 @@
         <v>0.75</v>
       </c>
       <c r="B77">
-        <v>0.08417472263385969</v>
+        <v>0.08208154245909458</v>
       </c>
       <c r="C77">
-        <v>2794.145387811064</v>
+        <v>3603.219314580638</v>
       </c>
       <c r="D77">
-        <v>14125.67038781106</v>
+        <v>14934.74431458064</v>
       </c>
       <c r="E77">
         <v>3545.325000000001</v>
@@ -7607,37 +7607,37 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M77">
-        <v>1007.797365425862</v>
+        <v>957.5931904258616</v>
       </c>
       <c r="N77">
-        <v>1020.335967907471</v>
+        <v>1070.540142907472</v>
       </c>
       <c r="O77">
-        <v>275.4907113350173</v>
+        <v>289.0458385850173</v>
       </c>
       <c r="P77">
-        <v>744.8452565724541</v>
+        <v>781.4943043224542</v>
       </c>
       <c r="Q77">
-        <v>1564.045256572454</v>
+        <v>1600.694304322454</v>
       </c>
       <c r="R77">
         <v>3</v>
       </c>
       <c r="S77">
-        <v>0.1696432686658628</v>
+        <v>0.1695925479668023</v>
       </c>
       <c r="T77">
         <v>2.267303990159127</v>
       </c>
       <c r="U77">
-        <v>0.07628110587651873</v>
+        <v>0.07248110587651872</v>
       </c>
       <c r="V77">
         <v>0.27</v>
       </c>
       <c r="W77">
-        <v>0.05568520728985867</v>
+        <v>0.05291120728985867</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>2.012441590851263</v>
+        <v>2.117948784108814</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7656,13 +7656,13 @@
         <v>0.76</v>
       </c>
       <c r="B78">
-        <v>0.08932839438531695</v>
+        <v>0.08204787714029711</v>
       </c>
       <c r="C78">
-        <v>945.5402670086569</v>
+        <v>3440.935000760766</v>
       </c>
       <c r="D78">
-        <v>12453.22026700866</v>
+        <v>14948.61500076077</v>
       </c>
       <c r="E78">
         <v>3721.480000000001</v>
@@ -7689,45 +7689,45 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M78">
-        <v>1145.74101763154</v>
+        <v>970.3610996315399</v>
       </c>
       <c r="N78">
-        <v>882.3923157017932</v>
+        <v>1057.772233701793</v>
       </c>
       <c r="O78">
-        <v>238.2459252394842</v>
+        <v>285.5985030994842</v>
       </c>
       <c r="P78">
-        <v>644.146390462309</v>
+        <v>772.1737306023091</v>
       </c>
       <c r="Q78">
-        <v>1463.346390462309</v>
+        <v>1591.373730602309</v>
       </c>
       <c r="R78">
         <v>3.166666666666667</v>
       </c>
       <c r="S78">
-        <v>0.1743666535209349</v>
+        <v>0.1743139983333522</v>
       </c>
       <c r="T78">
         <v>2.35377901172737</v>
       </c>
       <c r="U78">
-        <v>0.08558110587651872</v>
+        <v>0.07248110587651872</v>
       </c>
       <c r="V78">
         <v>0.27</v>
       </c>
       <c r="W78">
-        <v>0.06247420728985867</v>
+        <v>0.05291120728985867</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y78">
-        <v>1.770149887385426</v>
+        <v>2.090081036949487</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7738,13 +7738,13 @@
         <v>0.77</v>
       </c>
       <c r="B79">
-        <v>0.09203218613677422</v>
+        <v>0.08201421182149965</v>
       </c>
       <c r="C79">
-        <v>41.08498422718367</v>
+        <v>3278.676475770679</v>
       </c>
       <c r="D79">
-        <v>11724.91998422718</v>
+        <v>14962.51147577068</v>
       </c>
       <c r="E79">
         <v>3897.635</v>
@@ -7771,45 +7771,45 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M79">
-        <v>1224.567051837218</v>
+        <v>983.129008837218</v>
       </c>
       <c r="N79">
-        <v>803.5662814961154</v>
+        <v>1045.004324496115</v>
       </c>
       <c r="O79">
-        <v>216.9628960039512</v>
+        <v>282.1511676139511</v>
       </c>
       <c r="P79">
-        <v>586.6033854921642</v>
+        <v>762.8531568821641</v>
       </c>
       <c r="Q79">
-        <v>1405.803385492164</v>
+        <v>1582.053156882164</v>
       </c>
       <c r="R79">
         <v>3.347826086956522</v>
       </c>
       <c r="S79">
-        <v>0.1795007674938393</v>
+        <v>0.1794460096013412</v>
       </c>
       <c r="T79">
         <v>2.447773600388503</v>
       </c>
       <c r="U79">
-        <v>0.09028110587651872</v>
+        <v>0.07248110587651872</v>
       </c>
       <c r="V79">
         <v>0.27</v>
       </c>
       <c r="W79">
-        <v>0.06590520728985866</v>
+        <v>0.05291120728985867</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y79">
-        <v>1.656204395088472</v>
+        <v>2.062937127378714</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7820,13 +7820,13 @@
         <v>0.78</v>
       </c>
       <c r="B80">
-        <v>0.09212841788823148</v>
+        <v>0.0819805465027022</v>
       </c>
       <c r="C80">
-        <v>-159.4246049690319</v>
+        <v>3116.443811598434</v>
       </c>
       <c r="D80">
-        <v>11700.56539503097</v>
+        <v>14976.43381159843</v>
       </c>
       <c r="E80">
         <v>4073.790000000001</v>
@@ -7853,45 +7853,45 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M80">
-        <v>1240.470520042896</v>
+        <v>995.8969180428961</v>
       </c>
       <c r="N80">
-        <v>787.662813290437</v>
+        <v>1032.236415290437</v>
       </c>
       <c r="O80">
-        <v>212.668959588418</v>
+        <v>278.703832128418</v>
       </c>
       <c r="P80">
-        <v>574.993853702019</v>
+        <v>753.5325831620189</v>
       </c>
       <c r="Q80">
-        <v>1394.193853702019</v>
+        <v>1572.732583162019</v>
       </c>
       <c r="R80">
         <v>3.545454545454546</v>
       </c>
       <c r="S80">
-        <v>0.1851016191006442</v>
+        <v>0.1850445673482384</v>
       </c>
       <c r="T80">
         <v>2.550313151655193</v>
       </c>
       <c r="U80">
-        <v>0.09028110587651872</v>
+        <v>0.07248110587651872</v>
       </c>
       <c r="V80">
         <v>0.27</v>
       </c>
       <c r="W80">
-        <v>0.06590520728985866</v>
+        <v>0.05291120728985867</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y80">
-        <v>1.634971005407851</v>
+        <v>2.036489215489244</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7902,13 +7902,13 @@
         <v>0.79</v>
       </c>
       <c r="B81">
-        <v>0.09222464963968874</v>
+        <v>0.08194688118390475</v>
       </c>
       <c r="C81">
-        <v>-359.833226907871</v>
+        <v>2954.237080500285</v>
       </c>
       <c r="D81">
-        <v>11676.31177309213</v>
+        <v>14990.38208050029</v>
       </c>
       <c r="E81">
         <v>4249.945000000002</v>
@@ -7935,45 +7935,45 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M81">
-        <v>1256.373988248574</v>
+        <v>1008.664827248574</v>
       </c>
       <c r="N81">
-        <v>771.7593450847589</v>
+        <v>1019.468506084759</v>
       </c>
       <c r="O81">
-        <v>208.3750231728849</v>
+        <v>275.2564966428849</v>
       </c>
       <c r="P81">
-        <v>563.3843219118739</v>
+        <v>744.212009441874</v>
       </c>
       <c r="Q81">
-        <v>1382.584321911874</v>
+        <v>1563.412009441874</v>
       </c>
       <c r="R81">
         <v>3.761904761904763</v>
       </c>
       <c r="S81">
-        <v>0.1912358851461924</v>
+        <v>0.1911763210710305</v>
       </c>
       <c r="T81">
         <v>2.662618374471093</v>
       </c>
       <c r="U81">
-        <v>0.09028110587651872</v>
+        <v>0.07248110587651872</v>
       </c>
       <c r="V81">
         <v>0.27</v>
       </c>
       <c r="W81">
-        <v>0.06590520728985866</v>
+        <v>0.05291120728985867</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y81">
-        <v>1.614275169896359</v>
+        <v>2.01071087098938</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7984,13 +7984,13 @@
         <v>0.8</v>
       </c>
       <c r="B82">
-        <v>0.092320881391146</v>
+        <v>0.08646841586510731</v>
       </c>
       <c r="C82">
-        <v>-560.1415081631894</v>
+        <v>1111.443953107353</v>
       </c>
       <c r="D82">
-        <v>11652.15849183681</v>
+        <v>13323.74395310735</v>
       </c>
       <c r="E82">
         <v>4426.100000000002</v>
@@ -8017,45 +8017,45 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M82">
-        <v>1272.277456454253</v>
+        <v>1131.353456454253</v>
       </c>
       <c r="N82">
-        <v>755.8558768790806</v>
+        <v>896.7798768790803</v>
       </c>
       <c r="O82">
-        <v>204.0810867573518</v>
+        <v>242.1305667573517</v>
       </c>
       <c r="P82">
-        <v>551.7747901217288</v>
+        <v>654.6493101217286</v>
       </c>
       <c r="Q82">
-        <v>1370.974790121729</v>
+        <v>1473.849310121728</v>
       </c>
       <c r="R82">
         <v>4.000000000000001</v>
       </c>
       <c r="S82">
-        <v>0.1979835777962954</v>
+        <v>0.1979212501661018</v>
       </c>
       <c r="T82">
         <v>2.786154119568582</v>
       </c>
       <c r="U82">
-        <v>0.09028110587651872</v>
+        <v>0.08028110587651874</v>
       </c>
       <c r="V82">
         <v>0.27</v>
       </c>
       <c r="W82">
-        <v>0.06590520728985866</v>
+        <v>0.05860520728985868</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y82">
-        <v>1.594096730272654</v>
+        <v>1.792661101411805</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8066,13 +8066,13 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="B83">
-        <v>0.09241711314260326</v>
+        <v>0.08649169054630985</v>
       </c>
       <c r="C83">
-        <v>-760.3500701350986</v>
+        <v>927.6680877962899</v>
       </c>
       <c r="D83">
-        <v>11628.1049298649</v>
+        <v>13316.12308779629</v>
       </c>
       <c r="E83">
         <v>4602.255000000001</v>
@@ -8099,45 +8099,45 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M83">
-        <v>1288.18092465993</v>
+        <v>1145.495374659931</v>
       </c>
       <c r="N83">
-        <v>739.9524086734027</v>
+        <v>882.6379586734024</v>
       </c>
       <c r="O83">
-        <v>199.7871503418187</v>
+        <v>238.3122488418187</v>
       </c>
       <c r="P83">
-        <v>540.165258331584</v>
+        <v>644.3257098315837</v>
       </c>
       <c r="Q83">
-        <v>1359.365258331584</v>
+        <v>1463.525709831584</v>
       </c>
       <c r="R83">
         <v>4.263157894736843</v>
       </c>
       <c r="S83">
-        <v>0.2054415538832513</v>
+        <v>0.2053761717974965</v>
       </c>
       <c r="T83">
         <v>2.922693627307913</v>
       </c>
       <c r="U83">
-        <v>0.09028110587651872</v>
+        <v>0.08028110587651874</v>
       </c>
       <c r="V83">
         <v>0.27</v>
       </c>
       <c r="W83">
-        <v>0.06590520728985866</v>
+        <v>0.05860520728985868</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y83">
-        <v>1.574416523726079</v>
+        <v>1.770529482875857</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8148,13 +8148,13 @@
         <v>0.8200000000000001</v>
       </c>
       <c r="B84">
-        <v>0.09251334489406052</v>
+        <v>0.08884950522751239</v>
       </c>
       <c r="C84">
-        <v>-960.4595291032456</v>
+        <v>22.19110494941742</v>
       </c>
       <c r="D84">
-        <v>11604.15047089675</v>
+        <v>12586.80110494942</v>
       </c>
       <c r="E84">
         <v>4778.410000000002</v>
@@ -8181,37 +8181,37 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M84">
-        <v>1304.084392865609</v>
+        <v>1215.971661865609</v>
       </c>
       <c r="N84">
-        <v>724.0489404677244</v>
+        <v>812.1616714677243</v>
       </c>
       <c r="O84">
-        <v>195.4932139262856</v>
+        <v>219.2836512962856</v>
       </c>
       <c r="P84">
-        <v>528.5557265414388</v>
+        <v>592.8780201714387</v>
       </c>
       <c r="Q84">
-        <v>1347.755726541439</v>
+        <v>1412.078020171439</v>
       </c>
       <c r="R84">
         <v>4.555555555555557</v>
       </c>
       <c r="S84">
-        <v>0.213728193979869</v>
+        <v>0.2136594180546016</v>
       </c>
       <c r="T84">
         <v>3.074404191462725</v>
       </c>
       <c r="U84">
-        <v>0.09028110587651872</v>
+        <v>0.08418110587651872</v>
       </c>
       <c r="V84">
         <v>0.27</v>
       </c>
       <c r="W84">
-        <v>0.06590520728985866</v>
+        <v>0.06145220728985867</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8219,7 +8219,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>1.555216322217224</v>
+        <v>1.667911676676463</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8230,13 +8230,13 @@
         <v>0.8300000000000001</v>
       </c>
       <c r="B85">
-        <v>0.09260957664551778</v>
+        <v>0.08890124990871495</v>
       </c>
       <c r="C85">
-        <v>-1160.47049627946</v>
+        <v>-169.0748259844913</v>
       </c>
       <c r="D85">
-        <v>11580.29450372054</v>
+        <v>12571.69017401551</v>
       </c>
       <c r="E85">
         <v>4954.565000000002</v>
@@ -8263,37 +8263,37 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M85">
-        <v>1319.987861071287</v>
+        <v>1230.800584571287</v>
       </c>
       <c r="N85">
-        <v>708.1454722620463</v>
+        <v>797.3327487620461</v>
       </c>
       <c r="O85">
-        <v>191.1992775107525</v>
+        <v>215.2798421657525</v>
       </c>
       <c r="P85">
-        <v>516.9461947512938</v>
+        <v>582.0529065962936</v>
       </c>
       <c r="Q85">
-        <v>1336.146194751293</v>
+        <v>1401.252906596294</v>
       </c>
       <c r="R85">
         <v>4.882352941176473</v>
       </c>
       <c r="S85">
-        <v>0.222989732911383</v>
+        <v>0.2229171638713663</v>
       </c>
       <c r="T85">
         <v>3.243963057282809</v>
       </c>
       <c r="U85">
-        <v>0.09028110587651872</v>
+        <v>0.08418110587651872</v>
       </c>
       <c r="V85">
         <v>0.27</v>
       </c>
       <c r="W85">
-        <v>0.06590520728985866</v>
+        <v>0.06145220728985867</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8301,7 +8301,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>1.536478776166414</v>
+        <v>1.647816355270723</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8312,13 +8312,13 @@
         <v>0.84</v>
       </c>
       <c r="B86">
-        <v>0.09270580839697504</v>
+        <v>0.08895299458991748</v>
       </c>
       <c r="C86">
-        <v>-1360.383577859729</v>
+        <v>-360.3045179360706</v>
       </c>
       <c r="D86">
-        <v>11556.53642214027</v>
+        <v>12556.61548206393</v>
       </c>
       <c r="E86">
         <v>5130.719999999999</v>
@@ -8345,37 +8345,37 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M86">
-        <v>1335.891329276965</v>
+        <v>1245.629507276965</v>
       </c>
       <c r="N86">
-        <v>692.2420040563684</v>
+        <v>782.5038260563683</v>
       </c>
       <c r="O86">
-        <v>186.9053410952195</v>
+        <v>211.2760330352195</v>
       </c>
       <c r="P86">
-        <v>505.3366629611489</v>
+        <v>571.2277930211488</v>
       </c>
       <c r="Q86">
-        <v>1324.536662961149</v>
+        <v>1390.427793021149</v>
       </c>
       <c r="R86">
         <v>5.249999999999999</v>
       </c>
       <c r="S86">
-        <v>0.233408964209336</v>
+        <v>0.2333321279152263</v>
       </c>
       <c r="T86">
         <v>3.434716781330401</v>
       </c>
       <c r="U86">
-        <v>0.09028110587651872</v>
+        <v>0.08418110587651872</v>
       </c>
       <c r="V86">
         <v>0.27</v>
       </c>
       <c r="W86">
-        <v>0.06590520728985866</v>
+        <v>0.06145220728985867</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>1.518187362164433</v>
+        <v>1.628199493898453</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8394,13 +8394,13 @@
         <v>0.85</v>
       </c>
       <c r="B87">
-        <v>0.0928020401484323</v>
+        <v>0.08900473927112003</v>
       </c>
       <c r="C87">
-        <v>-1560.199375075556</v>
+        <v>-551.4981011115215</v>
       </c>
       <c r="D87">
-        <v>11532.87562492444</v>
+        <v>12541.57689888848</v>
       </c>
       <c r="E87">
         <v>5306.875</v>
@@ -8427,37 +8427,37 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M87">
-        <v>1351.794797482643</v>
+        <v>1260.458429982643</v>
       </c>
       <c r="N87">
-        <v>676.3385358506901</v>
+        <v>767.6749033506901</v>
       </c>
       <c r="O87">
-        <v>182.6114046796863</v>
+        <v>207.2722239046863</v>
       </c>
       <c r="P87">
-        <v>493.7271311710037</v>
+        <v>560.4026794460037</v>
       </c>
       <c r="Q87">
-        <v>1312.927131171004</v>
+        <v>1379.602679446004</v>
       </c>
       <c r="R87">
         <v>5.666666666666666</v>
       </c>
       <c r="S87">
-        <v>0.2452174263470162</v>
+        <v>0.2451357538316011</v>
       </c>
       <c r="T87">
         <v>3.650904335251007</v>
       </c>
       <c r="U87">
-        <v>0.09028110587651872</v>
+        <v>0.08418110587651872</v>
       </c>
       <c r="V87">
         <v>0.27</v>
       </c>
       <c r="W87">
-        <v>0.06590520728985866</v>
+        <v>0.06145220728985867</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8465,7 +8465,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>1.500326334374263</v>
+        <v>1.609044205734941</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8476,13 +8476,13 @@
         <v>0.86</v>
       </c>
       <c r="B88">
-        <v>0.1031314118998896</v>
+        <v>0.08905648395232259</v>
       </c>
       <c r="C88">
-        <v>-3814.226796937088</v>
+        <v>-742.6557050939846</v>
       </c>
       <c r="D88">
-        <v>9455.003203062912</v>
+        <v>12526.57429490601</v>
       </c>
       <c r="E88">
         <v>5483.030000000001</v>
@@ -8509,45 +8509,45 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M88">
-        <v>1614.632344688321</v>
+        <v>1275.287352688321</v>
       </c>
       <c r="N88">
-        <v>413.5009886450118</v>
+        <v>752.8459806450119</v>
       </c>
       <c r="O88">
-        <v>111.6452669341532</v>
+        <v>203.2684147741532</v>
       </c>
       <c r="P88">
-        <v>301.8557217108586</v>
+        <v>549.5775658708586</v>
       </c>
       <c r="Q88">
-        <v>1121.055721710859</v>
+        <v>1368.777565870858</v>
       </c>
       <c r="R88">
         <v>6.142857142857142</v>
       </c>
       <c r="S88">
-        <v>0.2587128116472222</v>
+        <v>0.2586256120217438</v>
       </c>
       <c r="T88">
         <v>3.897975825445986</v>
       </c>
       <c r="U88">
-        <v>0.1065811058765187</v>
+        <v>0.08418110587651872</v>
       </c>
       <c r="V88">
         <v>0.27</v>
       </c>
       <c r="W88">
-        <v>0.07780420728985867</v>
+        <v>0.06145220728985867</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y88">
-        <v>1.256096064224969</v>
+        <v>1.590334389389186</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8558,13 +8558,13 @@
         <v>0.87</v>
       </c>
       <c r="B89">
-        <v>0.1262001456945401</v>
+        <v>0.08910822863352512</v>
       </c>
       <c r="C89">
-        <v>-6703.249417198605</v>
+        <v>-933.7774588472894</v>
       </c>
       <c r="D89">
-        <v>6742.135582801395</v>
+        <v>12511.60754115271</v>
       </c>
       <c r="E89">
         <v>5659.185000000001</v>
@@ -8591,45 +8591,45 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M89">
-        <v>2134.550498894</v>
+        <v>1290.116275394</v>
       </c>
       <c r="N89">
-        <v>-106.4171655606665</v>
+        <v>738.0170579393337</v>
       </c>
       <c r="O89">
-        <v>-28.73263470137995</v>
+        <v>199.2646056436201</v>
       </c>
       <c r="P89">
-        <v>-77.68453085928654</v>
+        <v>538.7524522957135</v>
       </c>
       <c r="Q89">
-        <v>741.5154691407133</v>
+        <v>1357.952452295713</v>
       </c>
       <c r="R89">
         <v>6.692307692307692</v>
       </c>
       <c r="S89">
-        <v>0.2777816597656219</v>
+        <v>0.2741908330103698</v>
       </c>
       <c r="T89">
-        <v>4.247085437073216</v>
+        <v>4.1830583141325</v>
       </c>
       <c r="U89">
-        <v>0.1392811058765187</v>
+        <v>0.08418110587651872</v>
       </c>
       <c r="V89">
-        <v>0.2565392574613402</v>
+        <v>0.27</v>
       </c>
       <c r="W89">
-        <v>0.1035500343965623</v>
+        <v>0.06145220728985867</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y89">
-        <v>0.9501453980049637</v>
+        <v>1.572054683764023</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8640,13 +8640,13 @@
         <v>0.88</v>
       </c>
       <c r="B90">
-        <v>0.1271349567533052</v>
+        <v>0.08915997331472766</v>
       </c>
       <c r="C90">
-        <v>-6956.894135692135</v>
+        <v>-1124.863490719679</v>
       </c>
       <c r="D90">
-        <v>6664.645864307865</v>
+        <v>12496.67650928032</v>
       </c>
       <c r="E90">
         <v>5835.34</v>
@@ -8673,45 +8673,45 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M90">
-        <v>2159.085562099678</v>
+        <v>1304.945198099678</v>
       </c>
       <c r="N90">
-        <v>-130.9522287663444</v>
+        <v>723.1881352336554</v>
       </c>
       <c r="O90">
-        <v>-35.357101766913</v>
+        <v>195.260796513087</v>
       </c>
       <c r="P90">
-        <v>-95.59512699943144</v>
+        <v>527.9273387205685</v>
       </c>
       <c r="Q90">
-        <v>723.6048730005684</v>
+        <v>1347.127338720568</v>
       </c>
       <c r="R90">
         <v>7.333333333333334</v>
       </c>
       <c r="S90">
-        <v>0.2971134647460905</v>
+        <v>0.2923502574971004</v>
       </c>
       <c r="T90">
-        <v>4.601009223495985</v>
+        <v>4.515654550933434</v>
       </c>
       <c r="U90">
-        <v>0.1392811058765187</v>
+        <v>0.08418110587651872</v>
       </c>
       <c r="V90">
-        <v>0.2536240386265523</v>
+        <v>0.27</v>
       </c>
       <c r="W90">
-        <v>0.1039560692997436</v>
+        <v>0.06145220728985867</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y90">
-        <v>0.9393482912094528</v>
+        <v>1.554190425993977</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8722,13 +8722,13 @@
         <v>0.89</v>
       </c>
       <c r="B91">
-        <v>0.1280697678120704</v>
+        <v>0.08921171799593022</v>
       </c>
       <c r="C91">
-        <v>-7208.777861108503</v>
+        <v>-1315.913928447457</v>
       </c>
       <c r="D91">
-        <v>6588.917138891497</v>
+        <v>12481.78107155254</v>
       </c>
       <c r="E91">
         <v>6011.495000000001</v>
@@ -8755,45 +8755,45 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M91">
-        <v>2183.620625305356</v>
+        <v>1319.774120805356</v>
       </c>
       <c r="N91">
-        <v>-155.4872919720228</v>
+        <v>708.3592125279774</v>
       </c>
       <c r="O91">
-        <v>-41.98156883244616</v>
+        <v>191.2569873825539</v>
       </c>
       <c r="P91">
-        <v>-113.5057231395767</v>
+        <v>517.1022251454235</v>
       </c>
       <c r="Q91">
-        <v>705.6942768604231</v>
+        <v>1336.302225145423</v>
       </c>
       <c r="R91">
         <v>8.090909090909092</v>
       </c>
       <c r="S91">
-        <v>0.3199601433593714</v>
+        <v>0.3138113955268729</v>
       </c>
       <c r="T91">
-        <v>5.019282789268347</v>
+        <v>4.908722830789082</v>
       </c>
       <c r="U91">
-        <v>0.1392811058765187</v>
+        <v>0.08418110587651872</v>
       </c>
       <c r="V91">
-        <v>0.2507743303273775</v>
+        <v>0.27</v>
       </c>
       <c r="W91">
-        <v>0.1043529798230782</v>
+        <v>0.06145220728985867</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y91">
-        <v>0.928793816027324</v>
+        <v>1.536727612218764</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8804,13 +8804,13 @@
         <v>0.9</v>
       </c>
       <c r="B92">
-        <v>0.1290045788708356</v>
+        <v>0.08926346267713277</v>
       </c>
       <c r="C92">
-        <v>-7458.959948202893</v>
+        <v>-1506.928899158611</v>
       </c>
       <c r="D92">
-        <v>6514.890051797108</v>
+        <v>12466.92110084139</v>
       </c>
       <c r="E92">
         <v>6187.650000000001</v>
@@ -8837,45 +8837,45 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M92">
-        <v>2208.155688511034</v>
+        <v>1334.603043511034</v>
       </c>
       <c r="N92">
-        <v>-180.0223551777012</v>
+        <v>693.5302898222992</v>
       </c>
       <c r="O92">
-        <v>-48.60603589797933</v>
+        <v>187.2531782520208</v>
       </c>
       <c r="P92">
-        <v>-131.4163192797219</v>
+        <v>506.2771115702784</v>
       </c>
       <c r="Q92">
-        <v>687.783680720278</v>
+        <v>1325.477111570278</v>
       </c>
       <c r="R92">
         <v>9.000000000000002</v>
       </c>
       <c r="S92">
-        <v>0.3473761576953086</v>
+        <v>0.3395647611625998</v>
       </c>
       <c r="T92">
-        <v>5.521211068195182</v>
+        <v>5.38040476661586</v>
       </c>
       <c r="U92">
-        <v>0.1392811058765187</v>
+        <v>0.08418110587651872</v>
       </c>
       <c r="V92">
-        <v>0.2479879488792955</v>
+        <v>0.27</v>
       </c>
       <c r="W92">
-        <v>0.1047410701125609</v>
+        <v>0.06145220728985867</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y92">
-        <v>0.9184738847381315</v>
+        <v>1.519652860971889</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8886,13 +8886,13 @@
         <v>0.91</v>
       </c>
       <c r="B93">
-        <v>0.1299393899296008</v>
+        <v>0.08931520735833531</v>
       </c>
       <c r="C93">
-        <v>-7707.497113941852</v>
+        <v>-1697.90852937646</v>
       </c>
       <c r="D93">
-        <v>6442.50788605815</v>
+        <v>12452.09647062354</v>
       </c>
       <c r="E93">
         <v>6363.805000000002</v>
@@ -8919,45 +8919,45 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M93">
-        <v>2232.690751716712</v>
+        <v>1349.431966216712</v>
       </c>
       <c r="N93">
-        <v>-204.5574183833792</v>
+        <v>678.701367116621</v>
       </c>
       <c r="O93">
-        <v>-55.23050296351238</v>
+        <v>183.2493691214877</v>
       </c>
       <c r="P93">
-        <v>-149.3269154198668</v>
+        <v>495.4519979951333</v>
       </c>
       <c r="Q93">
-        <v>669.8730845801331</v>
+        <v>1314.651997995133</v>
       </c>
       <c r="R93">
         <v>10.11111111111111</v>
       </c>
       <c r="S93">
-        <v>0.380884619661454</v>
+        <v>0.3710410969395994</v>
       </c>
       <c r="T93">
-        <v>6.134678964661314</v>
+        <v>5.956904910404145</v>
       </c>
       <c r="U93">
-        <v>0.1392811058765187</v>
+        <v>0.08418110587651872</v>
       </c>
       <c r="V93">
-        <v>0.2452628065839187</v>
+        <v>0.27</v>
       </c>
       <c r="W93">
-        <v>0.1051206309451318</v>
+        <v>0.06145220728985867</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y93">
-        <v>0.9083807651256246</v>
+        <v>1.502953378983187</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8968,13 +8968,13 @@
         <v>0.92</v>
       </c>
       <c r="B94">
-        <v>0.130874200988366</v>
+        <v>0.09890367203953787</v>
       </c>
       <c r="C94">
-        <v>-7954.443582425849</v>
+        <v>-4122.429463969554</v>
       </c>
       <c r="D94">
-        <v>6371.716417574152</v>
+        <v>10203.73053603045</v>
       </c>
       <c r="E94">
         <v>6539.960000000001</v>
@@ -9001,45 +9001,45 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M94">
-        <v>2257.22581492239</v>
+        <v>1594.38978092239</v>
       </c>
       <c r="N94">
-        <v>-229.0924815890571</v>
+        <v>433.7435524109428</v>
       </c>
       <c r="O94">
-        <v>-61.85497002904543</v>
+        <v>117.1107591509546</v>
       </c>
       <c r="P94">
-        <v>-167.2375115600117</v>
+        <v>316.6327932599883</v>
       </c>
       <c r="Q94">
-        <v>651.9624884399882</v>
+        <v>1135.832793259988</v>
       </c>
       <c r="R94">
         <v>11.50000000000001</v>
       </c>
       <c r="S94">
-        <v>0.4227701971191358</v>
+        <v>0.4103865166608489</v>
       </c>
       <c r="T94">
-        <v>6.90151383524398</v>
+        <v>6.677530090139501</v>
       </c>
       <c r="U94">
-        <v>0.1392811058765187</v>
+        <v>0.09838110587651873</v>
       </c>
       <c r="V94">
-        <v>0.2425969065123544</v>
+        <v>0.27</v>
       </c>
       <c r="W94">
-        <v>0.1054919404552556</v>
+        <v>0.07181820728985867</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y94">
-        <v>0.898507061156868</v>
+        <v>1.272043610415022</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9050,13 +9050,13 @@
         <v>0.93</v>
       </c>
       <c r="B95">
-        <v>0.1318090120471312</v>
+        <v>0.09905907672074042</v>
       </c>
       <c r="C95">
-        <v>-8199.851220361046</v>
+        <v>-4328.357933369767</v>
       </c>
       <c r="D95">
-        <v>6302.463779638954</v>
+        <v>10173.95706663023</v>
       </c>
       <c r="E95">
         <v>6716.115000000002</v>
@@ -9083,45 +9083,45 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M95">
-        <v>2281.760878128069</v>
+        <v>1611.720104628069</v>
       </c>
       <c r="N95">
-        <v>-253.6275447947355</v>
+        <v>416.4132287052646</v>
       </c>
       <c r="O95">
-        <v>-68.4794370945786</v>
+        <v>112.4315717504215</v>
       </c>
       <c r="P95">
-        <v>-185.1481077001569</v>
+        <v>303.9816569548432</v>
       </c>
       <c r="Q95">
-        <v>634.0518922998428</v>
+        <v>1123.181656954843</v>
       </c>
       <c r="R95">
         <v>13.2857142857143</v>
       </c>
       <c r="S95">
-        <v>0.4766230824218696</v>
+        <v>0.4609734848738839</v>
       </c>
       <c r="T95">
-        <v>7.887444383135978</v>
+        <v>7.604048178370673</v>
       </c>
       <c r="U95">
-        <v>0.1392811058765187</v>
+        <v>0.09838110587651873</v>
       </c>
       <c r="V95">
-        <v>0.2399883376251247</v>
+        <v>0.27</v>
       </c>
       <c r="W95">
-        <v>0.105855264814624</v>
+        <v>0.07181820728985867</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y95">
-        <v>0.8888456949078692</v>
+        <v>1.258365722130989</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9132,13 +9132,13 @@
         <v>0.9400000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1327438231058964</v>
+        <v>0.1203305086871819</v>
       </c>
       <c r="C96">
-        <v>-8443.769663791611</v>
+        <v>-7408.218266720613</v>
       </c>
       <c r="D96">
-        <v>6234.70033620839</v>
+        <v>7270.251733279388</v>
       </c>
       <c r="E96">
         <v>6892.27</v>
@@ -9165,37 +9165,37 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M96">
-        <v>2306.295941333747</v>
+        <v>2102.625530333747</v>
       </c>
       <c r="N96">
-        <v>-278.1626080004135</v>
+        <v>-74.4921970004134</v>
       </c>
       <c r="O96">
-        <v>-75.10390416011164</v>
+        <v>-20.11289319011162</v>
       </c>
       <c r="P96">
-        <v>-203.0587038403018</v>
+        <v>-54.37930381030178</v>
       </c>
       <c r="Q96">
-        <v>616.141296159698</v>
+        <v>764.8206961896981</v>
       </c>
       <c r="R96">
         <v>15.66666666666668</v>
       </c>
       <c r="S96">
-        <v>0.5484269294921812</v>
+        <v>0.5342383558469402</v>
       </c>
       <c r="T96">
-        <v>9.202018446991977</v>
+        <v>8.945920019802125</v>
       </c>
       <c r="U96">
-        <v>0.1392811058765187</v>
+        <v>0.1269811058765187</v>
       </c>
       <c r="V96">
-        <v>0.2374352702035809</v>
+        <v>0.2604343912408791</v>
       </c>
       <c r="W96">
-        <v>0.106210858868474</v>
+        <v>0.09391085886847396</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.879389889642892</v>
+        <v>0.9645718194106635</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9214,13 +9214,13 @@
         <v>0.9500000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1336786341646616</v>
+        <v>0.1211423197459471</v>
       </c>
       <c r="C97">
-        <v>-8686.246436743319</v>
+        <v>-7662.709994033823</v>
       </c>
       <c r="D97">
-        <v>6168.378563256683</v>
+        <v>7191.915005966179</v>
       </c>
       <c r="E97">
         <v>7068.425000000003</v>
@@ -9247,37 +9247,37 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M97">
-        <v>2330.831004539425</v>
+        <v>2124.993887039425</v>
       </c>
       <c r="N97">
-        <v>-302.6976712060919</v>
+        <v>-96.86055370609211</v>
       </c>
       <c r="O97">
-        <v>-81.72837122564481</v>
+        <v>-26.15234950064487</v>
       </c>
       <c r="P97">
-        <v>-220.969299980447</v>
+        <v>-70.70820420544723</v>
       </c>
       <c r="Q97">
-        <v>598.2307000195528</v>
+        <v>748.4917957945526</v>
       </c>
       <c r="R97">
         <v>19.00000000000003</v>
       </c>
       <c r="S97">
-        <v>0.6489523153906178</v>
+        <v>0.6319260270163285</v>
       </c>
       <c r="T97">
-        <v>11.04242213639038</v>
+        <v>10.73510402376255</v>
       </c>
       <c r="U97">
-        <v>0.1392811058765187</v>
+        <v>0.1269811058765187</v>
       </c>
       <c r="V97">
-        <v>0.2349359515698589</v>
+        <v>0.2576929765962382</v>
       </c>
       <c r="W97">
-        <v>0.1065589667317165</v>
+        <v>0.09425896673171653</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.8701331539624404</v>
+        <v>0.9544184318379194</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9296,13 +9296,13 @@
         <v>0.96</v>
       </c>
       <c r="B98">
-        <v>0.1346134452234267</v>
+        <v>0.1219541308047123</v>
       </c>
       <c r="C98">
-        <v>-8927.327062374394</v>
+        <v>-7915.53156581198</v>
       </c>
       <c r="D98">
-        <v>6103.452937625607</v>
+        <v>7115.248434188021</v>
       </c>
       <c r="E98">
         <v>7244.580000000002</v>
@@ -9329,37 +9329,37 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M98">
-        <v>2355.366067745103</v>
+        <v>2147.362243745103</v>
       </c>
       <c r="N98">
-        <v>-327.2327344117703</v>
+        <v>-119.2289104117699</v>
       </c>
       <c r="O98">
-        <v>-88.35283829117797</v>
+        <v>-32.19180581117788</v>
       </c>
       <c r="P98">
-        <v>-238.8798961205923</v>
+        <v>-87.03710460059202</v>
       </c>
       <c r="Q98">
-        <v>580.3201038794075</v>
+        <v>732.1628953994078</v>
       </c>
       <c r="R98">
         <v>23.99999999999998</v>
       </c>
       <c r="S98">
-        <v>0.7997403942382706</v>
+        <v>0.7784575337704089</v>
       </c>
       <c r="T98">
-        <v>13.80302767048794</v>
+        <v>13.41888002970316</v>
       </c>
       <c r="U98">
-        <v>0.1392811058765187</v>
+        <v>0.1269811058765187</v>
       </c>
       <c r="V98">
-        <v>0.2324887020743396</v>
+        <v>0.2550086747566942</v>
       </c>
       <c r="W98">
-        <v>0.1068998223478082</v>
+        <v>0.09459982234780821</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.8610692669419983</v>
+        <v>0.9444765731729413</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9378,13 +9378,13 @@
         <v>0.97</v>
       </c>
       <c r="B99">
-        <v>0.1355482562821919</v>
+        <v>0.1227659418634774</v>
       </c>
       <c r="C99">
-        <v>-9167.055167179968</v>
+        <v>-8166.735830784028</v>
       </c>
       <c r="D99">
-        <v>6039.879832820032</v>
+        <v>7040.199169215972</v>
       </c>
       <c r="E99">
         <v>7420.735000000001</v>
@@ -9411,37 +9411,37 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M99">
-        <v>2379.901130950781</v>
+        <v>2169.730600450781</v>
       </c>
       <c r="N99">
-        <v>-351.7677976174482</v>
+        <v>-141.5972671174482</v>
       </c>
       <c r="O99">
-        <v>-94.97730535671101</v>
+        <v>-38.231262121711</v>
       </c>
       <c r="P99">
-        <v>-256.7904922607372</v>
+        <v>-103.3660049957371</v>
       </c>
       <c r="Q99">
-        <v>562.4095077392626</v>
+        <v>715.8339950042626</v>
       </c>
       <c r="R99">
         <v>32.33333333333331</v>
       </c>
       <c r="S99">
-        <v>1.051053858984361</v>
+        <v>1.022676711693879</v>
       </c>
       <c r="T99">
-        <v>18.40403689398392</v>
+        <v>17.89184003960422</v>
       </c>
       <c r="U99">
-        <v>0.1392811058765187</v>
+        <v>0.1269811058765187</v>
       </c>
       <c r="V99">
-        <v>0.2300919113313051</v>
+        <v>0.2523797193468313</v>
       </c>
       <c r="W99">
-        <v>0.1072336500130527</v>
+        <v>0.09493365001305265</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.8521922641900189</v>
+        <v>0.9347397012845604</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9460,13 +9460,13 @@
         <v>0.98</v>
       </c>
       <c r="B100">
-        <v>0.1364830673409571</v>
+        <v>0.1235777529222426</v>
       </c>
       <c r="C100">
-        <v>-9405.472578751294</v>
+        <v>-8416.37343122882</v>
       </c>
       <c r="D100">
-        <v>5977.617421248704</v>
+        <v>6966.716568771179</v>
       </c>
       <c r="E100">
         <v>7596.889999999999</v>
@@ -9493,37 +9493,37 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M100">
-        <v>2404.436194156459</v>
+        <v>2192.098957156459</v>
       </c>
       <c r="N100">
-        <v>-376.3028608231261</v>
+        <v>-163.965623823126</v>
       </c>
       <c r="O100">
-        <v>-101.6017724222441</v>
+        <v>-44.27071843224401</v>
       </c>
       <c r="P100">
-        <v>-274.7010884008821</v>
+        <v>-119.6949053908819</v>
       </c>
       <c r="Q100">
-        <v>544.4989115991177</v>
+        <v>699.5050946091179</v>
       </c>
       <c r="R100">
         <v>48.99999999999996</v>
       </c>
       <c r="S100">
-        <v>1.553680788476542</v>
+        <v>1.511115067540818</v>
       </c>
       <c r="T100">
-        <v>27.60605534097589</v>
+        <v>26.83776005940632</v>
       </c>
       <c r="U100">
-        <v>0.1392811058765187</v>
+        <v>0.1269811058765187</v>
       </c>
       <c r="V100">
-        <v>0.2277440346850673</v>
+        <v>0.2498044160881902</v>
       </c>
       <c r="W100">
-        <v>0.1075606648688023</v>
+        <v>0.0952606648688023</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9531,7 +9531,7 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.8434964247595087</v>
+        <v>0.9252015410673712</v>
       </c>
       <c r="Z100">
         <v>0</v>
@@ -9542,13 +9542,13 @@
         <v>0.99</v>
       </c>
       <c r="B101">
-        <v>0.1374178783997223</v>
+        <v>0.1243895639810078</v>
       </c>
       <c r="C101">
-        <v>-9642.61941755017</v>
+        <v>-8664.492916935578</v>
       </c>
       <c r="D101">
-        <v>5916.625582449831</v>
+        <v>6894.752083064423</v>
       </c>
       <c r="E101">
         <v>7773.045000000002</v>
@@ -9575,37 +9575,37 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M101">
-        <v>2428.971257362138</v>
+        <v>2214.467313862138</v>
       </c>
       <c r="N101">
-        <v>-400.8379240288045</v>
+        <v>-186.3339805288047</v>
       </c>
       <c r="O101">
-        <v>-108.2262394877772</v>
+        <v>-50.31017474277726</v>
       </c>
       <c r="P101">
-        <v>-292.6116845410273</v>
+        <v>-136.0238057860274</v>
       </c>
       <c r="Q101">
-        <v>526.5883154589725</v>
+        <v>683.1761942139724</v>
       </c>
       <c r="R101">
         <v>98.99999999999991</v>
       </c>
       <c r="S101">
-        <v>3.061561576953082</v>
+        <v>2.976430135081636</v>
       </c>
       <c r="T101">
-        <v>55.21211068195176</v>
+        <v>53.67552011881265</v>
       </c>
       <c r="U101">
-        <v>0.1392811058765187</v>
+        <v>0.1269811058765187</v>
       </c>
       <c r="V101">
-        <v>0.2254435898902687</v>
+        <v>0.2472811391580064</v>
       </c>
       <c r="W101">
-        <v>0.1078810733638298</v>
+        <v>0.09558107336382976</v>
       </c>
       <c r="X101" t="inlineStr">
         <is>
@@ -9613,7 +9613,7 @@
         </is>
       </c>
       <c r="Y101">
-        <v>0.8349762588528469</v>
+        <v>0.9158560709555793</v>
       </c>
       <c r="Z101">
         <v>0</v>

--- a/research/traditional_assets/database/data/chile/chile_retail_automotive.xlsx
+++ b/research/traditional_assets/database/data/chile/chile_retail_automotive.xlsx
@@ -1284,7 +1284,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1421,22 +1421,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08460644136890352</v>
+        <v>0.08447203605010607</v>
       </c>
       <c r="C2">
-        <v>15843.1314156912</v>
+        <v>15715.50516877711</v>
       </c>
       <c r="D2">
-        <v>13963.0314156912</v>
+        <v>14011.56016877711</v>
       </c>
       <c r="E2">
-        <v>-9666.299999999999</v>
+        <v>-9490.144999999999</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>176.155</v>
       </c>
       <c r="G2">
         <v>1880.1</v>
@@ -1457,28 +1457,28 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>10.33697020567816</v>
       </c>
       <c r="N2">
-        <v>2028.133333333333</v>
+        <v>2017.796363127655</v>
       </c>
       <c r="O2">
-        <v>547.596</v>
+        <v>544.8050180444669</v>
       </c>
       <c r="P2">
-        <v>1480.537333333333</v>
+        <v>1472.991345083188</v>
       </c>
       <c r="Q2">
-        <v>2299.737333333333</v>
+        <v>2292.191345083188</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08460644136890352</v>
+        <v>0.08489258987596716</v>
       </c>
       <c r="T2">
-        <v>0.7107536019307608</v>
+        <v>0.7159945123288362</v>
       </c>
       <c r="U2">
         <v>0.05868110587651873</v>
@@ -1495,7 +1495,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>196.20191342133</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1503,22 +1503,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08447203605010607</v>
+        <v>0.08433763073130862</v>
       </c>
       <c r="C3">
-        <v>15715.50516877711</v>
+        <v>15588.21742334355</v>
       </c>
       <c r="D3">
-        <v>14011.56016877711</v>
+        <v>14060.42742334354</v>
       </c>
       <c r="E3">
-        <v>-9490.144999999999</v>
+        <v>-9313.99</v>
       </c>
       <c r="F3">
-        <v>176.155</v>
+        <v>352.31</v>
       </c>
       <c r="G3">
         <v>1880.1</v>
@@ -1539,28 +1539,28 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M3">
-        <v>10.33697020567816</v>
+        <v>20.67394041135631</v>
       </c>
       <c r="N3">
-        <v>2017.796363127655</v>
+        <v>2007.459392921977</v>
       </c>
       <c r="O3">
-        <v>544.8050180444669</v>
+        <v>542.0140360889337</v>
       </c>
       <c r="P3">
-        <v>1472.991345083188</v>
+        <v>1465.445356833043</v>
       </c>
       <c r="Q3">
-        <v>2292.191345083188</v>
+        <v>2284.645356833043</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08489258987596716</v>
+        <v>0.08518457814848107</v>
       </c>
       <c r="T3">
-        <v>0.7159945123288362</v>
+        <v>0.7213423800819742</v>
       </c>
       <c r="U3">
         <v>0.05868110587651873</v>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>196.20191342133</v>
+        <v>98.10095671066499</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1585,22 +1585,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08433763073130862</v>
+        <v>0.08420322541251116</v>
       </c>
       <c r="C4">
-        <v>15588.21742334355</v>
+        <v>15461.27173349819</v>
       </c>
       <c r="D4">
-        <v>14060.42742334354</v>
+        <v>14109.63673349819</v>
       </c>
       <c r="E4">
-        <v>-9313.99</v>
+        <v>-9137.834999999999</v>
       </c>
       <c r="F4">
-        <v>352.31</v>
+        <v>528.465</v>
       </c>
       <c r="G4">
         <v>1880.1</v>
@@ -1621,28 +1621,28 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M4">
-        <v>20.67394041135631</v>
+        <v>31.01091061703447</v>
       </c>
       <c r="N4">
-        <v>2007.459392921977</v>
+        <v>1997.122422716299</v>
       </c>
       <c r="O4">
-        <v>542.0140360889337</v>
+        <v>539.2230541334008</v>
       </c>
       <c r="P4">
-        <v>1465.445356833043</v>
+        <v>1457.899368582898</v>
       </c>
       <c r="Q4">
-        <v>2284.645356833043</v>
+        <v>2277.099368582898</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08518457814848107</v>
+        <v>0.08548258679774784</v>
       </c>
       <c r="T4">
-        <v>0.7213423800819742</v>
+        <v>0.7268005131496099</v>
       </c>
       <c r="U4">
         <v>0.05868110587651873</v>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>98.10095671066499</v>
+        <v>65.40063780710999</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1667,22 +1667,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08420322541251116</v>
+        <v>0.08406882009371372</v>
       </c>
       <c r="C5">
-        <v>15461.27173349819</v>
+        <v>15334.67170327876</v>
       </c>
       <c r="D5">
-        <v>14109.63673349819</v>
+        <v>14159.19170327876</v>
       </c>
       <c r="E5">
-        <v>-9137.834999999999</v>
+        <v>-8961.679999999998</v>
       </c>
       <c r="F5">
-        <v>528.465</v>
+        <v>704.62</v>
       </c>
       <c r="G5">
         <v>1880.1</v>
@@ -1703,28 +1703,28 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M5">
-        <v>31.01091061703447</v>
+        <v>41.34788082271263</v>
       </c>
       <c r="N5">
-        <v>1997.122422716299</v>
+        <v>1986.785452510621</v>
       </c>
       <c r="O5">
-        <v>539.2230541334008</v>
+        <v>536.4320721778676</v>
       </c>
       <c r="P5">
-        <v>1457.899368582898</v>
+        <v>1450.353380332753</v>
       </c>
       <c r="Q5">
-        <v>2277.099368582898</v>
+        <v>2269.553380332753</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08548258679774784</v>
+        <v>0.08578680396054102</v>
       </c>
       <c r="T5">
-        <v>0.7268005131496099</v>
+        <v>0.7323723573228215</v>
       </c>
       <c r="U5">
         <v>0.05868110587651873</v>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>65.40063780710999</v>
+        <v>49.05047835533249</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1749,22 +1749,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08406882009371372</v>
+        <v>0.08393441477491626</v>
       </c>
       <c r="C6">
-        <v>15334.67170327876</v>
+        <v>15208.42098753292</v>
       </c>
       <c r="D6">
-        <v>14159.19170327876</v>
+        <v>14209.09598753292</v>
       </c>
       <c r="E6">
-        <v>-8961.679999999998</v>
+        <v>-8785.525</v>
       </c>
       <c r="F6">
-        <v>704.62</v>
+        <v>880.7750000000001</v>
       </c>
       <c r="G6">
         <v>1880.1</v>
@@ -1785,28 +1785,28 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M6">
-        <v>41.34788082271263</v>
+        <v>51.68485102839079</v>
       </c>
       <c r="N6">
-        <v>1986.785452510621</v>
+        <v>1976.448482304942</v>
       </c>
       <c r="O6">
-        <v>536.4320721778676</v>
+        <v>533.6410902223345</v>
       </c>
       <c r="P6">
-        <v>1450.353380332753</v>
+        <v>1442.807392082608</v>
       </c>
       <c r="Q6">
-        <v>2269.553380332753</v>
+        <v>2262.007392082608</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08578680396054102</v>
+        <v>0.08609742569518244</v>
       </c>
       <c r="T6">
-        <v>0.7323723573228215</v>
+        <v>0.7380615034786268</v>
       </c>
       <c r="U6">
         <v>0.05868110587651873</v>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>49.05047835533249</v>
+        <v>39.240382684266</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1831,22 +1831,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08393441477491626</v>
+        <v>0.0838000094561188</v>
       </c>
       <c r="C7">
-        <v>15208.42098753292</v>
+        <v>15082.52329281684</v>
       </c>
       <c r="D7">
-        <v>14209.09598753292</v>
+        <v>14259.35329281684</v>
       </c>
       <c r="E7">
-        <v>-8785.525</v>
+        <v>-8609.369999999999</v>
       </c>
       <c r="F7">
-        <v>880.7750000000001</v>
+        <v>1056.93</v>
       </c>
       <c r="G7">
         <v>1880.1</v>
@@ -1867,28 +1867,28 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M7">
-        <v>51.68485102839079</v>
+        <v>62.02182123406894</v>
       </c>
       <c r="N7">
-        <v>1976.448482304942</v>
+        <v>1966.111512099264</v>
       </c>
       <c r="O7">
-        <v>533.6410902223345</v>
+        <v>530.8501082668014</v>
       </c>
       <c r="P7">
-        <v>1442.807392082608</v>
+        <v>1435.261403832463</v>
       </c>
       <c r="Q7">
-        <v>2262.007392082608</v>
+        <v>2254.461403832463</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.08609742569518244</v>
+        <v>0.08641465640290137</v>
       </c>
       <c r="T7">
-        <v>0.7380615034786268</v>
+        <v>0.7438716952973218</v>
       </c>
       <c r="U7">
         <v>0.05868110587651873</v>
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>39.240382684266</v>
+        <v>32.70031890355499</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1913,22 +1913,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.0838000094561188</v>
+        <v>0.08366560413732137</v>
       </c>
       <c r="C8">
-        <v>15082.52329281684</v>
+        <v>14956.9823783129</v>
       </c>
       <c r="D8">
-        <v>14259.35329281684</v>
+        <v>14309.9673783129</v>
       </c>
       <c r="E8">
-        <v>-8609.369999999999</v>
+        <v>-8433.215</v>
       </c>
       <c r="F8">
-        <v>1056.93</v>
+        <v>1233.085</v>
       </c>
       <c r="G8">
         <v>1880.1</v>
@@ -1949,28 +1949,28 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M8">
-        <v>62.02182123406894</v>
+        <v>72.35879143974709</v>
       </c>
       <c r="N8">
-        <v>1966.111512099264</v>
+        <v>1955.774541893586</v>
       </c>
       <c r="O8">
-        <v>530.8501082668014</v>
+        <v>528.0591263112683</v>
       </c>
       <c r="P8">
-        <v>1435.261403832463</v>
+        <v>1427.715415582318</v>
       </c>
       <c r="Q8">
-        <v>2254.461403832463</v>
+        <v>2246.915415582318</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.08641465640290137</v>
+        <v>0.0867387092763777</v>
       </c>
       <c r="T8">
-        <v>0.7438716952973218</v>
+        <v>0.749806837477709</v>
       </c>
       <c r="U8">
         <v>0.05868110587651873</v>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>32.70031890355499</v>
+        <v>28.02884477447571</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1995,22 +1995,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08366560413732135</v>
+        <v>0.08353119881852392</v>
       </c>
       <c r="C9">
-        <v>14956.9823783129</v>
+        <v>14831.80205676704</v>
       </c>
       <c r="D9">
-        <v>14309.9673783129</v>
+        <v>14360.94205676703</v>
       </c>
       <c r="E9">
-        <v>-8433.215</v>
+        <v>-8257.059999999999</v>
       </c>
       <c r="F9">
-        <v>1233.085</v>
+        <v>1409.24</v>
       </c>
       <c r="G9">
         <v>1880.1</v>
@@ -2031,28 +2031,28 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M9">
-        <v>72.35879143974709</v>
+        <v>82.69576164542525</v>
       </c>
       <c r="N9">
-        <v>1955.774541893586</v>
+        <v>1945.437571687908</v>
       </c>
       <c r="O9">
-        <v>528.0591263112683</v>
+        <v>525.2681443557352</v>
       </c>
       <c r="P9">
-        <v>1427.715415582318</v>
+        <v>1420.169427332173</v>
       </c>
       <c r="Q9">
-        <v>2246.915415582318</v>
+        <v>2239.369427332173</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.0867387092763777</v>
+        <v>0.08706980677753828</v>
       </c>
       <c r="T9">
-        <v>0.749806837477709</v>
+        <v>0.7558710044881047</v>
       </c>
       <c r="U9">
         <v>0.05868110587651873</v>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>28.02884477447571</v>
+        <v>24.52523917766625</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2077,22 +2077,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08353119881852392</v>
+        <v>0.08339679349972645</v>
       </c>
       <c r="C10">
-        <v>14831.80205676704</v>
+        <v>14706.98619544613</v>
       </c>
       <c r="D10">
-        <v>14360.94205676703</v>
+        <v>14412.28119544613</v>
       </c>
       <c r="E10">
-        <v>-8257.059999999999</v>
+        <v>-8080.904999999999</v>
       </c>
       <c r="F10">
-        <v>1409.24</v>
+        <v>1585.395</v>
       </c>
       <c r="G10">
         <v>1880.1</v>
@@ -2113,28 +2113,28 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M10">
-        <v>82.69576164542525</v>
+        <v>93.03273185110341</v>
       </c>
       <c r="N10">
-        <v>1945.437571687908</v>
+        <v>1935.10060148223</v>
       </c>
       <c r="O10">
-        <v>525.2681443557352</v>
+        <v>522.4771624002021</v>
       </c>
       <c r="P10">
-        <v>1420.169427332173</v>
+        <v>1412.623439082028</v>
       </c>
       <c r="Q10">
-        <v>2239.369427332173</v>
+        <v>2231.823439082028</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.08706980677753828</v>
+        <v>0.08740818114685624</v>
       </c>
       <c r="T10">
-        <v>0.7558710044881047</v>
+        <v>0.7620684498943333</v>
       </c>
       <c r="U10">
         <v>0.05868110587651873</v>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>24.52523917766625</v>
+        <v>21.80021260237</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08339679349972645</v>
+        <v>0.083262388180929</v>
       </c>
       <c r="C11">
-        <v>14706.98619544613</v>
+        <v>14582.53871711605</v>
       </c>
       <c r="D11">
-        <v>14412.28119544613</v>
+        <v>14463.98871711605</v>
       </c>
       <c r="E11">
-        <v>-8080.904999999999</v>
+        <v>-7904.749999999999</v>
       </c>
       <c r="F11">
-        <v>1585.395</v>
+        <v>1761.55</v>
       </c>
       <c r="G11">
         <v>1880.1</v>
@@ -2195,28 +2195,28 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M11">
-        <v>93.03273185110341</v>
+        <v>103.3697020567816</v>
       </c>
       <c r="N11">
-        <v>1935.10060148223</v>
+        <v>1924.763631276552</v>
       </c>
       <c r="O11">
-        <v>522.4771624002021</v>
+        <v>519.6861804446689</v>
       </c>
       <c r="P11">
-        <v>1412.623439082028</v>
+        <v>1405.077450831883</v>
       </c>
       <c r="Q11">
-        <v>2231.823439082028</v>
+        <v>2224.277450831883</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.08740818114685624</v>
+        <v>0.08775407494660348</v>
       </c>
       <c r="T11">
-        <v>0.7620684498943333</v>
+        <v>0.7684036163095892</v>
       </c>
       <c r="U11">
         <v>0.05868110587651873</v>
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>21.80021260237</v>
+        <v>19.620191342133</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2241,22 +2241,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.083262388180929</v>
+        <v>0.08312798286213155</v>
       </c>
       <c r="C12">
-        <v>14582.53871711605</v>
+        <v>14458.46360104085</v>
       </c>
       <c r="D12">
-        <v>14463.98871711605</v>
+        <v>14516.06860104085</v>
       </c>
       <c r="E12">
-        <v>-7904.749999999999</v>
+        <v>-7728.594999999999</v>
       </c>
       <c r="F12">
-        <v>1761.55</v>
+        <v>1937.705</v>
       </c>
       <c r="G12">
         <v>1880.1</v>
@@ -2277,28 +2277,28 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M12">
-        <v>103.3697020567816</v>
+        <v>113.7066722624597</v>
       </c>
       <c r="N12">
-        <v>1924.763631276552</v>
+        <v>1914.426661070873</v>
       </c>
       <c r="O12">
-        <v>519.6861804446689</v>
+        <v>516.8951984891359</v>
       </c>
       <c r="P12">
-        <v>1405.077450831883</v>
+        <v>1397.531462581738</v>
       </c>
       <c r="Q12">
-        <v>2224.277450831883</v>
+        <v>2216.731462581738</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.08775407494660348</v>
+        <v>0.08810774164072707</v>
       </c>
       <c r="T12">
-        <v>0.7684036163095892</v>
+        <v>0.7748811460150755</v>
       </c>
       <c r="U12">
         <v>0.05868110587651873</v>
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>19.620191342133</v>
+        <v>17.83653758375727</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2323,22 +2323,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08312798286213155</v>
+        <v>0.08299357754333408</v>
       </c>
       <c r="C13">
-        <v>14458.46360104085</v>
+        <v>14334.76488400356</v>
       </c>
       <c r="D13">
-        <v>14516.06860104085</v>
+        <v>14568.52488400356</v>
       </c>
       <c r="E13">
-        <v>-7728.594999999999</v>
+        <v>-7552.439999999999</v>
       </c>
       <c r="F13">
-        <v>1937.705</v>
+        <v>2113.86</v>
       </c>
       <c r="G13">
         <v>1880.1</v>
@@ -2359,28 +2359,28 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M13">
-        <v>113.7066722624597</v>
+        <v>124.0436424681379</v>
       </c>
       <c r="N13">
-        <v>1914.426661070873</v>
+        <v>1904.089690865195</v>
       </c>
       <c r="O13">
-        <v>516.8951984891359</v>
+        <v>514.1042165336028</v>
       </c>
       <c r="P13">
-        <v>1397.531462581738</v>
+        <v>1389.985474331593</v>
       </c>
       <c r="Q13">
-        <v>2216.731462581738</v>
+        <v>2209.185474331593</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.08810774164072707</v>
+        <v>0.08846944621426256</v>
       </c>
       <c r="T13">
-        <v>0.7748811460150755</v>
+        <v>0.7815058923047774</v>
       </c>
       <c r="U13">
         <v>0.05868110587651873</v>
@@ -2397,7 +2397,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>17.83653758375727</v>
+        <v>16.3501594517775</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2405,22 +2405,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08299357754333408</v>
+        <v>0.08285917222453663</v>
       </c>
       <c r="C14">
-        <v>14334.76488400356</v>
+        <v>14211.44666134924</v>
       </c>
       <c r="D14">
-        <v>14568.52488400356</v>
+        <v>14621.36166134924</v>
       </c>
       <c r="E14">
-        <v>-7552.439999999999</v>
+        <v>-7376.285</v>
       </c>
       <c r="F14">
-        <v>2113.86</v>
+        <v>2290.015</v>
       </c>
       <c r="G14">
         <v>1880.1</v>
@@ -2441,28 +2441,28 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M14">
-        <v>124.0436424681379</v>
+        <v>134.380612673816</v>
       </c>
       <c r="N14">
-        <v>1904.089690865195</v>
+        <v>1893.752720659517</v>
       </c>
       <c r="O14">
-        <v>514.1042165336028</v>
+        <v>511.3132345780696</v>
       </c>
       <c r="P14">
-        <v>1389.985474331593</v>
+        <v>1382.439486081448</v>
       </c>
       <c r="Q14">
-        <v>2209.185474331593</v>
+        <v>2201.639486081447</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.08846944621426256</v>
+        <v>0.08883946583546554</v>
       </c>
       <c r="T14">
-        <v>0.7815058923047774</v>
+        <v>0.7882829316126334</v>
       </c>
       <c r="U14">
         <v>0.05868110587651873</v>
@@ -2479,7 +2479,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>16.3501594517775</v>
+        <v>15.09245487856384</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2487,22 +2487,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08285917222453663</v>
+        <v>0.08272476690573918</v>
       </c>
       <c r="C15">
-        <v>14211.44666134924</v>
+        <v>14088.51308805082</v>
       </c>
       <c r="D15">
-        <v>14621.36166134924</v>
+        <v>14674.58308805082</v>
       </c>
       <c r="E15">
-        <v>-7376.285</v>
+        <v>-7200.129999999999</v>
       </c>
       <c r="F15">
-        <v>2290.015</v>
+        <v>2466.17</v>
       </c>
       <c r="G15">
         <v>1880.1</v>
@@ -2523,28 +2523,28 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M15">
-        <v>134.380612673816</v>
+        <v>144.7175828794942</v>
       </c>
       <c r="N15">
-        <v>1893.752720659517</v>
+        <v>1883.415750453839</v>
       </c>
       <c r="O15">
-        <v>511.3132345780696</v>
+        <v>508.5222526225366</v>
       </c>
       <c r="P15">
-        <v>1382.439486081448</v>
+        <v>1374.893497831303</v>
       </c>
       <c r="Q15">
-        <v>2201.639486081447</v>
+        <v>2194.093497831303</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.08883946583546554</v>
+        <v>0.08921809056413835</v>
       </c>
       <c r="T15">
-        <v>0.7882829316126334</v>
+        <v>0.7952175764857884</v>
       </c>
       <c r="U15">
         <v>0.05868110587651873</v>
@@ -2561,7 +2561,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>15.09245487856384</v>
+        <v>14.01442238723786</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2569,22 +2569,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.08272476690573918</v>
+        <v>0.08259036158694175</v>
       </c>
       <c r="C16">
-        <v>14088.51308805082</v>
+        <v>13965.96837979823</v>
       </c>
       <c r="D16">
-        <v>14674.58308805082</v>
+        <v>14728.19337979823</v>
       </c>
       <c r="E16">
-        <v>-7200.129999999999</v>
+        <v>-7023.974999999999</v>
       </c>
       <c r="F16">
-        <v>2466.17</v>
+        <v>2642.325</v>
       </c>
       <c r="G16">
         <v>1880.1</v>
@@ -2605,28 +2605,28 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M16">
-        <v>144.7175828794942</v>
+        <v>155.0545530851724</v>
       </c>
       <c r="N16">
-        <v>1883.415750453839</v>
+        <v>1873.078780248161</v>
       </c>
       <c r="O16">
-        <v>508.5222526225366</v>
+        <v>505.7312706670035</v>
       </c>
       <c r="P16">
-        <v>1374.893497831303</v>
+        <v>1367.347509581158</v>
       </c>
       <c r="Q16">
-        <v>2194.093497831303</v>
+        <v>2186.547509581157</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.08921809056413835</v>
+        <v>0.0896056241099564</v>
       </c>
       <c r="T16">
-        <v>0.7952175764857884</v>
+        <v>0.8023153894736059</v>
       </c>
       <c r="U16">
         <v>0.05868110587651873</v>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>14.01442238723786</v>
+        <v>13.080127561422</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2651,22 +2651,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.08259036158694175</v>
+        <v>0.08245595626814428</v>
       </c>
       <c r="C17">
-        <v>13965.96837979823</v>
+        <v>13843.81681411166</v>
       </c>
       <c r="D17">
-        <v>14728.19337979823</v>
+        <v>14782.19681411166</v>
       </c>
       <c r="E17">
-        <v>-7023.974999999999</v>
+        <v>-6847.82</v>
       </c>
       <c r="F17">
-        <v>2642.325</v>
+        <v>2818.48</v>
       </c>
       <c r="G17">
         <v>1880.1</v>
@@ -2687,28 +2687,28 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M17">
-        <v>155.0545530851723</v>
+        <v>165.3915232908505</v>
       </c>
       <c r="N17">
-        <v>1873.078780248161</v>
+        <v>1862.741810042483</v>
       </c>
       <c r="O17">
-        <v>505.7312706670035</v>
+        <v>502.9402887114704</v>
       </c>
       <c r="P17">
-        <v>1367.347509581158</v>
+        <v>1359.801521331012</v>
       </c>
       <c r="Q17">
-        <v>2186.547509581157</v>
+        <v>2179.001521331012</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.0896056241099564</v>
+        <v>0.09000238464496059</v>
       </c>
       <c r="T17">
-        <v>0.8023153894736059</v>
+        <v>0.8095821980087523</v>
       </c>
       <c r="U17">
         <v>0.05868110587651873</v>
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>13.080127561422</v>
+        <v>12.26261958883312</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2733,22 +2733,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.08245595626814428</v>
+        <v>0.08232155094934683</v>
       </c>
       <c r="C18">
-        <v>13843.81681411166</v>
+        <v>13722.06273147913</v>
       </c>
       <c r="D18">
-        <v>14782.19681411166</v>
+        <v>14836.59773147913</v>
       </c>
       <c r="E18">
-        <v>-6847.82</v>
+        <v>-6671.664999999999</v>
       </c>
       <c r="F18">
-        <v>2818.48</v>
+        <v>2994.635</v>
       </c>
       <c r="G18">
         <v>1880.1</v>
@@ -2769,28 +2769,28 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M18">
-        <v>165.3915232908505</v>
+        <v>175.7284934965287</v>
       </c>
       <c r="N18">
-        <v>1862.741810042483</v>
+        <v>1852.404839836805</v>
       </c>
       <c r="O18">
-        <v>502.9402887114704</v>
+        <v>500.1493067559372</v>
       </c>
       <c r="P18">
-        <v>1359.801521331012</v>
+        <v>1352.255533080867</v>
       </c>
       <c r="Q18">
-        <v>2179.001521331012</v>
+        <v>2171.455533080867</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.09000238464496059</v>
+        <v>0.09040870567478416</v>
       </c>
       <c r="T18">
-        <v>0.8095821980087523</v>
+        <v>0.8170241103640228</v>
       </c>
       <c r="U18">
         <v>0.05868110587651873</v>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>12.26261958883312</v>
+        <v>11.54128902478412</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2815,22 +2815,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.08232155094934683</v>
+        <v>0.08218714563054938</v>
       </c>
       <c r="C19">
-        <v>13722.06273147913</v>
+        <v>13600.71053651957</v>
       </c>
       <c r="D19">
-        <v>14836.59773147913</v>
+        <v>14891.40053651957</v>
       </c>
       <c r="E19">
-        <v>-6671.664999999999</v>
+        <v>-6495.509999999998</v>
       </c>
       <c r="F19">
-        <v>2994.635</v>
+        <v>3170.79</v>
       </c>
       <c r="G19">
         <v>1880.1</v>
@@ -2851,28 +2851,28 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M19">
-        <v>175.7284934965287</v>
+        <v>186.0654637022068</v>
       </c>
       <c r="N19">
-        <v>1852.404839836805</v>
+        <v>1842.067869631126</v>
       </c>
       <c r="O19">
-        <v>500.1493067559372</v>
+        <v>497.3583248004041</v>
       </c>
       <c r="P19">
-        <v>1352.255533080867</v>
+        <v>1344.709544830722</v>
       </c>
       <c r="Q19">
-        <v>2171.455533080867</v>
+        <v>2163.909544830722</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.09040870567478416</v>
+        <v>0.09082493697362783</v>
       </c>
       <c r="T19">
-        <v>0.8170241103640228</v>
+        <v>0.8246475327767387</v>
       </c>
       <c r="U19">
         <v>0.05868110587651873</v>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>11.54128902478412</v>
+        <v>10.900106301185</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2897,22 +2897,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.08218714563054939</v>
+        <v>0.08205274031175194</v>
       </c>
       <c r="C20">
-        <v>13600.71053651956</v>
+        <v>13479.76469917154</v>
       </c>
       <c r="D20">
-        <v>14891.40053651956</v>
+        <v>14946.60969917154</v>
       </c>
       <c r="E20">
-        <v>-6495.509999999999</v>
+        <v>-6319.355</v>
       </c>
       <c r="F20">
-        <v>3170.79</v>
+        <v>3346.945</v>
       </c>
       <c r="G20">
         <v>1880.1</v>
@@ -2933,28 +2933,28 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M20">
-        <v>186.0654637022068</v>
+        <v>196.402433907885</v>
       </c>
       <c r="N20">
-        <v>1842.067869631126</v>
+        <v>1831.730899425448</v>
       </c>
       <c r="O20">
-        <v>497.3583248004041</v>
+        <v>494.567342844871</v>
       </c>
       <c r="P20">
-        <v>1344.709544830722</v>
+        <v>1337.163556580577</v>
       </c>
       <c r="Q20">
-        <v>2163.909544830722</v>
+        <v>2156.363556580577</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.09082493697362783</v>
+        <v>0.09125144558849232</v>
       </c>
       <c r="T20">
-        <v>0.8246475327767387</v>
+        <v>0.8324591878416207</v>
       </c>
       <c r="U20">
         <v>0.05868110587651873</v>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>10.900106301185</v>
+        <v>10.32641649585947</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2979,22 +2979,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.08205274031175194</v>
+        <v>0.08191833499295448</v>
       </c>
       <c r="C21">
-        <v>13479.76469917154</v>
+        <v>13359.22975590866</v>
       </c>
       <c r="D21">
-        <v>14946.60969917154</v>
+        <v>15002.22975590866</v>
       </c>
       <c r="E21">
-        <v>-6319.355</v>
+        <v>-6143.199999999999</v>
       </c>
       <c r="F21">
-        <v>3346.945</v>
+        <v>3523.1</v>
       </c>
       <c r="G21">
         <v>1880.1</v>
@@ -3015,28 +3015,28 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M21">
-        <v>196.402433907885</v>
+        <v>206.7394041135632</v>
       </c>
       <c r="N21">
-        <v>1831.730899425448</v>
+        <v>1821.39392921977</v>
       </c>
       <c r="O21">
-        <v>494.567342844871</v>
+        <v>491.776360889338</v>
       </c>
       <c r="P21">
-        <v>1337.163556580577</v>
+        <v>1329.617568330432</v>
       </c>
       <c r="Q21">
-        <v>2156.363556580577</v>
+        <v>2148.817568330432</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.09125144558849232</v>
+        <v>0.09168861691872843</v>
       </c>
       <c r="T21">
-        <v>0.8324591878416207</v>
+        <v>0.8404661342831247</v>
       </c>
       <c r="U21">
         <v>0.05868110587651873</v>
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>10.32641649585947</v>
+        <v>9.810095671066499</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3061,22 +3061,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.08191833499295448</v>
+        <v>0.08178392967415703</v>
       </c>
       <c r="C22">
-        <v>13359.22975590866</v>
+        <v>13239.11031098211</v>
       </c>
       <c r="D22">
-        <v>15002.22975590866</v>
+        <v>15058.26531098211</v>
       </c>
       <c r="E22">
-        <v>-6143.199999999999</v>
+        <v>-5967.044999999998</v>
       </c>
       <c r="F22">
-        <v>3523.1</v>
+        <v>3699.255000000001</v>
       </c>
       <c r="G22">
         <v>1880.1</v>
@@ -3097,28 +3097,28 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M22">
-        <v>206.7394041135632</v>
+        <v>217.0763743192413</v>
       </c>
       <c r="N22">
-        <v>1821.39392921977</v>
+        <v>1811.056959014092</v>
       </c>
       <c r="O22">
-        <v>491.776360889338</v>
+        <v>488.9853789338048</v>
       </c>
       <c r="P22">
-        <v>1329.617568330432</v>
+        <v>1322.071580080287</v>
       </c>
       <c r="Q22">
-        <v>2148.817568330432</v>
+        <v>2141.271580080287</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.09168861691872843</v>
+        <v>0.0921368558775781</v>
       </c>
       <c r="T22">
-        <v>0.8404661342831247</v>
+        <v>0.8486757882294768</v>
       </c>
       <c r="U22">
         <v>0.05868110587651873</v>
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>9.810095671066499</v>
+        <v>9.34294825815857</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3143,22 +3143,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.08178392967415703</v>
+        <v>0.08164952435535958</v>
       </c>
       <c r="C23">
-        <v>13239.11031098211</v>
+        <v>13119.41103769126</v>
       </c>
       <c r="D23">
-        <v>15058.26531098211</v>
+        <v>15114.72103769126</v>
       </c>
       <c r="E23">
-        <v>-5967.045</v>
+        <v>-5790.889999999999</v>
       </c>
       <c r="F23">
-        <v>3699.255</v>
+        <v>3875.41</v>
       </c>
       <c r="G23">
         <v>1880.1</v>
@@ -3179,28 +3179,28 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M23">
-        <v>217.0763743192413</v>
+        <v>227.4133445249194</v>
       </c>
       <c r="N23">
-        <v>1811.056959014092</v>
+        <v>1800.719988808414</v>
       </c>
       <c r="O23">
-        <v>488.9853789338048</v>
+        <v>486.1943969782718</v>
       </c>
       <c r="P23">
-        <v>1322.071580080287</v>
+        <v>1314.525591830142</v>
       </c>
       <c r="Q23">
-        <v>2141.271580080287</v>
+        <v>2133.725591830142</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.0921368558775781</v>
+        <v>0.09259658814306496</v>
       </c>
       <c r="T23">
-        <v>0.8486757882294768</v>
+        <v>0.8570959461231713</v>
       </c>
       <c r="U23">
         <v>0.05868110587651873</v>
@@ -3217,7 +3217,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>9.342948258158572</v>
+        <v>8.918268791878635</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.08164952435535958</v>
+        <v>0.08176696903656212</v>
       </c>
       <c r="C24">
-        <v>13119.41103769126</v>
+        <v>12893.90120904466</v>
       </c>
       <c r="D24">
-        <v>15114.72103769126</v>
+        <v>15065.36620904466</v>
       </c>
       <c r="E24">
-        <v>-5790.889999999999</v>
+        <v>-5614.734999999999</v>
       </c>
       <c r="F24">
-        <v>3875.41</v>
+        <v>4051.565</v>
       </c>
       <c r="G24">
         <v>1880.1</v>
@@ -3261,45 +3261,45 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M24">
-        <v>227.4133445249194</v>
+        <v>243.8276622305976</v>
       </c>
       <c r="N24">
-        <v>1800.719988808414</v>
+        <v>1784.305671102736</v>
       </c>
       <c r="O24">
-        <v>486.1943969782718</v>
+        <v>481.7625311977387</v>
       </c>
       <c r="P24">
-        <v>1314.525591830142</v>
+        <v>1302.543139904997</v>
       </c>
       <c r="Q24">
-        <v>2133.725591830142</v>
+        <v>2121.743139904997</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.09259658814306496</v>
+        <v>0.09306826150635665</v>
       </c>
       <c r="T24">
-        <v>0.8570959461231713</v>
+        <v>0.865734809416702</v>
       </c>
       <c r="U24">
-        <v>0.05868110587651873</v>
+        <v>0.06018110587651872</v>
       </c>
       <c r="V24">
         <v>0.27</v>
       </c>
       <c r="W24">
-        <v>0.04283720728985867</v>
+        <v>0.04393220728985867</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y24">
-        <v>8.918268791878635</v>
+        <v>8.317896807849662</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3307,22 +3307,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.08176696903656212</v>
+        <v>0.08164351371776465</v>
       </c>
       <c r="C25">
-        <v>12893.90120904466</v>
+        <v>12769.6356416149</v>
       </c>
       <c r="D25">
-        <v>15065.36620904466</v>
+        <v>15117.2556416149</v>
       </c>
       <c r="E25">
-        <v>-5614.734999999999</v>
+        <v>-5438.579999999999</v>
       </c>
       <c r="F25">
-        <v>4051.565</v>
+        <v>4227.72</v>
       </c>
       <c r="G25">
         <v>1880.1</v>
@@ -3343,28 +3343,28 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M25">
-        <v>243.8276622305976</v>
+        <v>254.4288649362757</v>
       </c>
       <c r="N25">
-        <v>1784.305671102736</v>
+        <v>1773.704468397058</v>
       </c>
       <c r="O25">
-        <v>481.7625311977387</v>
+        <v>478.9002064672056</v>
       </c>
       <c r="P25">
-        <v>1302.543139904997</v>
+        <v>1294.804261929852</v>
       </c>
       <c r="Q25">
-        <v>2121.743139904997</v>
+        <v>2114.004261929852</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.09306826150635665</v>
+        <v>0.09355234732657708</v>
       </c>
       <c r="T25">
-        <v>0.865734809416702</v>
+        <v>0.8746010112179572</v>
       </c>
       <c r="U25">
         <v>0.06018110587651872</v>
@@ -3381,7 +3381,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>8.317896807849662</v>
+        <v>7.971317774189259</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3389,22 +3389,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.08164351371776465</v>
+        <v>0.0815200583989672</v>
       </c>
       <c r="C26">
-        <v>12769.6356416149</v>
+        <v>12645.72875369055</v>
       </c>
       <c r="D26">
-        <v>15117.2556416149</v>
+        <v>15169.50375369055</v>
       </c>
       <c r="E26">
-        <v>-5438.579999999999</v>
+        <v>-5262.424999999999</v>
       </c>
       <c r="F26">
-        <v>4227.72</v>
+        <v>4403.875</v>
       </c>
       <c r="G26">
         <v>1880.1</v>
@@ -3425,28 +3425,28 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M26">
-        <v>254.4288649362757</v>
+        <v>265.0300676419539</v>
       </c>
       <c r="N26">
-        <v>1773.704468397058</v>
+        <v>1763.103265691379</v>
       </c>
       <c r="O26">
-        <v>478.9002064672056</v>
+        <v>476.0378817366725</v>
       </c>
       <c r="P26">
-        <v>1294.804261929852</v>
+        <v>1287.065383954707</v>
       </c>
       <c r="Q26">
-        <v>2114.004261929852</v>
+        <v>2106.265383954707</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.09355234732657708</v>
+        <v>0.09404934210200339</v>
       </c>
       <c r="T26">
-        <v>0.8746010112179572</v>
+        <v>0.883703645067246</v>
       </c>
       <c r="U26">
         <v>0.06018110587651872</v>
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>7.971317774189259</v>
+        <v>7.652465063221689</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3471,22 +3471,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.0815200583989672</v>
+        <v>0.08139660308016976</v>
       </c>
       <c r="C27">
-        <v>12645.72875369055</v>
+        <v>12522.18427716363</v>
       </c>
       <c r="D27">
-        <v>15169.50375369055</v>
+        <v>15222.11427716362</v>
       </c>
       <c r="E27">
-        <v>-5262.424999999999</v>
+        <v>-5086.27</v>
       </c>
       <c r="F27">
-        <v>4403.875</v>
+        <v>4580.03</v>
       </c>
       <c r="G27">
         <v>1880.1</v>
@@ -3507,28 +3507,28 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M27">
-        <v>265.0300676419539</v>
+        <v>275.631270347632</v>
       </c>
       <c r="N27">
-        <v>1763.103265691379</v>
+        <v>1752.502062985701</v>
       </c>
       <c r="O27">
-        <v>476.0378817366725</v>
+        <v>473.1755570061394</v>
       </c>
       <c r="P27">
-        <v>1287.065383954707</v>
+        <v>1279.326505979562</v>
       </c>
       <c r="Q27">
-        <v>2106.265383954707</v>
+        <v>2098.526505979562</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.09404934210200339</v>
+        <v>0.09455976916865744</v>
       </c>
       <c r="T27">
-        <v>0.883703645067246</v>
+        <v>0.8930522960475964</v>
       </c>
       <c r="U27">
         <v>0.06018110587651872</v>
@@ -3545,7 +3545,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>7.652465063221689</v>
+        <v>7.358139483867009</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3553,22 +3553,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.08139660308016976</v>
+        <v>0.08127314776137229</v>
       </c>
       <c r="C28">
-        <v>12522.18427716363</v>
+        <v>12399.00599587775</v>
       </c>
       <c r="D28">
-        <v>15222.11427716362</v>
+        <v>15275.09099587775</v>
       </c>
       <c r="E28">
-        <v>-5086.27</v>
+        <v>-4910.114999999999</v>
       </c>
       <c r="F28">
-        <v>4580.03</v>
+        <v>4756.185</v>
       </c>
       <c r="G28">
         <v>1880.1</v>
@@ -3589,28 +3589,28 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M28">
-        <v>275.631270347632</v>
+        <v>286.2324730533102</v>
       </c>
       <c r="N28">
-        <v>1752.502062985701</v>
+        <v>1741.900860280023</v>
       </c>
       <c r="O28">
-        <v>473.1755570061394</v>
+        <v>470.3132322756062</v>
       </c>
       <c r="P28">
-        <v>1279.326505979562</v>
+        <v>1271.587628004417</v>
       </c>
       <c r="Q28">
-        <v>2098.526505979562</v>
+        <v>2090.787628004417</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.09455976916865744</v>
+        <v>0.09508418053850748</v>
       </c>
       <c r="T28">
-        <v>0.8930522960475964</v>
+        <v>0.9026570744520662</v>
       </c>
       <c r="U28">
         <v>0.06018110587651872</v>
@@ -3627,7 +3627,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>7.358139483867009</v>
+        <v>7.085615799279341</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3635,22 +3635,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.08127314776137229</v>
+        <v>0.08114969244257485</v>
       </c>
       <c r="C29">
-        <v>12399.00599587775</v>
+        <v>12276.19774653532</v>
       </c>
       <c r="D29">
-        <v>15275.09099587775</v>
+        <v>15328.43774653532</v>
       </c>
       <c r="E29">
-        <v>-4910.114999999999</v>
+        <v>-4733.959999999999</v>
       </c>
       <c r="F29">
-        <v>4756.185</v>
+        <v>4932.34</v>
       </c>
       <c r="G29">
         <v>1880.1</v>
@@ -3671,28 +3671,28 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M29">
-        <v>286.2324730533102</v>
+        <v>296.8336757589884</v>
       </c>
       <c r="N29">
-        <v>1741.900860280023</v>
+        <v>1731.299657574345</v>
       </c>
       <c r="O29">
-        <v>470.3132322756062</v>
+        <v>467.4509075450731</v>
       </c>
       <c r="P29">
-        <v>1271.587628004417</v>
+        <v>1263.848750029272</v>
       </c>
       <c r="Q29">
-        <v>2090.787628004417</v>
+        <v>2083.048750029272</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.09508418053850748</v>
+        <v>0.09562315889085336</v>
       </c>
       <c r="T29">
-        <v>0.9026570744520662</v>
+        <v>0.91252865225666</v>
       </c>
       <c r="U29">
         <v>0.06018110587651872</v>
@@ -3709,7 +3709,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>7.085615799279341</v>
+        <v>6.832558092162222</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3717,22 +3717,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.08114969244257485</v>
+        <v>0.08138612712377739</v>
       </c>
       <c r="C30">
-        <v>12276.19774653532</v>
+        <v>11998.20041119691</v>
       </c>
       <c r="D30">
-        <v>15328.43774653532</v>
+        <v>15226.59541119691</v>
       </c>
       <c r="E30">
-        <v>-4733.959999999999</v>
+        <v>-4557.804999999998</v>
       </c>
       <c r="F30">
-        <v>4932.34</v>
+        <v>5108.495000000001</v>
       </c>
       <c r="G30">
         <v>1880.1</v>
@@ -3753,45 +3753,45 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M30">
-        <v>296.8336757589884</v>
+        <v>316.1193199646665</v>
       </c>
       <c r="N30">
-        <v>1731.299657574345</v>
+        <v>1712.014013368667</v>
       </c>
       <c r="O30">
-        <v>467.4509075450731</v>
+        <v>462.24378360954</v>
       </c>
       <c r="P30">
-        <v>1263.848750029272</v>
+        <v>1249.770229759127</v>
       </c>
       <c r="Q30">
-        <v>2083.048750029272</v>
+        <v>2068.970229759127</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.09562315889085336</v>
+        <v>0.09617731973199772</v>
       </c>
       <c r="T30">
-        <v>0.91252865225666</v>
+        <v>0.9226783026754679</v>
       </c>
       <c r="U30">
-        <v>0.06018110587651872</v>
+        <v>0.06188110587651872</v>
       </c>
       <c r="V30">
         <v>0.27</v>
       </c>
       <c r="W30">
-        <v>0.04393220728985867</v>
+        <v>0.04517320728985866</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y30">
-        <v>6.832558092162222</v>
+        <v>6.415720916899425</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3799,22 +3799,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.08138612712377739</v>
+        <v>0.08127508180497994</v>
       </c>
       <c r="C31">
-        <v>11998.20041119691</v>
+        <v>11869.70822282709</v>
       </c>
       <c r="D31">
-        <v>15226.59541119691</v>
+        <v>15274.25822282709</v>
       </c>
       <c r="E31">
-        <v>-4557.804999999999</v>
+        <v>-4381.65</v>
       </c>
       <c r="F31">
-        <v>5108.495</v>
+        <v>5284.65</v>
       </c>
       <c r="G31">
         <v>1880.1</v>
@@ -3835,28 +3835,28 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M31">
-        <v>316.1193199646665</v>
+        <v>327.0199861703447</v>
       </c>
       <c r="N31">
-        <v>1712.014013368667</v>
+        <v>1701.113347162988</v>
       </c>
       <c r="O31">
-        <v>462.2437836095401</v>
+        <v>459.3006037340069</v>
       </c>
       <c r="P31">
-        <v>1249.770229759127</v>
+        <v>1241.812743428982</v>
       </c>
       <c r="Q31">
-        <v>2068.970229759127</v>
+        <v>2061.012743428982</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.09617731973199772</v>
+        <v>0.09674731374003193</v>
       </c>
       <c r="T31">
-        <v>0.9226783026754679</v>
+        <v>0.9331179431062416</v>
       </c>
       <c r="U31">
         <v>0.06188110587651872</v>
@@ -3873,7 +3873,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>6.415720916899427</v>
+        <v>6.201863553002778</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3881,22 +3881,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.08127508180497994</v>
+        <v>0.08116403648618248</v>
       </c>
       <c r="C32">
-        <v>11869.70822282709</v>
+        <v>11741.51536296376</v>
       </c>
       <c r="D32">
-        <v>15274.25822282709</v>
+        <v>15322.22036296377</v>
       </c>
       <c r="E32">
-        <v>-4381.65</v>
+        <v>-4205.494999999999</v>
       </c>
       <c r="F32">
-        <v>5284.65</v>
+        <v>5460.805</v>
       </c>
       <c r="G32">
         <v>1880.1</v>
@@ -3917,28 +3917,28 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M32">
-        <v>327.0199861703447</v>
+        <v>337.9206523760229</v>
       </c>
       <c r="N32">
-        <v>1701.113347162988</v>
+        <v>1690.21268095731</v>
       </c>
       <c r="O32">
-        <v>459.3006037340069</v>
+        <v>456.3574238584738</v>
       </c>
       <c r="P32">
-        <v>1241.812743428982</v>
+        <v>1233.855257098837</v>
       </c>
       <c r="Q32">
-        <v>2061.012743428982</v>
+        <v>2053.055257098837</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.09674731374003193</v>
+        <v>0.09733382931351638</v>
       </c>
       <c r="T32">
-        <v>0.9331179431062416</v>
+        <v>0.9438601818103711</v>
       </c>
       <c r="U32">
         <v>0.06188110587651872</v>
@@ -3955,7 +3955,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>6.201863553002778</v>
+        <v>6.001803438389785</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3963,22 +3963,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.08116403648618248</v>
+        <v>0.08105299116738504</v>
       </c>
       <c r="C33">
-        <v>11741.51536296376</v>
+        <v>11613.62466022045</v>
       </c>
       <c r="D33">
-        <v>15322.22036296377</v>
+        <v>15370.48466022045</v>
       </c>
       <c r="E33">
-        <v>-4205.494999999999</v>
+        <v>-4029.339999999999</v>
       </c>
       <c r="F33">
-        <v>5460.805</v>
+        <v>5636.96</v>
       </c>
       <c r="G33">
         <v>1880.1</v>
@@ -3999,28 +3999,28 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M33">
-        <v>337.9206523760229</v>
+        <v>348.821318581701</v>
       </c>
       <c r="N33">
-        <v>1690.21268095731</v>
+        <v>1679.312014751632</v>
       </c>
       <c r="O33">
-        <v>456.3574238584738</v>
+        <v>453.4142439829407</v>
       </c>
       <c r="P33">
-        <v>1233.855257098837</v>
+        <v>1225.897770768692</v>
       </c>
       <c r="Q33">
-        <v>2053.055257098837</v>
+        <v>2045.097770768691</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.09733382931351638</v>
+        <v>0.09793759534504451</v>
       </c>
       <c r="T33">
-        <v>0.9438601818103711</v>
+        <v>0.9549183687116809</v>
       </c>
       <c r="U33">
         <v>0.06188110587651872</v>
@@ -4037,7 +4037,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>6.001803438389785</v>
+        <v>5.814247080940104</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4045,22 +4045,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.08105299116738504</v>
+        <v>0.08094194584858759</v>
       </c>
       <c r="C34">
-        <v>11613.62466022045</v>
+        <v>11486.03897896334</v>
       </c>
       <c r="D34">
-        <v>15370.48466022045</v>
+        <v>15419.05397896334</v>
       </c>
       <c r="E34">
-        <v>-4029.339999999999</v>
+        <v>-3853.184999999999</v>
       </c>
       <c r="F34">
-        <v>5636.96</v>
+        <v>5813.115000000001</v>
       </c>
       <c r="G34">
         <v>1880.1</v>
@@ -4081,28 +4081,28 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M34">
-        <v>348.821318581701</v>
+        <v>359.7219847873792</v>
       </c>
       <c r="N34">
-        <v>1679.312014751632</v>
+        <v>1668.411348545954</v>
       </c>
       <c r="O34">
-        <v>453.4142439829407</v>
+        <v>450.4710641074076</v>
       </c>
       <c r="P34">
-        <v>1225.897770768692</v>
+        <v>1217.940284438546</v>
       </c>
       <c r="Q34">
-        <v>2045.097770768691</v>
+        <v>2037.140284438546</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.09793759534504451</v>
+        <v>0.09855938424318542</v>
       </c>
       <c r="T34">
-        <v>0.9549183687116809</v>
+        <v>0.9663066507443732</v>
       </c>
       <c r="U34">
         <v>0.06188110587651872</v>
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>5.814247080940104</v>
+        <v>5.63805777545707</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4127,22 +4127,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.08094194584858759</v>
+        <v>0.08102946052979013</v>
       </c>
       <c r="C35">
-        <v>11486.03897896334</v>
+        <v>11271.58099126154</v>
       </c>
       <c r="D35">
-        <v>15419.05397896334</v>
+        <v>15380.75099126154</v>
       </c>
       <c r="E35">
-        <v>-3853.184999999999</v>
+        <v>-3677.029999999999</v>
       </c>
       <c r="F35">
-        <v>5813.115000000001</v>
+        <v>5989.27</v>
       </c>
       <c r="G35">
         <v>1880.1</v>
@@ -4163,45 +4163,45 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M35">
-        <v>359.7219847873792</v>
+        <v>375.4140669930574</v>
       </c>
       <c r="N35">
-        <v>1668.411348545954</v>
+        <v>1652.719266340276</v>
       </c>
       <c r="O35">
-        <v>450.4710641074076</v>
+        <v>446.2342019118745</v>
       </c>
       <c r="P35">
-        <v>1217.940284438546</v>
+        <v>1206.485064428401</v>
       </c>
       <c r="Q35">
-        <v>2037.140284438546</v>
+        <v>2025.685064428401</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.09855938424318542</v>
+        <v>0.09920001522914876</v>
       </c>
       <c r="T35">
-        <v>0.9663066507443732</v>
+        <v>0.9780400322326014</v>
       </c>
       <c r="U35">
-        <v>0.06188110587651872</v>
+        <v>0.06268110587651873</v>
       </c>
       <c r="V35">
         <v>0.27</v>
       </c>
       <c r="W35">
-        <v>0.04517320728985866</v>
+        <v>0.04575720728985867</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y35">
-        <v>5.63805777545707</v>
+        <v>5.402390351480463</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4209,22 +4209,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.08102946052979013</v>
+        <v>0.08092425521099268</v>
       </c>
       <c r="C36">
-        <v>11271.58099126154</v>
+        <v>11141.49492003055</v>
       </c>
       <c r="D36">
-        <v>15380.75099126154</v>
+        <v>15426.81992003055</v>
       </c>
       <c r="E36">
-        <v>-3677.029999999999</v>
+        <v>-3500.874999999999</v>
       </c>
       <c r="F36">
-        <v>5989.27</v>
+        <v>6165.425</v>
       </c>
       <c r="G36">
         <v>1880.1</v>
@@ -4245,28 +4245,28 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M36">
-        <v>375.4140669930574</v>
+        <v>386.4556571987355</v>
       </c>
       <c r="N36">
-        <v>1652.719266340276</v>
+        <v>1641.677676134598</v>
       </c>
       <c r="O36">
-        <v>446.2342019118745</v>
+        <v>443.2529725563414</v>
       </c>
       <c r="P36">
-        <v>1206.485064428401</v>
+        <v>1198.424703578256</v>
       </c>
       <c r="Q36">
-        <v>2025.685064428401</v>
+        <v>2017.624703578256</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.09920001522914876</v>
+        <v>0.09986035793775715</v>
       </c>
       <c r="T36">
-        <v>0.9780400322326014</v>
+        <v>0.9901344408435444</v>
       </c>
       <c r="U36">
         <v>0.06268110587651873</v>
@@ -4283,7 +4283,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>5.402390351480463</v>
+        <v>5.248036341438164</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.08092425521099268</v>
+        <v>0.08081904989219521</v>
       </c>
       <c r="C37">
-        <v>11141.49492003055</v>
+        <v>11011.68565221672</v>
       </c>
       <c r="D37">
-        <v>15426.81992003055</v>
+        <v>15473.16565221672</v>
       </c>
       <c r="E37">
-        <v>-3500.874999999999</v>
+        <v>-3324.719999999998</v>
       </c>
       <c r="F37">
-        <v>6165.425</v>
+        <v>6341.580000000001</v>
       </c>
       <c r="G37">
         <v>1880.1</v>
@@ -4327,28 +4327,28 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M37">
-        <v>386.4556571987355</v>
+        <v>397.4972474044137</v>
       </c>
       <c r="N37">
-        <v>1641.677676134598</v>
+        <v>1630.63608592892</v>
       </c>
       <c r="O37">
-        <v>443.2529725563414</v>
+        <v>440.2717432008083</v>
       </c>
       <c r="P37">
-        <v>1198.424703578256</v>
+        <v>1190.364342728111</v>
       </c>
       <c r="Q37">
-        <v>2017.624703578256</v>
+        <v>2009.564342728111</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.09986035793775715</v>
+        <v>0.1005413363560095</v>
       </c>
       <c r="T37">
-        <v>0.9901344408435444</v>
+        <v>1.002606799723579</v>
       </c>
       <c r="U37">
         <v>0.06268110587651873</v>
@@ -4365,7 +4365,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>5.248036341438164</v>
+        <v>5.102257554175992</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4373,22 +4373,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.08081904989219522</v>
+        <v>0.08071384457339775</v>
       </c>
       <c r="C38">
-        <v>11011.68565221672</v>
+        <v>10882.15569008172</v>
       </c>
       <c r="D38">
-        <v>15473.16565221672</v>
+        <v>15519.79069008172</v>
       </c>
       <c r="E38">
-        <v>-3324.719999999999</v>
+        <v>-3148.565</v>
       </c>
       <c r="F38">
-        <v>6341.58</v>
+        <v>6517.735</v>
       </c>
       <c r="G38">
         <v>1880.1</v>
@@ -4409,28 +4409,28 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M38">
-        <v>397.4972474044137</v>
+        <v>408.5388376100918</v>
       </c>
       <c r="N38">
-        <v>1630.63608592892</v>
+        <v>1619.594495723241</v>
       </c>
       <c r="O38">
-        <v>440.2717432008083</v>
+        <v>437.2905138452752</v>
       </c>
       <c r="P38">
-        <v>1190.364342728111</v>
+        <v>1182.303981877966</v>
       </c>
       <c r="Q38">
-        <v>2009.564342728111</v>
+        <v>2001.503981877966</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1005413363560095</v>
+        <v>0.1012439331367461</v>
       </c>
       <c r="T38">
-        <v>1.002606799723579</v>
+        <v>1.015475106504568</v>
       </c>
       <c r="U38">
         <v>0.06268110587651873</v>
@@ -4447,7 +4447,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>5.102257554175993</v>
+        <v>4.964358701360426</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4455,22 +4455,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.08071384457339775</v>
+        <v>0.08060863925460031</v>
       </c>
       <c r="C39">
-        <v>10882.15569008172</v>
+        <v>10752.90756613847</v>
       </c>
       <c r="D39">
-        <v>15519.79069008172</v>
+        <v>15566.69756613847</v>
       </c>
       <c r="E39">
-        <v>-3148.565</v>
+        <v>-2972.409999999999</v>
       </c>
       <c r="F39">
-        <v>6517.735</v>
+        <v>6693.89</v>
       </c>
       <c r="G39">
         <v>1880.1</v>
@@ -4491,28 +4491,28 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M39">
-        <v>408.5388376100918</v>
+        <v>419.58042781577</v>
       </c>
       <c r="N39">
-        <v>1619.594495723241</v>
+        <v>1608.552905517563</v>
       </c>
       <c r="O39">
-        <v>437.2905138452752</v>
+        <v>434.3092844897421</v>
       </c>
       <c r="P39">
-        <v>1182.303981877966</v>
+        <v>1174.243621027821</v>
       </c>
       <c r="Q39">
-        <v>2001.503981877966</v>
+        <v>1993.443621027821</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1012439331367461</v>
+        <v>0.1019691943297645</v>
       </c>
       <c r="T39">
-        <v>1.015475106504568</v>
+        <v>1.028758519955911</v>
       </c>
       <c r="U39">
         <v>0.06268110587651873</v>
@@ -4529,7 +4529,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>4.964358701360426</v>
+        <v>4.833717682903572</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4537,22 +4537,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.08060863925460031</v>
+        <v>0.08050343393580288</v>
       </c>
       <c r="C40">
-        <v>10752.90756613847</v>
+        <v>10623.9438436097</v>
       </c>
       <c r="D40">
-        <v>15566.69756613847</v>
+        <v>15613.8888436097</v>
       </c>
       <c r="E40">
-        <v>-2972.409999999999</v>
+        <v>-2796.254999999999</v>
       </c>
       <c r="F40">
-        <v>6693.89</v>
+        <v>6870.045</v>
       </c>
       <c r="G40">
         <v>1880.1</v>
@@ -4573,28 +4573,28 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M40">
-        <v>419.58042781577</v>
+        <v>430.6220180214481</v>
       </c>
       <c r="N40">
-        <v>1608.552905517563</v>
+        <v>1597.511315311885</v>
       </c>
       <c r="O40">
-        <v>434.3092844897421</v>
+        <v>431.328055134209</v>
       </c>
       <c r="P40">
-        <v>1174.243621027821</v>
+        <v>1166.183260177676</v>
       </c>
       <c r="Q40">
-        <v>1993.443621027821</v>
+        <v>1985.383260177676</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1019691943297645</v>
+        <v>0.1027182345782918</v>
       </c>
       <c r="T40">
-        <v>1.028758519955911</v>
+        <v>1.042477455159757</v>
       </c>
       <c r="U40">
         <v>0.06268110587651873</v>
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>4.833717682903572</v>
+        <v>4.709776203854762</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4619,22 +4619,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.08050343393580288</v>
+        <v>0.08039822861700542</v>
       </c>
       <c r="C41">
-        <v>10623.9438436097</v>
+        <v>10495.26711689484</v>
       </c>
       <c r="D41">
-        <v>15613.8888436097</v>
+        <v>15661.36711689484</v>
       </c>
       <c r="E41">
-        <v>-2796.254999999999</v>
+        <v>-2620.099999999999</v>
       </c>
       <c r="F41">
-        <v>6870.045</v>
+        <v>7046.200000000001</v>
       </c>
       <c r="G41">
         <v>1880.1</v>
@@ -4655,28 +4655,28 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M41">
-        <v>430.6220180214481</v>
+        <v>441.6636082271264</v>
       </c>
       <c r="N41">
-        <v>1597.511315311885</v>
+        <v>1586.469725106207</v>
       </c>
       <c r="O41">
-        <v>431.328055134209</v>
+        <v>428.3468257786758</v>
       </c>
       <c r="P41">
-        <v>1166.183260177676</v>
+        <v>1158.122899327531</v>
       </c>
       <c r="Q41">
-        <v>1985.383260177676</v>
+        <v>1977.322899327531</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1027182345782918</v>
+        <v>0.1034922428351032</v>
       </c>
       <c r="T41">
-        <v>1.042477455159757</v>
+        <v>1.056653688203731</v>
       </c>
       <c r="U41">
         <v>0.06268110587651873</v>
@@ -4693,7 +4693,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>4.709776203854762</v>
+        <v>4.592031798758393</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4701,22 +4701,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.08039822861700542</v>
+        <v>0.08029302329820796</v>
       </c>
       <c r="C42">
-        <v>10495.26711689484</v>
+        <v>10366.88001204547</v>
       </c>
       <c r="D42">
-        <v>15661.36711689484</v>
+        <v>15709.13501204547</v>
       </c>
       <c r="E42">
-        <v>-2620.099999999999</v>
+        <v>-2443.944999999999</v>
       </c>
       <c r="F42">
-        <v>7046.200000000001</v>
+        <v>7222.355</v>
       </c>
       <c r="G42">
         <v>1880.1</v>
@@ -4737,28 +4737,28 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M42">
-        <v>441.6636082271264</v>
+        <v>452.7051984328045</v>
       </c>
       <c r="N42">
-        <v>1586.469725106207</v>
+        <v>1575.428134900529</v>
       </c>
       <c r="O42">
-        <v>428.3468257786758</v>
+        <v>425.3655964231428</v>
       </c>
       <c r="P42">
-        <v>1158.122899327531</v>
+        <v>1150.062538477386</v>
       </c>
       <c r="Q42">
-        <v>1977.322899327531</v>
+        <v>1969.262538477386</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1034922428351032</v>
+        <v>0.1042924886599422</v>
       </c>
       <c r="T42">
-        <v>1.056653688203731</v>
+        <v>1.071310471520382</v>
       </c>
       <c r="U42">
         <v>0.06268110587651873</v>
@@ -4775,7 +4775,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>4.592031798758393</v>
+        <v>4.48003102317892</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4783,22 +4783,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.08029302329820796</v>
+        <v>0.08018781797941052</v>
       </c>
       <c r="C43">
-        <v>10366.88001204547</v>
+        <v>10238.78518724948</v>
       </c>
       <c r="D43">
-        <v>15709.13501204547</v>
+        <v>15757.19518724948</v>
       </c>
       <c r="E43">
-        <v>-2443.944999999999</v>
+        <v>-2267.789999999998</v>
       </c>
       <c r="F43">
-        <v>7222.355</v>
+        <v>7398.510000000001</v>
       </c>
       <c r="G43">
         <v>1880.1</v>
@@ -4819,28 +4819,28 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M43">
-        <v>452.7051984328045</v>
+        <v>463.7467886384827</v>
       </c>
       <c r="N43">
-        <v>1575.428134900529</v>
+        <v>1564.38654469485</v>
       </c>
       <c r="O43">
-        <v>425.3655964231428</v>
+        <v>422.3843670676097</v>
       </c>
       <c r="P43">
-        <v>1150.062538477386</v>
+        <v>1142.002177627241</v>
       </c>
       <c r="Q43">
-        <v>1969.262538477386</v>
+        <v>1961.202177627241</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1042924886599422</v>
+        <v>0.1051203291683963</v>
       </c>
       <c r="T43">
-        <v>1.071310471520382</v>
+        <v>1.086472661158298</v>
       </c>
       <c r="U43">
         <v>0.06268110587651873</v>
@@ -4857,7 +4857,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>4.48003102317892</v>
+        <v>4.373363617865136</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4865,22 +4865,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.08018781797941051</v>
+        <v>0.08008261266061306</v>
       </c>
       <c r="C44">
-        <v>10238.78518724949</v>
+        <v>10110.98533332424</v>
       </c>
       <c r="D44">
-        <v>15757.19518724949</v>
+        <v>15805.55033332425</v>
       </c>
       <c r="E44">
-        <v>-2267.79</v>
+        <v>-2091.634999999999</v>
       </c>
       <c r="F44">
-        <v>7398.509999999999</v>
+        <v>7574.665</v>
       </c>
       <c r="G44">
         <v>1880.1</v>
@@ -4901,28 +4901,28 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M44">
-        <v>463.7467886384826</v>
+        <v>474.7883788441608</v>
       </c>
       <c r="N44">
-        <v>1564.386544694851</v>
+        <v>1553.344954489172</v>
       </c>
       <c r="O44">
-        <v>422.3843670676097</v>
+        <v>419.4031377120766</v>
       </c>
       <c r="P44">
-        <v>1142.002177627241</v>
+        <v>1133.941816777096</v>
       </c>
       <c r="Q44">
-        <v>1961.202177627241</v>
+        <v>1953.141816777096</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1051203291683963</v>
+        <v>0.1059772167122348</v>
       </c>
       <c r="T44">
-        <v>1.086472661158297</v>
+        <v>1.102166857450174</v>
       </c>
       <c r="U44">
         <v>0.06268110587651873</v>
@@ -4939,7 +4939,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>4.373363617865137</v>
+        <v>4.27165748721711</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4947,22 +4947,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.08008261266061306</v>
+        <v>0.0802986073418156</v>
       </c>
       <c r="C45">
-        <v>10110.98533332424</v>
+        <v>9835.872286361606</v>
       </c>
       <c r="D45">
-        <v>15805.55033332425</v>
+        <v>15706.59228636161</v>
       </c>
       <c r="E45">
-        <v>-2091.634999999999</v>
+        <v>-1915.48</v>
       </c>
       <c r="F45">
-        <v>7574.665</v>
+        <v>7750.82</v>
       </c>
       <c r="G45">
         <v>1880.1</v>
@@ -4983,45 +4983,45 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M45">
-        <v>474.7883788441608</v>
+        <v>493.5807890498389</v>
       </c>
       <c r="N45">
-        <v>1553.344954489172</v>
+        <v>1534.552544283494</v>
       </c>
       <c r="O45">
-        <v>419.4031377120766</v>
+        <v>414.3291869565435</v>
       </c>
       <c r="P45">
-        <v>1133.941816777096</v>
+        <v>1120.223357326951</v>
       </c>
       <c r="Q45">
-        <v>1953.141816777096</v>
+        <v>1939.423357326951</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1059772167122348</v>
+        <v>0.1068647073826389</v>
       </c>
       <c r="T45">
-        <v>1.102166857450174</v>
+        <v>1.118421560752475</v>
       </c>
       <c r="U45">
-        <v>0.06268110587651873</v>
+        <v>0.06368110587651873</v>
       </c>
       <c r="V45">
         <v>0.27</v>
       </c>
       <c r="W45">
-        <v>0.04575720728985867</v>
+        <v>0.04648720728985867</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y45">
-        <v>4.27165748721711</v>
+        <v>4.109019999010829</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5029,22 +5029,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.0802986073418156</v>
+        <v>0.08020070202301816</v>
       </c>
       <c r="C46">
-        <v>9835.872286361606</v>
+        <v>9704.418668443535</v>
       </c>
       <c r="D46">
-        <v>15706.59228636161</v>
+        <v>15751.29366844354</v>
       </c>
       <c r="E46">
-        <v>-1915.48</v>
+        <v>-1739.324999999999</v>
       </c>
       <c r="F46">
-        <v>7750.82</v>
+        <v>7926.975</v>
       </c>
       <c r="G46">
         <v>1880.1</v>
@@ -5065,28 +5065,28 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M46">
-        <v>493.5807890498389</v>
+        <v>504.7985342555171</v>
       </c>
       <c r="N46">
-        <v>1534.552544283494</v>
+        <v>1523.334799077816</v>
       </c>
       <c r="O46">
-        <v>414.3291869565435</v>
+        <v>411.3003957510104</v>
       </c>
       <c r="P46">
-        <v>1120.223357326951</v>
+        <v>1112.034403326806</v>
       </c>
       <c r="Q46">
-        <v>1939.423357326951</v>
+        <v>1931.234403326805</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1068647073826389</v>
+        <v>0.1077844704410577</v>
       </c>
       <c r="T46">
-        <v>1.118421560752475</v>
+        <v>1.13526734417486</v>
       </c>
       <c r="U46">
         <v>0.06368110587651873</v>
@@ -5103,7 +5103,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>4.109019999010829</v>
+        <v>4.017708443477255</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5111,22 +5111,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.08020070202301816</v>
+        <v>0.08010279670422071</v>
       </c>
       <c r="C47">
-        <v>9704.418668443535</v>
+        <v>9573.220219402872</v>
       </c>
       <c r="D47">
-        <v>15751.29366844354</v>
+        <v>15796.25021940287</v>
       </c>
       <c r="E47">
-        <v>-1739.324999999999</v>
+        <v>-1563.169999999999</v>
       </c>
       <c r="F47">
-        <v>7926.975</v>
+        <v>8103.13</v>
       </c>
       <c r="G47">
         <v>1880.1</v>
@@ -5147,28 +5147,28 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M47">
-        <v>504.7985342555171</v>
+        <v>516.0162794611953</v>
       </c>
       <c r="N47">
-        <v>1523.334799077816</v>
+        <v>1512.117053872138</v>
       </c>
       <c r="O47">
-        <v>411.3003957510104</v>
+        <v>408.2716045454773</v>
       </c>
       <c r="P47">
-        <v>1112.034403326806</v>
+        <v>1103.845449326661</v>
       </c>
       <c r="Q47">
-        <v>1931.234403326805</v>
+        <v>1923.045449326661</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1077844704410577</v>
+        <v>0.1087382987979365</v>
       </c>
       <c r="T47">
-        <v>1.13526734417486</v>
+        <v>1.152737045501778</v>
       </c>
       <c r="U47">
         <v>0.06368110587651873</v>
@@ -5185,7 +5185,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>4.017708443477255</v>
+        <v>3.930366955575575</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5193,22 +5193,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.08010279670422071</v>
+        <v>0.08000489138542326</v>
       </c>
       <c r="C48">
-        <v>9573.220219402872</v>
+        <v>9442.27913036399</v>
       </c>
       <c r="D48">
-        <v>15796.25021940287</v>
+        <v>15841.46413036399</v>
       </c>
       <c r="E48">
-        <v>-1563.169999999999</v>
+        <v>-1387.014999999999</v>
       </c>
       <c r="F48">
-        <v>8103.13</v>
+        <v>8279.285</v>
       </c>
       <c r="G48">
         <v>1880.1</v>
@@ -5229,28 +5229,28 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M48">
-        <v>516.0162794611953</v>
+        <v>527.2340246668734</v>
       </c>
       <c r="N48">
-        <v>1512.117053872138</v>
+        <v>1500.89930866646</v>
       </c>
       <c r="O48">
-        <v>408.2716045454773</v>
+        <v>405.2428133399442</v>
       </c>
       <c r="P48">
-        <v>1103.845449326661</v>
+        <v>1095.656495326516</v>
       </c>
       <c r="Q48">
-        <v>1923.045449326661</v>
+        <v>1914.856495326515</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1087382987979365</v>
+        <v>0.1097281206777164</v>
       </c>
       <c r="T48">
-        <v>1.152737045501778</v>
+        <v>1.170865980841032</v>
       </c>
       <c r="U48">
         <v>0.06368110587651873</v>
@@ -5267,7 +5267,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>3.930366955575575</v>
+        <v>3.846742126733541</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5275,22 +5275,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.08000489138542326</v>
+        <v>0.07990698606662579</v>
       </c>
       <c r="C49">
-        <v>9442.27913036399</v>
+        <v>9311.597617610039</v>
       </c>
       <c r="D49">
-        <v>15841.46413036399</v>
+        <v>15886.93761761004</v>
       </c>
       <c r="E49">
-        <v>-1387.014999999999</v>
+        <v>-1210.859999999999</v>
       </c>
       <c r="F49">
-        <v>8279.285</v>
+        <v>8455.440000000001</v>
       </c>
       <c r="G49">
         <v>1880.1</v>
@@ -5311,28 +5311,28 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M49">
-        <v>527.2340246668734</v>
+        <v>538.4517698725516</v>
       </c>
       <c r="N49">
-        <v>1500.89930866646</v>
+        <v>1489.681563460781</v>
       </c>
       <c r="O49">
-        <v>405.2428133399442</v>
+        <v>402.214022134411</v>
       </c>
       <c r="P49">
-        <v>1095.656495326516</v>
+        <v>1087.46754132637</v>
       </c>
       <c r="Q49">
-        <v>1914.856495326515</v>
+        <v>1906.66754132637</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1097281206777164</v>
+        <v>0.1107560126297954</v>
       </c>
       <c r="T49">
-        <v>1.170865980841032</v>
+        <v>1.189692182924104</v>
       </c>
       <c r="U49">
         <v>0.06368110587651873</v>
@@ -5349,7 +5349,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>3.846742126733541</v>
+        <v>3.766601665759926</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.07990698606662579</v>
+        <v>0.07980908074782835</v>
       </c>
       <c r="C50">
-        <v>9311.597617610039</v>
+        <v>9181.177922945115</v>
       </c>
       <c r="D50">
-        <v>15886.93761761004</v>
+        <v>15932.67292294512</v>
       </c>
       <c r="E50">
-        <v>-1210.859999999999</v>
+        <v>-1034.705</v>
       </c>
       <c r="F50">
-        <v>8455.440000000001</v>
+        <v>8631.594999999999</v>
       </c>
       <c r="G50">
         <v>1880.1</v>
@@ -5393,28 +5393,28 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M50">
-        <v>538.4517698725516</v>
+        <v>549.6695150782297</v>
       </c>
       <c r="N50">
-        <v>1489.681563460781</v>
+        <v>1478.463818255103</v>
       </c>
       <c r="O50">
-        <v>402.214022134411</v>
+        <v>399.185230928878</v>
       </c>
       <c r="P50">
-        <v>1087.46754132637</v>
+        <v>1079.278587326226</v>
       </c>
       <c r="Q50">
-        <v>1906.66754132637</v>
+        <v>1898.478587326225</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1107560126297954</v>
+        <v>0.1118242140701914</v>
       </c>
       <c r="T50">
-        <v>1.189692182924104</v>
+        <v>1.209256667441806</v>
       </c>
       <c r="U50">
         <v>0.06368110587651873</v>
@@ -5431,7 +5431,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>3.766601665759926</v>
+        <v>3.689732244009724</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5439,22 +5439,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.07980908074782835</v>
+        <v>0.07971117542903089</v>
       </c>
       <c r="C51">
-        <v>9181.177922945115</v>
+        <v>9051.022314062684</v>
       </c>
       <c r="D51">
-        <v>15932.67292294512</v>
+        <v>15978.67231406269</v>
       </c>
       <c r="E51">
-        <v>-1034.705</v>
+        <v>-858.5499999999993</v>
       </c>
       <c r="F51">
-        <v>8631.594999999999</v>
+        <v>8807.75</v>
       </c>
       <c r="G51">
         <v>1880.1</v>
@@ -5475,28 +5475,28 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M51">
-        <v>549.6695150782297</v>
+        <v>560.8872602839078</v>
       </c>
       <c r="N51">
-        <v>1478.463818255103</v>
+        <v>1467.246073049425</v>
       </c>
       <c r="O51">
-        <v>399.185230928878</v>
+        <v>396.1564397233449</v>
       </c>
       <c r="P51">
-        <v>1079.278587326226</v>
+        <v>1071.089633326081</v>
       </c>
       <c r="Q51">
-        <v>1898.478587326225</v>
+        <v>1890.28963332608</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1118242140701914</v>
+        <v>0.1129351435682031</v>
       </c>
       <c r="T51">
-        <v>1.209256667441806</v>
+        <v>1.229603731340216</v>
       </c>
       <c r="U51">
         <v>0.06368110587651873</v>
@@ -5513,7 +5513,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>3.689732244009724</v>
+        <v>3.61593759912953</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5521,22 +5521,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.07971117542903089</v>
+        <v>0.07961327011023343</v>
       </c>
       <c r="C52">
-        <v>9051.022314062684</v>
+        <v>8921.13308492035</v>
       </c>
       <c r="D52">
-        <v>15978.67231406269</v>
+        <v>16024.93808492035</v>
       </c>
       <c r="E52">
-        <v>-858.5499999999993</v>
+        <v>-682.3949999999986</v>
       </c>
       <c r="F52">
-        <v>8807.75</v>
+        <v>8983.905000000001</v>
       </c>
       <c r="G52">
         <v>1880.1</v>
@@ -5557,28 +5557,28 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M52">
-        <v>560.8872602839078</v>
+        <v>572.1050054895861</v>
       </c>
       <c r="N52">
-        <v>1467.246073049425</v>
+        <v>1456.028327843747</v>
       </c>
       <c r="O52">
-        <v>396.1564397233449</v>
+        <v>393.1276485178117</v>
       </c>
       <c r="P52">
-        <v>1071.089633326081</v>
+        <v>1062.900679325935</v>
       </c>
       <c r="Q52">
-        <v>1890.28963332608</v>
+        <v>1882.100679325935</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1129351435682031</v>
+        <v>0.1140914171273582</v>
       </c>
       <c r="T52">
-        <v>1.229603731340216</v>
+        <v>1.250781287642643</v>
       </c>
       <c r="U52">
         <v>0.06368110587651873</v>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>3.61593759912953</v>
+        <v>3.545036861891695</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5603,22 +5603,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.07961327011023343</v>
+        <v>0.07951536479143598</v>
       </c>
       <c r="C53">
-        <v>8921.13308492035</v>
+        <v>8791.512556121213</v>
       </c>
       <c r="D53">
-        <v>16024.93808492035</v>
+        <v>16071.47255612121</v>
       </c>
       <c r="E53">
-        <v>-682.3949999999986</v>
+        <v>-506.2399999999998</v>
       </c>
       <c r="F53">
-        <v>8983.905000000001</v>
+        <v>9160.059999999999</v>
       </c>
       <c r="G53">
         <v>1880.1</v>
@@ -5639,28 +5639,28 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M53">
-        <v>572.1050054895861</v>
+        <v>583.3227506952642</v>
       </c>
       <c r="N53">
-        <v>1456.028327843747</v>
+        <v>1444.810582638069</v>
       </c>
       <c r="O53">
-        <v>393.1276485178117</v>
+        <v>390.0988573122787</v>
       </c>
       <c r="P53">
-        <v>1062.900679325935</v>
+        <v>1054.71172532579</v>
       </c>
       <c r="Q53">
-        <v>1882.100679325935</v>
+        <v>1873.91172532579</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1140914171273582</v>
+        <v>0.1152958687514781</v>
       </c>
       <c r="T53">
-        <v>1.250781287642643</v>
+        <v>1.272841242124338</v>
       </c>
       <c r="U53">
         <v>0.06368110587651873</v>
@@ -5677,7 +5677,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>3.545036861891695</v>
+        <v>3.476863076086086</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5685,22 +5685,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.07951536479143598</v>
+        <v>0.07941745947263854</v>
       </c>
       <c r="C54">
-        <v>8791.512556121213</v>
+        <v>8662.163075301865</v>
       </c>
       <c r="D54">
-        <v>16071.47255612121</v>
+        <v>16118.27807530187</v>
       </c>
       <c r="E54">
-        <v>-506.2399999999998</v>
+        <v>-330.0849999999991</v>
       </c>
       <c r="F54">
-        <v>9160.059999999999</v>
+        <v>9336.215</v>
       </c>
       <c r="G54">
         <v>1880.1</v>
@@ -5721,28 +5721,28 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M54">
-        <v>583.3227506952642</v>
+        <v>594.5404959009423</v>
       </c>
       <c r="N54">
-        <v>1444.810582638069</v>
+        <v>1433.592837432391</v>
       </c>
       <c r="O54">
-        <v>390.0988573122787</v>
+        <v>387.0700661067455</v>
       </c>
       <c r="P54">
-        <v>1054.71172532579</v>
+        <v>1046.522771325645</v>
       </c>
       <c r="Q54">
-        <v>1873.91172532579</v>
+        <v>1865.722771325645</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1152958687514781</v>
+        <v>0.1165515736361988</v>
       </c>
       <c r="T54">
-        <v>1.272841242124338</v>
+        <v>1.295839918073338</v>
       </c>
       <c r="U54">
         <v>0.06368110587651873</v>
@@ -5759,7 +5759,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>3.476863076086086</v>
+        <v>3.411261885971254</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5767,22 +5767,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.07941745947263854</v>
+        <v>0.07931955415384107</v>
       </c>
       <c r="C55">
-        <v>8662.163075301865</v>
+        <v>8533.08701752723</v>
       </c>
       <c r="D55">
-        <v>16118.27807530187</v>
+        <v>16165.35701752723</v>
       </c>
       <c r="E55">
-        <v>-330.0849999999991</v>
+        <v>-153.9299999999985</v>
       </c>
       <c r="F55">
-        <v>9336.215</v>
+        <v>9512.370000000001</v>
       </c>
       <c r="G55">
         <v>1880.1</v>
@@ -5803,28 +5803,28 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M55">
-        <v>594.5404959009423</v>
+        <v>605.7582411066205</v>
       </c>
       <c r="N55">
-        <v>1433.592837432391</v>
+        <v>1422.375092226713</v>
       </c>
       <c r="O55">
-        <v>387.0700661067455</v>
+        <v>384.0412749012124</v>
       </c>
       <c r="P55">
-        <v>1046.522771325645</v>
+        <v>1038.3338173255</v>
       </c>
       <c r="Q55">
-        <v>1865.722771325645</v>
+        <v>1857.5338173255</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1165515736361988</v>
+        <v>0.1178618743854726</v>
       </c>
       <c r="T55">
-        <v>1.295839918073338</v>
+        <v>1.319838536454904</v>
       </c>
       <c r="U55">
         <v>0.06368110587651873</v>
@@ -5841,7 +5841,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>3.411261885971254</v>
+        <v>3.348090369564379</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5849,22 +5849,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.07931955415384107</v>
+        <v>0.07922164883504362</v>
       </c>
       <c r="C56">
-        <v>8533.08701752723</v>
+        <v>8404.286785692228</v>
       </c>
       <c r="D56">
-        <v>16165.35701752723</v>
+        <v>16212.71178569223</v>
       </c>
       <c r="E56">
-        <v>-153.9299999999985</v>
+        <v>22.22500000000218</v>
       </c>
       <c r="F56">
-        <v>9512.370000000001</v>
+        <v>9688.525000000001</v>
       </c>
       <c r="G56">
         <v>1880.1</v>
@@ -5885,28 +5885,28 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M56">
-        <v>605.7582411066205</v>
+        <v>616.9759863122988</v>
       </c>
       <c r="N56">
-        <v>1422.375092226713</v>
+        <v>1411.157347021034</v>
       </c>
       <c r="O56">
-        <v>384.0412749012124</v>
+        <v>381.0124836956793</v>
       </c>
       <c r="P56">
-        <v>1038.3338173255</v>
+        <v>1030.144863325355</v>
       </c>
       <c r="Q56">
-        <v>1857.5338173255</v>
+        <v>1849.344863325355</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1178618743854726</v>
+        <v>0.119230410723603</v>
       </c>
       <c r="T56">
-        <v>1.319838536454904</v>
+        <v>1.344903760097873</v>
       </c>
       <c r="U56">
         <v>0.06368110587651873</v>
@@ -5923,7 +5923,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>3.348090369564379</v>
+        <v>3.287215999208662</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5931,22 +5931,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.07922164883504362</v>
+        <v>0.07912374351624617</v>
       </c>
       <c r="C57">
-        <v>8404.286785692228</v>
+        <v>8275.76481093069</v>
       </c>
       <c r="D57">
-        <v>16212.71178569223</v>
+        <v>16260.34481093069</v>
       </c>
       <c r="E57">
-        <v>22.22500000000218</v>
+        <v>198.380000000001</v>
       </c>
       <c r="F57">
-        <v>9688.525000000001</v>
+        <v>9864.68</v>
       </c>
       <c r="G57">
         <v>1880.1</v>
@@ -5967,28 +5967,28 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M57">
-        <v>616.9759863122988</v>
+        <v>628.1937315179769</v>
       </c>
       <c r="N57">
-        <v>1411.157347021034</v>
+        <v>1399.939601815356</v>
       </c>
       <c r="O57">
-        <v>381.0124836956793</v>
+        <v>377.9836924901463</v>
       </c>
       <c r="P57">
-        <v>1030.144863325355</v>
+        <v>1021.95590932521</v>
       </c>
       <c r="Q57">
-        <v>1849.344863325355</v>
+        <v>1841.15590932521</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.119230410723603</v>
+        <v>0.1206611532589212</v>
       </c>
       <c r="T57">
-        <v>1.344903760097873</v>
+        <v>1.371108312088249</v>
       </c>
       <c r="U57">
         <v>0.06368110587651873</v>
@@ -6005,7 +6005,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>3.287215999208662</v>
+        <v>3.228515713508508</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6013,22 +6013,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.07912374351624617</v>
+        <v>0.07902583819744873</v>
       </c>
       <c r="C58">
-        <v>8275.76481093069</v>
+        <v>8147.523553031342</v>
       </c>
       <c r="D58">
-        <v>16260.34481093069</v>
+        <v>16308.25855303134</v>
       </c>
       <c r="E58">
-        <v>198.380000000001</v>
+        <v>374.5350000000017</v>
       </c>
       <c r="F58">
-        <v>9864.68</v>
+        <v>10040.835</v>
       </c>
       <c r="G58">
         <v>1880.1</v>
@@ -6049,28 +6049,28 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M58">
-        <v>628.1937315179769</v>
+        <v>639.411476723655</v>
       </c>
       <c r="N58">
-        <v>1399.939601815356</v>
+        <v>1388.721856609678</v>
       </c>
       <c r="O58">
-        <v>377.9836924901463</v>
+        <v>374.9549012846131</v>
       </c>
       <c r="P58">
-        <v>1021.95590932521</v>
+        <v>1013.766955325065</v>
       </c>
       <c r="Q58">
-        <v>1841.15590932521</v>
+        <v>1832.966955325065</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1206611532589212</v>
+        <v>0.1221584419586728</v>
       </c>
       <c r="T58">
-        <v>1.371108312088249</v>
+        <v>1.398531680450272</v>
       </c>
       <c r="U58">
         <v>0.06368110587651873</v>
@@ -6087,7 +6087,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>3.228515713508508</v>
+        <v>3.171875086955727</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6095,22 +6095,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.07902583819744873</v>
+        <v>0.07892793287865127</v>
       </c>
       <c r="C59">
-        <v>8147.523553031342</v>
+        <v>8019.565500861274</v>
       </c>
       <c r="D59">
-        <v>16308.25855303134</v>
+        <v>16356.45550086128</v>
       </c>
       <c r="E59">
-        <v>374.5350000000017</v>
+        <v>550.6900000000023</v>
       </c>
       <c r="F59">
-        <v>10040.835</v>
+        <v>10216.99</v>
       </c>
       <c r="G59">
         <v>1880.1</v>
@@ -6131,28 +6131,28 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M59">
-        <v>639.411476723655</v>
+        <v>650.6292219293332</v>
       </c>
       <c r="N59">
-        <v>1388.721856609678</v>
+        <v>1377.504111404</v>
       </c>
       <c r="O59">
-        <v>374.9549012846131</v>
+        <v>371.92611007908</v>
       </c>
       <c r="P59">
-        <v>1013.766955325065</v>
+        <v>1005.57800132492</v>
       </c>
       <c r="Q59">
-        <v>1832.966955325065</v>
+        <v>1824.77800132492</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1221584419586728</v>
+        <v>0.1237270301203172</v>
       </c>
       <c r="T59">
-        <v>1.398531680450272</v>
+        <v>1.427260923496199</v>
       </c>
       <c r="U59">
         <v>0.06368110587651873</v>
@@ -6169,7 +6169,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>3.171875086955727</v>
+        <v>3.11718758545649</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6177,22 +6177,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.07892793287865127</v>
+        <v>0.07883002755985381</v>
       </c>
       <c r="C60">
-        <v>8019.565500861276</v>
+        <v>7891.893172796879</v>
       </c>
       <c r="D60">
-        <v>16356.45550086128</v>
+        <v>16404.93817279688</v>
       </c>
       <c r="E60">
-        <v>550.6900000000005</v>
+        <v>726.8449999999993</v>
       </c>
       <c r="F60">
-        <v>10216.99</v>
+        <v>10393.145</v>
       </c>
       <c r="G60">
         <v>1880.1</v>
@@ -6213,28 +6213,28 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M60">
-        <v>650.6292219293331</v>
+        <v>661.8469671350113</v>
       </c>
       <c r="N60">
-        <v>1377.504111404</v>
+        <v>1366.286366198322</v>
       </c>
       <c r="O60">
-        <v>371.92611007908</v>
+        <v>368.897318873547</v>
       </c>
       <c r="P60">
-        <v>1005.57800132492</v>
+        <v>997.389047324775</v>
       </c>
       <c r="Q60">
-        <v>1824.77800132492</v>
+        <v>1816.589047324775</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1237270301203172</v>
+        <v>0.1253721347776517</v>
       </c>
       <c r="T60">
-        <v>1.427260923496199</v>
+        <v>1.457391593032172</v>
       </c>
       <c r="U60">
         <v>0.06368110587651873</v>
@@ -6251,7 +6251,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>3.117187585456491</v>
+        <v>3.064353897567398</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6259,22 +6259,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.07883002755985381</v>
+        <v>0.07873212224105636</v>
       </c>
       <c r="C61">
-        <v>7891.893172796879</v>
+        <v>7764.509117162492</v>
       </c>
       <c r="D61">
-        <v>16404.93817279688</v>
+        <v>16453.70911716249</v>
       </c>
       <c r="E61">
-        <v>726.8449999999993</v>
+        <v>903</v>
       </c>
       <c r="F61">
-        <v>10393.145</v>
+        <v>10569.3</v>
       </c>
       <c r="G61">
         <v>1880.1</v>
@@ -6295,28 +6295,28 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M61">
-        <v>661.8469671350113</v>
+        <v>673.0647123406894</v>
       </c>
       <c r="N61">
-        <v>1366.286366198322</v>
+        <v>1355.068620992644</v>
       </c>
       <c r="O61">
-        <v>368.897318873547</v>
+        <v>365.8685276680139</v>
       </c>
       <c r="P61">
-        <v>997.389047324775</v>
+        <v>989.20009332463</v>
       </c>
       <c r="Q61">
-        <v>1816.589047324775</v>
+        <v>1808.40009332463</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1253721347776517</v>
+        <v>0.1270994946678529</v>
       </c>
       <c r="T61">
-        <v>1.457391593032172</v>
+        <v>1.489028796044944</v>
       </c>
       <c r="U61">
         <v>0.06368110587651873</v>
@@ -6333,7 +6333,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>3.064353897567398</v>
+        <v>3.013281332607941</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6341,22 +6341,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.07873212224105636</v>
+        <v>0.07974746692225891</v>
       </c>
       <c r="C62">
-        <v>7764.509117162492</v>
+        <v>7096.235336211243</v>
       </c>
       <c r="D62">
-        <v>16453.70911716249</v>
+        <v>15961.59033621124</v>
       </c>
       <c r="E62">
-        <v>903</v>
+        <v>1079.155000000001</v>
       </c>
       <c r="F62">
-        <v>10569.3</v>
+        <v>10745.455</v>
       </c>
       <c r="G62">
         <v>1880.1</v>
@@ -6377,45 +6377,45 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M62">
-        <v>673.0647123406894</v>
+        <v>711.1460950463675</v>
       </c>
       <c r="N62">
-        <v>1355.068620992644</v>
+        <v>1316.987238286966</v>
       </c>
       <c r="O62">
-        <v>365.8685276680139</v>
+        <v>355.5865543374808</v>
       </c>
       <c r="P62">
-        <v>989.20009332463</v>
+        <v>961.400683949485</v>
       </c>
       <c r="Q62">
-        <v>1808.40009332463</v>
+        <v>1780.600683949485</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1270994946678529</v>
+        <v>0.1289154371165259</v>
       </c>
       <c r="T62">
-        <v>1.489028796044944</v>
+        <v>1.522288419725037</v>
       </c>
       <c r="U62">
-        <v>0.06368110587651873</v>
+        <v>0.06618110587651872</v>
       </c>
       <c r="V62">
         <v>0.27</v>
       </c>
       <c r="W62">
-        <v>0.04648720728985867</v>
+        <v>0.04831220728985867</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y62">
-        <v>3.013281332607941</v>
+        <v>2.851922196382302</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.07974746692225891</v>
+        <v>0.07966781160346145</v>
       </c>
       <c r="C63">
-        <v>7096.235336211243</v>
+        <v>6957.621160567767</v>
       </c>
       <c r="D63">
-        <v>15961.59033621124</v>
+        <v>15999.13116056777</v>
       </c>
       <c r="E63">
-        <v>1079.155000000001</v>
+        <v>1255.310000000001</v>
       </c>
       <c r="F63">
-        <v>10745.455</v>
+        <v>10921.61</v>
       </c>
       <c r="G63">
         <v>1880.1</v>
@@ -6459,28 +6459,28 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M63">
-        <v>711.1460950463675</v>
+        <v>722.8042277520457</v>
       </c>
       <c r="N63">
-        <v>1316.987238286966</v>
+        <v>1305.329105581287</v>
       </c>
       <c r="O63">
-        <v>355.5865543374808</v>
+        <v>352.4388585069476</v>
       </c>
       <c r="P63">
-        <v>961.400683949485</v>
+        <v>952.8902470743399</v>
       </c>
       <c r="Q63">
-        <v>1780.600683949485</v>
+        <v>1772.09024707434</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1289154371165259</v>
+        <v>0.1308269554835502</v>
       </c>
       <c r="T63">
-        <v>1.522288419725037</v>
+        <v>1.557298549914609</v>
       </c>
       <c r="U63">
         <v>0.06618110587651872</v>
@@ -6497,7 +6497,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>2.851922196382302</v>
+        <v>2.80592345127936</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6505,22 +6505,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.07966781160346145</v>
+        <v>0.07958815628466399</v>
       </c>
       <c r="C64">
-        <v>6957.621160567767</v>
+        <v>6819.183989334171</v>
       </c>
       <c r="D64">
-        <v>15999.13116056777</v>
+        <v>16036.84898933417</v>
       </c>
       <c r="E64">
-        <v>1255.310000000001</v>
+        <v>1431.465</v>
       </c>
       <c r="F64">
-        <v>10921.61</v>
+        <v>11097.765</v>
       </c>
       <c r="G64">
         <v>1880.1</v>
@@ -6541,28 +6541,28 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M64">
-        <v>722.8042277520457</v>
+        <v>734.4623604577238</v>
       </c>
       <c r="N64">
-        <v>1305.329105581287</v>
+        <v>1293.67097287561</v>
       </c>
       <c r="O64">
-        <v>352.4388585069476</v>
+        <v>349.2911626764146</v>
       </c>
       <c r="P64">
-        <v>952.8902470743399</v>
+        <v>944.3798101991949</v>
       </c>
       <c r="Q64">
-        <v>1772.09024707434</v>
+        <v>1763.579810199195</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1308269554835502</v>
+        <v>0.1328417991677109</v>
       </c>
       <c r="T64">
-        <v>1.557298549914609</v>
+        <v>1.594201119573887</v>
       </c>
       <c r="U64">
         <v>0.06618110587651872</v>
@@ -6579,7 +6579,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>2.80592345127936</v>
+        <v>2.761384983798736</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6587,22 +6587,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.07958815628466399</v>
+        <v>0.07950850096586655</v>
       </c>
       <c r="C65">
-        <v>6819.183989334171</v>
+        <v>6680.925077328275</v>
       </c>
       <c r="D65">
-        <v>16036.84898933417</v>
+        <v>16074.74507732827</v>
       </c>
       <c r="E65">
-        <v>1431.465</v>
+        <v>1607.620000000001</v>
       </c>
       <c r="F65">
-        <v>11097.765</v>
+        <v>11273.92</v>
       </c>
       <c r="G65">
         <v>1880.1</v>
@@ -6623,28 +6623,28 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M65">
-        <v>734.4623604577238</v>
+        <v>746.120493163402</v>
       </c>
       <c r="N65">
-        <v>1293.67097287561</v>
+        <v>1282.012840169931</v>
       </c>
       <c r="O65">
-        <v>349.2911626764146</v>
+        <v>346.1434668458814</v>
       </c>
       <c r="P65">
-        <v>944.3798101991949</v>
+        <v>935.8693733240498</v>
       </c>
       <c r="Q65">
-        <v>1763.579810199195</v>
+        <v>1755.06937332405</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1328417991677109</v>
+        <v>0.1349685786121028</v>
       </c>
       <c r="T65">
-        <v>1.594201119573887</v>
+        <v>1.633153831992015</v>
       </c>
       <c r="U65">
         <v>0.06618110587651872</v>
@@ -6661,7 +6661,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>2.761384983798736</v>
+        <v>2.718238343426881</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6669,22 +6669,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.07950850096586655</v>
+        <v>0.07942884564706909</v>
       </c>
       <c r="C66">
-        <v>6680.925077328275</v>
+        <v>6542.84569125688</v>
       </c>
       <c r="D66">
-        <v>16074.74507732827</v>
+        <v>16112.82069125688</v>
       </c>
       <c r="E66">
-        <v>1607.620000000001</v>
+        <v>1783.775000000001</v>
       </c>
       <c r="F66">
-        <v>11273.92</v>
+        <v>11450.075</v>
       </c>
       <c r="G66">
         <v>1880.1</v>
@@ -6705,28 +6705,28 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M66">
-        <v>746.120493163402</v>
+        <v>757.7786258690802</v>
       </c>
       <c r="N66">
-        <v>1282.012840169931</v>
+        <v>1270.354707464253</v>
       </c>
       <c r="O66">
-        <v>346.1434668458814</v>
+        <v>342.9957710153483</v>
       </c>
       <c r="P66">
-        <v>935.8693733240498</v>
+        <v>927.3589364489046</v>
       </c>
       <c r="Q66">
-        <v>1755.06937332405</v>
+        <v>1746.558936448904</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1349685786121028</v>
+        <v>0.1372168883104599</v>
       </c>
       <c r="T66">
-        <v>1.633153831992015</v>
+        <v>1.674332413691178</v>
       </c>
       <c r="U66">
         <v>0.06618110587651872</v>
@@ -6743,7 +6743,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>2.718238343426881</v>
+        <v>2.676419291989544</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6751,22 +6751,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.07942884564706909</v>
+        <v>0.07934919032827163</v>
       </c>
       <c r="C67">
-        <v>6542.84569125688</v>
+        <v>6404.947109856845</v>
       </c>
       <c r="D67">
-        <v>16112.82069125688</v>
+        <v>16151.07710985685</v>
       </c>
       <c r="E67">
-        <v>1783.775000000001</v>
+        <v>1959.930000000002</v>
       </c>
       <c r="F67">
-        <v>11450.075</v>
+        <v>11626.23</v>
       </c>
       <c r="G67">
         <v>1880.1</v>
@@ -6787,28 +6787,28 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M67">
-        <v>757.7786258690802</v>
+        <v>769.4367585747584</v>
       </c>
       <c r="N67">
-        <v>1270.354707464253</v>
+        <v>1258.696574758575</v>
       </c>
       <c r="O67">
-        <v>342.9957710153483</v>
+        <v>339.8480751848152</v>
       </c>
       <c r="P67">
-        <v>927.3589364489046</v>
+        <v>918.8484995737596</v>
       </c>
       <c r="Q67">
-        <v>1746.558936448904</v>
+        <v>1738.048499573759</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1372168883104599</v>
+        <v>0.1395974515204851</v>
       </c>
       <c r="T67">
-        <v>1.674332413691178</v>
+        <v>1.717933264902056</v>
       </c>
       <c r="U67">
         <v>0.06618110587651872</v>
@@ -6825,7 +6825,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>2.676419291989544</v>
+        <v>2.635867484535157</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6833,22 +6833,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.07934919032827163</v>
+        <v>0.07926953500947419</v>
       </c>
       <c r="C68">
-        <v>6404.947109856845</v>
+        <v>6267.230624038284</v>
       </c>
       <c r="D68">
-        <v>16151.07710985685</v>
+        <v>16189.51562403828</v>
       </c>
       <c r="E68">
-        <v>1959.930000000002</v>
+        <v>2136.085000000001</v>
       </c>
       <c r="F68">
-        <v>11626.23</v>
+        <v>11802.385</v>
       </c>
       <c r="G68">
         <v>1880.1</v>
@@ -6869,28 +6869,28 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M68">
-        <v>769.4367585747584</v>
+        <v>781.0948912804364</v>
       </c>
       <c r="N68">
-        <v>1258.696574758575</v>
+        <v>1247.038442052897</v>
       </c>
       <c r="O68">
-        <v>339.8480751848152</v>
+        <v>336.7003793542821</v>
       </c>
       <c r="P68">
-        <v>918.8484995737596</v>
+        <v>910.3380626986145</v>
       </c>
       <c r="Q68">
-        <v>1738.048499573759</v>
+        <v>1729.538062698614</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1395974515204851</v>
+        <v>0.1421222912886936</v>
       </c>
       <c r="T68">
-        <v>1.717933264902056</v>
+        <v>1.764176591943898</v>
       </c>
       <c r="U68">
         <v>0.06618110587651872</v>
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>2.635867484535157</v>
+        <v>2.596526178795826</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6915,22 +6915,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.07926953500947419</v>
+        <v>0.07918987969067673</v>
       </c>
       <c r="C69">
-        <v>6267.230624038284</v>
+        <v>6129.697537029759</v>
       </c>
       <c r="D69">
-        <v>16189.51562403828</v>
+        <v>16228.13753702976</v>
       </c>
       <c r="E69">
-        <v>2136.085000000001</v>
+        <v>2312.240000000002</v>
       </c>
       <c r="F69">
-        <v>11802.385</v>
+        <v>11978.54</v>
       </c>
       <c r="G69">
         <v>1880.1</v>
@@ -6951,28 +6951,28 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M69">
-        <v>781.0948912804364</v>
+        <v>792.7530239861146</v>
       </c>
       <c r="N69">
-        <v>1247.038442052897</v>
+        <v>1235.380309347219</v>
       </c>
       <c r="O69">
-        <v>336.7003793542821</v>
+        <v>333.5526835237491</v>
       </c>
       <c r="P69">
-        <v>910.3380626986145</v>
+        <v>901.8276258234696</v>
       </c>
       <c r="Q69">
-        <v>1729.538062698614</v>
+        <v>1721.027625823469</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1421222912886936</v>
+        <v>0.1448049335424151</v>
       </c>
       <c r="T69">
-        <v>1.764176591943898</v>
+        <v>1.813310126925854</v>
       </c>
       <c r="U69">
         <v>0.06618110587651872</v>
@@ -6989,7 +6989,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>2.596526178795826</v>
+        <v>2.558341970284123</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6997,22 +6997,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.07918987969067673</v>
+        <v>0.07911022437187928</v>
       </c>
       <c r="C70">
-        <v>6129.697537029759</v>
+        <v>5992.349164525558</v>
       </c>
       <c r="D70">
-        <v>16228.13753702976</v>
+        <v>16266.94416452556</v>
       </c>
       <c r="E70">
-        <v>2312.240000000002</v>
+        <v>2488.395000000002</v>
       </c>
       <c r="F70">
-        <v>11978.54</v>
+        <v>12154.695</v>
       </c>
       <c r="G70">
         <v>1880.1</v>
@@ -7033,28 +7033,28 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M70">
-        <v>792.7530239861146</v>
+        <v>804.4111566917928</v>
       </c>
       <c r="N70">
-        <v>1235.380309347219</v>
+        <v>1223.72217664154</v>
       </c>
       <c r="O70">
-        <v>333.5526835237491</v>
+        <v>330.404987693216</v>
       </c>
       <c r="P70">
-        <v>901.8276258234696</v>
+        <v>893.3171889483245</v>
       </c>
       <c r="Q70">
-        <v>1721.027625823469</v>
+        <v>1712.517188948324</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1448049335424151</v>
+        <v>0.1476606494899252</v>
       </c>
       <c r="T70">
-        <v>1.813310126925854</v>
+        <v>1.865613567390516</v>
       </c>
       <c r="U70">
         <v>0.06618110587651872</v>
@@ -7071,7 +7071,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>2.558341970284123</v>
+        <v>2.521264550424933</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7079,22 +7079,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.07911022437187928</v>
+        <v>0.08081906905308184</v>
       </c>
       <c r="C71">
-        <v>5992.349164525558</v>
+        <v>5022.407185984443</v>
       </c>
       <c r="D71">
-        <v>16266.94416452556</v>
+        <v>15473.15718598444</v>
       </c>
       <c r="E71">
-        <v>2488.395000000002</v>
+        <v>2664.550000000001</v>
       </c>
       <c r="F71">
-        <v>12154.695</v>
+        <v>12330.85</v>
       </c>
       <c r="G71">
         <v>1880.1</v>
@@ -7115,45 +7115,45 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M71">
-        <v>804.4111566917928</v>
+        <v>859.227264397471</v>
       </c>
       <c r="N71">
-        <v>1223.72217664154</v>
+        <v>1168.906068935862</v>
       </c>
       <c r="O71">
-        <v>330.404987693216</v>
+        <v>315.6046386126828</v>
       </c>
       <c r="P71">
-        <v>893.3171889483245</v>
+        <v>853.3014303231794</v>
       </c>
       <c r="Q71">
-        <v>1712.517188948324</v>
+        <v>1672.501430323179</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1476606494899252</v>
+        <v>0.1507067465006026</v>
       </c>
       <c r="T71">
-        <v>1.865613567390516</v>
+        <v>1.921403903886157</v>
       </c>
       <c r="U71">
-        <v>0.06618110587651872</v>
+        <v>0.06968110587651873</v>
       </c>
       <c r="V71">
         <v>0.27</v>
       </c>
       <c r="W71">
-        <v>0.04831220728985867</v>
+        <v>0.05086720728985867</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y71">
-        <v>2.521264550424933</v>
+        <v>2.360415477220164</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7161,22 +7161,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.08081906905308184</v>
+        <v>0.08076496373428438</v>
       </c>
       <c r="C72">
-        <v>5022.407185984443</v>
+        <v>4870.195585689158</v>
       </c>
       <c r="D72">
-        <v>15473.15718598444</v>
+        <v>15497.10058568916</v>
       </c>
       <c r="E72">
-        <v>2664.550000000001</v>
+        <v>2840.705000000002</v>
       </c>
       <c r="F72">
-        <v>12330.85</v>
+        <v>12507.005</v>
       </c>
       <c r="G72">
         <v>1880.1</v>
@@ -7197,28 +7197,28 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M72">
-        <v>859.227264397471</v>
+        <v>871.5019396031491</v>
       </c>
       <c r="N72">
-        <v>1168.906068935862</v>
+        <v>1156.631393730184</v>
       </c>
       <c r="O72">
-        <v>315.6046386126828</v>
+        <v>312.2904763071497</v>
       </c>
       <c r="P72">
-        <v>853.3014303231794</v>
+        <v>844.3409174230344</v>
       </c>
       <c r="Q72">
-        <v>1672.501430323179</v>
+        <v>1663.540917423034</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1507067465006026</v>
+        <v>0.1539629191671887</v>
       </c>
       <c r="T72">
-        <v>1.921403903886157</v>
+        <v>1.98104184979529</v>
       </c>
       <c r="U72">
         <v>0.06968110587651873</v>
@@ -7235,7 +7235,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>2.360415477220164</v>
+        <v>2.327170188808613</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7243,22 +7243,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.08076496373428438</v>
+        <v>0.08071085841548693</v>
       </c>
       <c r="C73">
-        <v>4870.19558568916</v>
+        <v>4718.058201000873</v>
       </c>
       <c r="D73">
-        <v>15497.10058568916</v>
+        <v>15521.11820100087</v>
       </c>
       <c r="E73">
-        <v>2840.705</v>
+        <v>3016.860000000001</v>
       </c>
       <c r="F73">
-        <v>12507.005</v>
+        <v>12683.16</v>
       </c>
       <c r="G73">
         <v>1880.1</v>
@@ -7279,28 +7279,28 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M73">
-        <v>871.501939603149</v>
+        <v>883.7766148088273</v>
       </c>
       <c r="N73">
-        <v>1156.631393730184</v>
+        <v>1144.356718524506</v>
       </c>
       <c r="O73">
-        <v>312.2904763071498</v>
+        <v>308.9763140016166</v>
       </c>
       <c r="P73">
-        <v>844.3409174230345</v>
+        <v>835.3804045228894</v>
       </c>
       <c r="Q73">
-        <v>1663.540917423034</v>
+        <v>1654.580404522889</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1539629191671887</v>
+        <v>0.1574516755956739</v>
       </c>
       <c r="T73">
-        <v>1.981041849795289</v>
+        <v>2.044939648983646</v>
       </c>
       <c r="U73">
         <v>0.06968110587651873</v>
@@ -7317,7 +7317,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>2.327170188808614</v>
+        <v>2.294848380630716</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7325,22 +7325,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.08071085841548693</v>
+        <v>0.08065675309668946</v>
       </c>
       <c r="C74">
-        <v>4718.058201000873</v>
+        <v>4565.995377516252</v>
       </c>
       <c r="D74">
-        <v>15521.11820100087</v>
+        <v>15545.21037751625</v>
       </c>
       <c r="E74">
-        <v>3016.860000000001</v>
+        <v>3193.015000000001</v>
       </c>
       <c r="F74">
-        <v>12683.16</v>
+        <v>12859.315</v>
       </c>
       <c r="G74">
         <v>1880.1</v>
@@ -7361,28 +7361,28 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M74">
-        <v>883.7766148088273</v>
+        <v>896.0512900145054</v>
       </c>
       <c r="N74">
-        <v>1144.356718524506</v>
+        <v>1132.082043318828</v>
       </c>
       <c r="O74">
-        <v>308.9763140016166</v>
+        <v>305.6621516960835</v>
       </c>
       <c r="P74">
-        <v>835.3804045228894</v>
+        <v>826.4198916227442</v>
       </c>
       <c r="Q74">
-        <v>1654.580404522889</v>
+        <v>1645.619891622744</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1574516755956739</v>
+        <v>0.161198858426269</v>
       </c>
       <c r="T74">
-        <v>2.044939648983646</v>
+        <v>2.113570618482251</v>
       </c>
       <c r="U74">
         <v>0.06968110587651873</v>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>2.294848380630716</v>
+        <v>2.263412101443994</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7407,22 +7407,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.08065675309668946</v>
+        <v>0.08211520777789202</v>
       </c>
       <c r="C75">
-        <v>4565.995377516252</v>
+        <v>3765.529345509172</v>
       </c>
       <c r="D75">
-        <v>15545.21037751625</v>
+        <v>14920.89934550917</v>
       </c>
       <c r="E75">
-        <v>3193.015000000001</v>
+        <v>3369.17</v>
       </c>
       <c r="F75">
-        <v>12859.315</v>
+        <v>13035.47</v>
       </c>
       <c r="G75">
         <v>1880.1</v>
@@ -7443,45 +7443,45 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M75">
-        <v>896.0512900145054</v>
+        <v>944.8252812201835</v>
       </c>
       <c r="N75">
-        <v>1132.082043318828</v>
+        <v>1083.30805211315</v>
       </c>
       <c r="O75">
-        <v>305.6621516960835</v>
+        <v>292.4931740705504</v>
       </c>
       <c r="P75">
-        <v>826.4198916227442</v>
+        <v>790.8148780425993</v>
       </c>
       <c r="Q75">
-        <v>1645.619891622744</v>
+        <v>1610.014878042599</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.161198858426269</v>
+        <v>0.1652342860899869</v>
       </c>
       <c r="T75">
-        <v>2.113570618482251</v>
+        <v>2.187480893326903</v>
       </c>
       <c r="U75">
-        <v>0.06968110587651873</v>
+        <v>0.07248110587651872</v>
       </c>
       <c r="V75">
         <v>0.27</v>
       </c>
       <c r="W75">
-        <v>0.05086720728985867</v>
+        <v>0.05291120728985867</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y75">
-        <v>2.263412101443994</v>
+        <v>2.146569713623798</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7489,22 +7489,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.08211520777789202</v>
+        <v>0.08208154245909458</v>
       </c>
       <c r="C76">
-        <v>3765.529345509172</v>
+        <v>3603.219314580638</v>
       </c>
       <c r="D76">
-        <v>14920.89934550917</v>
+        <v>14934.74431458064</v>
       </c>
       <c r="E76">
-        <v>3369.17</v>
+        <v>3545.325000000001</v>
       </c>
       <c r="F76">
-        <v>13035.47</v>
+        <v>13211.625</v>
       </c>
       <c r="G76">
         <v>1880.1</v>
@@ -7525,28 +7525,28 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M76">
-        <v>944.8252812201835</v>
+        <v>957.5931904258616</v>
       </c>
       <c r="N76">
-        <v>1083.30805211315</v>
+        <v>1070.540142907472</v>
       </c>
       <c r="O76">
-        <v>292.4931740705504</v>
+        <v>289.0458385850173</v>
       </c>
       <c r="P76">
-        <v>790.8148780425993</v>
+        <v>781.4943043224542</v>
       </c>
       <c r="Q76">
-        <v>1610.014878042599</v>
+        <v>1600.694304322454</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1652342860899869</v>
+        <v>0.1695925479668023</v>
       </c>
       <c r="T76">
-        <v>2.187480893326903</v>
+        <v>2.267303990159127</v>
       </c>
       <c r="U76">
         <v>0.07248110587651872</v>
@@ -7563,7 +7563,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>2.146569713623798</v>
+        <v>2.117948784108814</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7571,22 +7571,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.08208154245909458</v>
+        <v>0.08204787714029711</v>
       </c>
       <c r="C77">
-        <v>3603.219314580638</v>
+        <v>3440.935000760766</v>
       </c>
       <c r="D77">
-        <v>14934.74431458064</v>
+        <v>14948.61500076077</v>
       </c>
       <c r="E77">
-        <v>3545.325000000001</v>
+        <v>3721.480000000001</v>
       </c>
       <c r="F77">
-        <v>13211.625</v>
+        <v>13387.78</v>
       </c>
       <c r="G77">
         <v>1880.1</v>
@@ -7607,28 +7607,28 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M77">
-        <v>957.5931904258616</v>
+        <v>970.3610996315399</v>
       </c>
       <c r="N77">
-        <v>1070.540142907472</v>
+        <v>1057.772233701793</v>
       </c>
       <c r="O77">
-        <v>289.0458385850173</v>
+        <v>285.5985030994842</v>
       </c>
       <c r="P77">
-        <v>781.4943043224542</v>
+        <v>772.1737306023091</v>
       </c>
       <c r="Q77">
-        <v>1600.694304322454</v>
+        <v>1591.373730602309</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1695925479668023</v>
+        <v>0.1743139983333522</v>
       </c>
       <c r="T77">
-        <v>2.267303990159127</v>
+        <v>2.35377901172737</v>
       </c>
       <c r="U77">
         <v>0.07248110587651872</v>
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>2.117948784108814</v>
+        <v>2.090081036949487</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7653,22 +7653,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.08204787714029711</v>
+        <v>0.08201421182149965</v>
       </c>
       <c r="C78">
-        <v>3440.935000760766</v>
+        <v>3278.676475770679</v>
       </c>
       <c r="D78">
-        <v>14948.61500076077</v>
+        <v>14962.51147577068</v>
       </c>
       <c r="E78">
-        <v>3721.480000000001</v>
+        <v>3897.635</v>
       </c>
       <c r="F78">
-        <v>13387.78</v>
+        <v>13563.935</v>
       </c>
       <c r="G78">
         <v>1880.1</v>
@@ -7689,28 +7689,28 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M78">
-        <v>970.3610996315399</v>
+        <v>983.129008837218</v>
       </c>
       <c r="N78">
-        <v>1057.772233701793</v>
+        <v>1045.004324496115</v>
       </c>
       <c r="O78">
-        <v>285.5985030994842</v>
+        <v>282.1511676139511</v>
       </c>
       <c r="P78">
-        <v>772.1737306023091</v>
+        <v>762.8531568821641</v>
       </c>
       <c r="Q78">
-        <v>1591.373730602309</v>
+        <v>1582.053156882164</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1743139983333522</v>
+        <v>0.1794460096013412</v>
       </c>
       <c r="T78">
-        <v>2.35377901172737</v>
+        <v>2.447773600388503</v>
       </c>
       <c r="U78">
         <v>0.07248110587651872</v>
@@ -7727,7 +7727,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>2.090081036949487</v>
+        <v>2.062937127378714</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7735,22 +7735,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.08201421182149965</v>
+        <v>0.0819805465027022</v>
       </c>
       <c r="C79">
-        <v>3278.676475770679</v>
+        <v>3116.443811598434</v>
       </c>
       <c r="D79">
-        <v>14962.51147577068</v>
+        <v>14976.43381159843</v>
       </c>
       <c r="E79">
-        <v>3897.635</v>
+        <v>4073.790000000001</v>
       </c>
       <c r="F79">
-        <v>13563.935</v>
+        <v>13740.09</v>
       </c>
       <c r="G79">
         <v>1880.1</v>
@@ -7771,28 +7771,28 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M79">
-        <v>983.129008837218</v>
+        <v>995.8969180428961</v>
       </c>
       <c r="N79">
-        <v>1045.004324496115</v>
+        <v>1032.236415290437</v>
       </c>
       <c r="O79">
-        <v>282.1511676139511</v>
+        <v>278.703832128418</v>
       </c>
       <c r="P79">
-        <v>762.8531568821641</v>
+        <v>753.5325831620189</v>
       </c>
       <c r="Q79">
-        <v>1582.053156882164</v>
+        <v>1572.732583162019</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1794460096013412</v>
+        <v>0.1850445673482384</v>
       </c>
       <c r="T79">
-        <v>2.447773600388503</v>
+        <v>2.550313151655193</v>
       </c>
       <c r="U79">
         <v>0.07248110587651872</v>
@@ -7809,7 +7809,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>2.062937127378714</v>
+        <v>2.036489215489244</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7817,22 +7817,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.0819805465027022</v>
+        <v>0.08194688118390475</v>
       </c>
       <c r="C80">
-        <v>3116.443811598434</v>
+        <v>2954.237080500285</v>
       </c>
       <c r="D80">
-        <v>14976.43381159843</v>
+        <v>14990.38208050029</v>
       </c>
       <c r="E80">
-        <v>4073.790000000001</v>
+        <v>4249.945000000002</v>
       </c>
       <c r="F80">
-        <v>13740.09</v>
+        <v>13916.245</v>
       </c>
       <c r="G80">
         <v>1880.1</v>
@@ -7853,28 +7853,28 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M80">
-        <v>995.8969180428961</v>
+        <v>1008.664827248574</v>
       </c>
       <c r="N80">
-        <v>1032.236415290437</v>
+        <v>1019.468506084759</v>
       </c>
       <c r="O80">
-        <v>278.703832128418</v>
+        <v>275.2564966428849</v>
       </c>
       <c r="P80">
-        <v>753.5325831620189</v>
+        <v>744.212009441874</v>
       </c>
       <c r="Q80">
-        <v>1572.732583162019</v>
+        <v>1563.412009441874</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1850445673482384</v>
+        <v>0.1911763210710305</v>
       </c>
       <c r="T80">
-        <v>2.550313151655193</v>
+        <v>2.662618374471093</v>
       </c>
       <c r="U80">
         <v>0.07248110587651872</v>
@@ -7891,7 +7891,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>2.036489215489244</v>
+        <v>2.01071087098938</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7899,22 +7899,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.08194688118390475</v>
+        <v>0.08646841586510731</v>
       </c>
       <c r="C81">
-        <v>2954.237080500285</v>
+        <v>1111.443953107353</v>
       </c>
       <c r="D81">
-        <v>14990.38208050029</v>
+        <v>13323.74395310735</v>
       </c>
       <c r="E81">
-        <v>4249.945000000002</v>
+        <v>4426.100000000002</v>
       </c>
       <c r="F81">
-        <v>13916.245</v>
+        <v>14092.4</v>
       </c>
       <c r="G81">
         <v>1880.1</v>
@@ -7935,45 +7935,45 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M81">
-        <v>1008.664827248574</v>
+        <v>1131.353456454253</v>
       </c>
       <c r="N81">
-        <v>1019.468506084759</v>
+        <v>896.7798768790803</v>
       </c>
       <c r="O81">
-        <v>275.2564966428849</v>
+        <v>242.1305667573517</v>
       </c>
       <c r="P81">
-        <v>744.212009441874</v>
+        <v>654.6493101217286</v>
       </c>
       <c r="Q81">
-        <v>1563.412009441874</v>
+        <v>1473.849310121728</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1911763210710305</v>
+        <v>0.1979212501661018</v>
       </c>
       <c r="T81">
-        <v>2.662618374471093</v>
+        <v>2.786154119568582</v>
       </c>
       <c r="U81">
-        <v>0.07248110587651872</v>
+        <v>0.08028110587651874</v>
       </c>
       <c r="V81">
         <v>0.27</v>
       </c>
       <c r="W81">
-        <v>0.05291120728985867</v>
+        <v>0.05860520728985868</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y81">
-        <v>2.01071087098938</v>
+        <v>1.792661101411805</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7981,22 +7981,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.08646841586510731</v>
+        <v>0.08649169054630985</v>
       </c>
       <c r="C82">
-        <v>1111.443953107353</v>
+        <v>927.6680877962899</v>
       </c>
       <c r="D82">
-        <v>13323.74395310735</v>
+        <v>13316.12308779629</v>
       </c>
       <c r="E82">
-        <v>4426.100000000002</v>
+        <v>4602.255000000001</v>
       </c>
       <c r="F82">
-        <v>14092.4</v>
+        <v>14268.555</v>
       </c>
       <c r="G82">
         <v>1880.1</v>
@@ -8017,28 +8017,28 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M82">
-        <v>1131.353456454253</v>
+        <v>1145.495374659931</v>
       </c>
       <c r="N82">
-        <v>896.7798768790803</v>
+        <v>882.6379586734024</v>
       </c>
       <c r="O82">
-        <v>242.1305667573517</v>
+        <v>238.3122488418187</v>
       </c>
       <c r="P82">
-        <v>654.6493101217286</v>
+        <v>644.3257098315837</v>
       </c>
       <c r="Q82">
-        <v>1473.849310121728</v>
+        <v>1463.525709831584</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.1979212501661018</v>
+        <v>0.2053761717974965</v>
       </c>
       <c r="T82">
-        <v>2.786154119568582</v>
+        <v>2.922693627307913</v>
       </c>
       <c r="U82">
         <v>0.08028110587651874</v>
@@ -8055,7 +8055,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>1.792661101411805</v>
+        <v>1.770529482875857</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8063,22 +8063,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.08649169054630985</v>
+        <v>0.08884950522751239</v>
       </c>
       <c r="C83">
-        <v>927.6680877962899</v>
+        <v>22.19110494941742</v>
       </c>
       <c r="D83">
-        <v>13316.12308779629</v>
+        <v>12586.80110494942</v>
       </c>
       <c r="E83">
-        <v>4602.255000000001</v>
+        <v>4778.410000000002</v>
       </c>
       <c r="F83">
-        <v>14268.555</v>
+        <v>14444.71</v>
       </c>
       <c r="G83">
         <v>1880.1</v>
@@ -8099,45 +8099,45 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M83">
-        <v>1145.495374659931</v>
+        <v>1215.971661865609</v>
       </c>
       <c r="N83">
-        <v>882.6379586734024</v>
+        <v>812.1616714677243</v>
       </c>
       <c r="O83">
-        <v>238.3122488418187</v>
+        <v>219.2836512962856</v>
       </c>
       <c r="P83">
-        <v>644.3257098315837</v>
+        <v>592.8780201714387</v>
       </c>
       <c r="Q83">
-        <v>1463.525709831584</v>
+        <v>1412.078020171439</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2053761717974965</v>
+        <v>0.2136594180546016</v>
       </c>
       <c r="T83">
-        <v>2.922693627307913</v>
+        <v>3.074404191462725</v>
       </c>
       <c r="U83">
-        <v>0.08028110587651874</v>
+        <v>0.08418110587651872</v>
       </c>
       <c r="V83">
         <v>0.27</v>
       </c>
       <c r="W83">
-        <v>0.05860520728985868</v>
+        <v>0.06145220728985867</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y83">
-        <v>1.770529482875857</v>
+        <v>1.667911676676463</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8145,22 +8145,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.08884950522751239</v>
+        <v>0.08890124990871495</v>
       </c>
       <c r="C84">
-        <v>22.19110494941742</v>
+        <v>-169.0748259844913</v>
       </c>
       <c r="D84">
-        <v>12586.80110494942</v>
+        <v>12571.69017401551</v>
       </c>
       <c r="E84">
-        <v>4778.410000000002</v>
+        <v>4954.565000000002</v>
       </c>
       <c r="F84">
-        <v>14444.71</v>
+        <v>14620.865</v>
       </c>
       <c r="G84">
         <v>1880.1</v>
@@ -8181,28 +8181,28 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M84">
-        <v>1215.971661865609</v>
+        <v>1230.800584571287</v>
       </c>
       <c r="N84">
-        <v>812.1616714677243</v>
+        <v>797.3327487620461</v>
       </c>
       <c r="O84">
-        <v>219.2836512962856</v>
+        <v>215.2798421657525</v>
       </c>
       <c r="P84">
-        <v>592.8780201714387</v>
+        <v>582.0529065962936</v>
       </c>
       <c r="Q84">
-        <v>1412.078020171439</v>
+        <v>1401.252906596294</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2136594180546016</v>
+        <v>0.2229171638713663</v>
       </c>
       <c r="T84">
-        <v>3.074404191462725</v>
+        <v>3.243963057282809</v>
       </c>
       <c r="U84">
         <v>0.08418110587651872</v>
@@ -8219,7 +8219,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>1.667911676676463</v>
+        <v>1.647816355270723</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8227,22 +8227,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.08890124990871495</v>
+        <v>0.0889529945899175</v>
       </c>
       <c r="C85">
-        <v>-169.0748259844913</v>
+        <v>-360.3045179360797</v>
       </c>
       <c r="D85">
-        <v>12571.69017401551</v>
+        <v>12556.61548206392</v>
       </c>
       <c r="E85">
-        <v>4954.565000000002</v>
+        <v>5130.720000000003</v>
       </c>
       <c r="F85">
-        <v>14620.865</v>
+        <v>14797.02</v>
       </c>
       <c r="G85">
         <v>1880.1</v>
@@ -8263,28 +8263,28 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M85">
-        <v>1230.800584571287</v>
+        <v>1245.629507276965</v>
       </c>
       <c r="N85">
-        <v>797.3327487620461</v>
+        <v>782.5038260563679</v>
       </c>
       <c r="O85">
-        <v>215.2798421657525</v>
+        <v>211.2760330352193</v>
       </c>
       <c r="P85">
-        <v>582.0529065962936</v>
+        <v>571.2277930211485</v>
       </c>
       <c r="Q85">
-        <v>1401.252906596294</v>
+        <v>1390.427793021148</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2229171638713663</v>
+        <v>0.2333321279152264</v>
       </c>
       <c r="T85">
-        <v>3.243963057282809</v>
+        <v>3.434716781330403</v>
       </c>
       <c r="U85">
         <v>0.08418110587651872</v>
@@ -8301,7 +8301,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>1.647816355270723</v>
+        <v>1.628199493898452</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8309,22 +8309,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.08895299458991748</v>
+        <v>0.08900473927112003</v>
       </c>
       <c r="C86">
-        <v>-360.3045179360706</v>
+        <v>-551.4981011115215</v>
       </c>
       <c r="D86">
-        <v>12556.61548206393</v>
+        <v>12541.57689888848</v>
       </c>
       <c r="E86">
-        <v>5130.719999999999</v>
+        <v>5306.875</v>
       </c>
       <c r="F86">
-        <v>14797.02</v>
+        <v>14973.175</v>
       </c>
       <c r="G86">
         <v>1880.1</v>
@@ -8345,28 +8345,28 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M86">
-        <v>1245.629507276965</v>
+        <v>1260.458429982643</v>
       </c>
       <c r="N86">
-        <v>782.5038260563683</v>
+        <v>767.6749033506901</v>
       </c>
       <c r="O86">
-        <v>211.2760330352195</v>
+        <v>207.2722239046863</v>
       </c>
       <c r="P86">
-        <v>571.2277930211488</v>
+        <v>560.4026794460037</v>
       </c>
       <c r="Q86">
-        <v>1390.427793021149</v>
+        <v>1379.602679446004</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2333321279152263</v>
+        <v>0.2451357538316011</v>
       </c>
       <c r="T86">
-        <v>3.434716781330401</v>
+        <v>3.650904335251007</v>
       </c>
       <c r="U86">
         <v>0.08418110587651872</v>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>1.628199493898453</v>
+        <v>1.609044205734941</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8391,22 +8391,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.08900473927112003</v>
+        <v>0.08905648395232259</v>
       </c>
       <c r="C87">
-        <v>-551.4981011115215</v>
+        <v>-742.6557050939846</v>
       </c>
       <c r="D87">
-        <v>12541.57689888848</v>
+        <v>12526.57429490601</v>
       </c>
       <c r="E87">
-        <v>5306.875</v>
+        <v>5483.030000000001</v>
       </c>
       <c r="F87">
-        <v>14973.175</v>
+        <v>15149.33</v>
       </c>
       <c r="G87">
         <v>1880.1</v>
@@ -8427,28 +8427,28 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M87">
-        <v>1260.458429982643</v>
+        <v>1275.287352688321</v>
       </c>
       <c r="N87">
-        <v>767.6749033506901</v>
+        <v>752.8459806450119</v>
       </c>
       <c r="O87">
-        <v>207.2722239046863</v>
+        <v>203.2684147741532</v>
       </c>
       <c r="P87">
-        <v>560.4026794460037</v>
+        <v>549.5775658708586</v>
       </c>
       <c r="Q87">
-        <v>1379.602679446004</v>
+        <v>1368.777565870858</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2451357538316011</v>
+        <v>0.2586256120217438</v>
       </c>
       <c r="T87">
-        <v>3.650904335251007</v>
+        <v>3.897975825445986</v>
       </c>
       <c r="U87">
         <v>0.08418110587651872</v>
@@ -8465,7 +8465,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>1.609044205734941</v>
+        <v>1.590334389389186</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8473,22 +8473,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.08905648395232259</v>
+        <v>0.08910822863352512</v>
       </c>
       <c r="C88">
-        <v>-742.6557050939846</v>
+        <v>-933.7774588472894</v>
       </c>
       <c r="D88">
-        <v>12526.57429490601</v>
+        <v>12511.60754115271</v>
       </c>
       <c r="E88">
-        <v>5483.030000000001</v>
+        <v>5659.185000000001</v>
       </c>
       <c r="F88">
-        <v>15149.33</v>
+        <v>15325.485</v>
       </c>
       <c r="G88">
         <v>1880.1</v>
@@ -8509,28 +8509,28 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M88">
-        <v>1275.287352688321</v>
+        <v>1290.116275394</v>
       </c>
       <c r="N88">
-        <v>752.8459806450119</v>
+        <v>738.0170579393337</v>
       </c>
       <c r="O88">
-        <v>203.2684147741532</v>
+        <v>199.2646056436201</v>
       </c>
       <c r="P88">
-        <v>549.5775658708586</v>
+        <v>538.7524522957135</v>
       </c>
       <c r="Q88">
-        <v>1368.777565870858</v>
+        <v>1357.952452295713</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2586256120217438</v>
+        <v>0.2741908330103698</v>
       </c>
       <c r="T88">
-        <v>3.897975825445986</v>
+        <v>4.1830583141325</v>
       </c>
       <c r="U88">
         <v>0.08418110587651872</v>
@@ -8547,7 +8547,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>1.590334389389186</v>
+        <v>1.572054683764023</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8555,22 +8555,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.08910822863352512</v>
+        <v>0.08915997331472766</v>
       </c>
       <c r="C89">
-        <v>-933.7774588472894</v>
+        <v>-1124.863490719679</v>
       </c>
       <c r="D89">
-        <v>12511.60754115271</v>
+        <v>12496.67650928032</v>
       </c>
       <c r="E89">
-        <v>5659.185000000001</v>
+        <v>5835.34</v>
       </c>
       <c r="F89">
-        <v>15325.485</v>
+        <v>15501.64</v>
       </c>
       <c r="G89">
         <v>1880.1</v>
@@ -8591,28 +8591,28 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M89">
-        <v>1290.116275394</v>
+        <v>1304.945198099678</v>
       </c>
       <c r="N89">
-        <v>738.0170579393337</v>
+        <v>723.1881352336554</v>
       </c>
       <c r="O89">
-        <v>199.2646056436201</v>
+        <v>195.260796513087</v>
       </c>
       <c r="P89">
-        <v>538.7524522957135</v>
+        <v>527.9273387205685</v>
       </c>
       <c r="Q89">
-        <v>1357.952452295713</v>
+        <v>1347.127338720568</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2741908330103698</v>
+        <v>0.2923502574971004</v>
       </c>
       <c r="T89">
-        <v>4.1830583141325</v>
+        <v>4.515654550933434</v>
       </c>
       <c r="U89">
         <v>0.08418110587651872</v>
@@ -8629,7 +8629,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>1.572054683764023</v>
+        <v>1.554190425993977</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8637,22 +8637,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.08915997331472766</v>
+        <v>0.08921171799593022</v>
       </c>
       <c r="C90">
-        <v>-1124.863490719679</v>
+        <v>-1315.913928447457</v>
       </c>
       <c r="D90">
-        <v>12496.67650928032</v>
+        <v>12481.78107155254</v>
       </c>
       <c r="E90">
-        <v>5835.34</v>
+        <v>6011.495000000001</v>
       </c>
       <c r="F90">
-        <v>15501.64</v>
+        <v>15677.795</v>
       </c>
       <c r="G90">
         <v>1880.1</v>
@@ -8673,28 +8673,28 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M90">
-        <v>1304.945198099678</v>
+        <v>1319.774120805356</v>
       </c>
       <c r="N90">
-        <v>723.1881352336554</v>
+        <v>708.3592125279774</v>
       </c>
       <c r="O90">
-        <v>195.260796513087</v>
+        <v>191.2569873825539</v>
       </c>
       <c r="P90">
-        <v>527.9273387205685</v>
+        <v>517.1022251454235</v>
       </c>
       <c r="Q90">
-        <v>1347.127338720568</v>
+        <v>1336.302225145423</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.2923502574971004</v>
+        <v>0.3138113955268729</v>
       </c>
       <c r="T90">
-        <v>4.515654550933434</v>
+        <v>4.908722830789082</v>
       </c>
       <c r="U90">
         <v>0.08418110587651872</v>
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>1.554190425993977</v>
+        <v>1.536727612218764</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8719,22 +8719,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.08921171799593022</v>
+        <v>0.08926346267713277</v>
       </c>
       <c r="C91">
-        <v>-1315.913928447457</v>
+        <v>-1506.928899158611</v>
       </c>
       <c r="D91">
-        <v>12481.78107155254</v>
+        <v>12466.92110084139</v>
       </c>
       <c r="E91">
-        <v>6011.495000000001</v>
+        <v>6187.650000000001</v>
       </c>
       <c r="F91">
-        <v>15677.795</v>
+        <v>15853.95</v>
       </c>
       <c r="G91">
         <v>1880.1</v>
@@ -8755,28 +8755,28 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M91">
-        <v>1319.774120805356</v>
+        <v>1334.603043511034</v>
       </c>
       <c r="N91">
-        <v>708.3592125279774</v>
+        <v>693.5302898222992</v>
       </c>
       <c r="O91">
-        <v>191.2569873825539</v>
+        <v>187.2531782520208</v>
       </c>
       <c r="P91">
-        <v>517.1022251454235</v>
+        <v>506.2771115702784</v>
       </c>
       <c r="Q91">
-        <v>1336.302225145423</v>
+        <v>1325.477111570278</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3138113955268729</v>
+        <v>0.3395647611625998</v>
       </c>
       <c r="T91">
-        <v>4.908722830789082</v>
+        <v>5.38040476661586</v>
       </c>
       <c r="U91">
         <v>0.08418110587651872</v>
@@ -8793,7 +8793,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>1.536727612218764</v>
+        <v>1.519652860971889</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8801,22 +8801,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.08926346267713277</v>
+        <v>0.08931520735833531</v>
       </c>
       <c r="C92">
-        <v>-1506.928899158611</v>
+        <v>-1697.90852937646</v>
       </c>
       <c r="D92">
-        <v>12466.92110084139</v>
+        <v>12452.09647062354</v>
       </c>
       <c r="E92">
-        <v>6187.650000000001</v>
+        <v>6363.805000000002</v>
       </c>
       <c r="F92">
-        <v>15853.95</v>
+        <v>16030.105</v>
       </c>
       <c r="G92">
         <v>1880.1</v>
@@ -8837,28 +8837,28 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M92">
-        <v>1334.603043511034</v>
+        <v>1349.431966216712</v>
       </c>
       <c r="N92">
-        <v>693.5302898222992</v>
+        <v>678.701367116621</v>
       </c>
       <c r="O92">
-        <v>187.2531782520208</v>
+        <v>183.2493691214877</v>
       </c>
       <c r="P92">
-        <v>506.2771115702784</v>
+        <v>495.4519979951333</v>
       </c>
       <c r="Q92">
-        <v>1325.477111570278</v>
+        <v>1314.651997995133</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.3395647611625998</v>
+        <v>0.3710410969395994</v>
       </c>
       <c r="T92">
-        <v>5.38040476661586</v>
+        <v>5.956904910404145</v>
       </c>
       <c r="U92">
         <v>0.08418110587651872</v>
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>1.519652860971889</v>
+        <v>1.502953378983187</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8883,22 +8883,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.08931520735833531</v>
+        <v>0.09890367203953787</v>
       </c>
       <c r="C93">
-        <v>-1697.90852937646</v>
+        <v>-4122.429463969554</v>
       </c>
       <c r="D93">
-        <v>12452.09647062354</v>
+        <v>10203.73053603045</v>
       </c>
       <c r="E93">
-        <v>6363.805000000002</v>
+        <v>6539.960000000001</v>
       </c>
       <c r="F93">
-        <v>16030.105</v>
+        <v>16206.26</v>
       </c>
       <c r="G93">
         <v>1880.1</v>
@@ -8919,45 +8919,45 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M93">
-        <v>1349.431966216712</v>
+        <v>1594.38978092239</v>
       </c>
       <c r="N93">
-        <v>678.701367116621</v>
+        <v>433.7435524109428</v>
       </c>
       <c r="O93">
-        <v>183.2493691214877</v>
+        <v>117.1107591509546</v>
       </c>
       <c r="P93">
-        <v>495.4519979951333</v>
+        <v>316.6327932599883</v>
       </c>
       <c r="Q93">
-        <v>1314.651997995133</v>
+        <v>1135.832793259988</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.3710410969395994</v>
+        <v>0.4103865166608489</v>
       </c>
       <c r="T93">
-        <v>5.956904910404145</v>
+        <v>6.677530090139501</v>
       </c>
       <c r="U93">
-        <v>0.08418110587651872</v>
+        <v>0.09838110587651873</v>
       </c>
       <c r="V93">
         <v>0.27</v>
       </c>
       <c r="W93">
-        <v>0.06145220728985867</v>
+        <v>0.07181820728985867</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y93">
-        <v>1.502953378983187</v>
+        <v>1.272043610415022</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8965,22 +8965,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.09890367203953787</v>
+        <v>0.09905907672074042</v>
       </c>
       <c r="C94">
-        <v>-4122.429463969554</v>
+        <v>-4328.357933369767</v>
       </c>
       <c r="D94">
-        <v>10203.73053603045</v>
+        <v>10173.95706663023</v>
       </c>
       <c r="E94">
-        <v>6539.960000000001</v>
+        <v>6716.115000000002</v>
       </c>
       <c r="F94">
-        <v>16206.26</v>
+        <v>16382.415</v>
       </c>
       <c r="G94">
         <v>1880.1</v>
@@ -9001,28 +9001,28 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M94">
-        <v>1594.38978092239</v>
+        <v>1611.720104628069</v>
       </c>
       <c r="N94">
-        <v>433.7435524109428</v>
+        <v>416.4132287052646</v>
       </c>
       <c r="O94">
-        <v>117.1107591509546</v>
+        <v>112.4315717504215</v>
       </c>
       <c r="P94">
-        <v>316.6327932599883</v>
+        <v>303.9816569548432</v>
       </c>
       <c r="Q94">
-        <v>1135.832793259988</v>
+        <v>1123.181656954843</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.4103865166608489</v>
+        <v>0.4609734848738839</v>
       </c>
       <c r="T94">
-        <v>6.677530090139501</v>
+        <v>7.604048178370673</v>
       </c>
       <c r="U94">
         <v>0.09838110587651873</v>
@@ -9039,7 +9039,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>1.272043610415022</v>
+        <v>1.258365722130989</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9047,22 +9047,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.09905907672074042</v>
+        <v>0.1203305086871819</v>
       </c>
       <c r="C95">
-        <v>-4328.357933369767</v>
+        <v>-7408.218266720613</v>
       </c>
       <c r="D95">
-        <v>10173.95706663023</v>
+        <v>7270.251733279388</v>
       </c>
       <c r="E95">
-        <v>6716.115000000002</v>
+        <v>6892.27</v>
       </c>
       <c r="F95">
-        <v>16382.415</v>
+        <v>16558.57</v>
       </c>
       <c r="G95">
         <v>1880.1</v>
@@ -9083,45 +9083,45 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M95">
-        <v>1611.720104628069</v>
+        <v>2102.625530333747</v>
       </c>
       <c r="N95">
-        <v>416.4132287052646</v>
+        <v>-74.4921970004134</v>
       </c>
       <c r="O95">
-        <v>112.4315717504215</v>
+        <v>-20.11289319011162</v>
       </c>
       <c r="P95">
-        <v>303.9816569548432</v>
+        <v>-54.37930381030178</v>
       </c>
       <c r="Q95">
-        <v>1123.181656954843</v>
+        <v>764.8206961896981</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.4609734848738839</v>
+        <v>0.5342383558469402</v>
       </c>
       <c r="T95">
-        <v>7.604048178370673</v>
+        <v>8.945920019802125</v>
       </c>
       <c r="U95">
-        <v>0.09838110587651873</v>
+        <v>0.1269811058765187</v>
       </c>
       <c r="V95">
-        <v>0.27</v>
+        <v>0.2604343912408791</v>
       </c>
       <c r="W95">
-        <v>0.07181820728985867</v>
+        <v>0.09391085886847396</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y95">
-        <v>1.258365722130989</v>
+        <v>0.9645718194106635</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9129,22 +9129,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1203305086871819</v>
+        <v>0.1211423197459471</v>
       </c>
       <c r="C96">
-        <v>-7408.218266720613</v>
+        <v>-7662.709994033823</v>
       </c>
       <c r="D96">
-        <v>7270.251733279388</v>
+        <v>7191.915005966179</v>
       </c>
       <c r="E96">
-        <v>6892.27</v>
+        <v>7068.425000000003</v>
       </c>
       <c r="F96">
-        <v>16558.57</v>
+        <v>16734.725</v>
       </c>
       <c r="G96">
         <v>1880.1</v>
@@ -9165,37 +9165,37 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M96">
-        <v>2102.625530333747</v>
+        <v>2124.993887039425</v>
       </c>
       <c r="N96">
-        <v>-74.4921970004134</v>
+        <v>-96.86055370609211</v>
       </c>
       <c r="O96">
-        <v>-20.11289319011162</v>
+        <v>-26.15234950064487</v>
       </c>
       <c r="P96">
-        <v>-54.37930381030178</v>
+        <v>-70.70820420544723</v>
       </c>
       <c r="Q96">
-        <v>764.8206961896981</v>
+        <v>748.4917957945526</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.5342383558469402</v>
+        <v>0.6319260270163285</v>
       </c>
       <c r="T96">
-        <v>8.945920019802125</v>
+        <v>10.73510402376255</v>
       </c>
       <c r="U96">
         <v>0.1269811058765187</v>
       </c>
       <c r="V96">
-        <v>0.2604343912408791</v>
+        <v>0.2576929765962382</v>
       </c>
       <c r="W96">
-        <v>0.09391085886847396</v>
+        <v>0.09425896673171653</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.9645718194106635</v>
+        <v>0.9544184318379194</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9211,22 +9211,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1211423197459471</v>
+        <v>0.1219541308047123</v>
       </c>
       <c r="C97">
-        <v>-7662.709994033823</v>
+        <v>-7915.53156581198</v>
       </c>
       <c r="D97">
-        <v>7191.915005966179</v>
+        <v>7115.248434188021</v>
       </c>
       <c r="E97">
-        <v>7068.425000000003</v>
+        <v>7244.580000000002</v>
       </c>
       <c r="F97">
-        <v>16734.725</v>
+        <v>16910.88</v>
       </c>
       <c r="G97">
         <v>1880.1</v>
@@ -9247,37 +9247,37 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M97">
-        <v>2124.993887039425</v>
+        <v>2147.362243745103</v>
       </c>
       <c r="N97">
-        <v>-96.86055370609211</v>
+        <v>-119.2289104117699</v>
       </c>
       <c r="O97">
-        <v>-26.15234950064487</v>
+        <v>-32.19180581117788</v>
       </c>
       <c r="P97">
-        <v>-70.70820420544723</v>
+        <v>-87.03710460059202</v>
       </c>
       <c r="Q97">
-        <v>748.4917957945526</v>
+        <v>732.1628953994078</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.6319260270163285</v>
+        <v>0.7784575337704109</v>
       </c>
       <c r="T97">
-        <v>10.73510402376255</v>
+        <v>13.4188800297032</v>
       </c>
       <c r="U97">
         <v>0.1269811058765187</v>
       </c>
       <c r="V97">
-        <v>0.2576929765962382</v>
+        <v>0.2550086747566942</v>
       </c>
       <c r="W97">
-        <v>0.09425896673171653</v>
+        <v>0.09459982234780821</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.9544184318379194</v>
+        <v>0.9444765731729413</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9293,22 +9293,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1219541308047123</v>
+        <v>0.1227659418634774</v>
       </c>
       <c r="C98">
-        <v>-7915.53156581198</v>
+        <v>-8166.735830784028</v>
       </c>
       <c r="D98">
-        <v>7115.248434188021</v>
+        <v>7040.199169215972</v>
       </c>
       <c r="E98">
-        <v>7244.580000000002</v>
+        <v>7420.735000000001</v>
       </c>
       <c r="F98">
-        <v>16910.88</v>
+        <v>17087.035</v>
       </c>
       <c r="G98">
         <v>1880.1</v>
@@ -9329,37 +9329,37 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M98">
-        <v>2147.362243745103</v>
+        <v>2169.730600450781</v>
       </c>
       <c r="N98">
-        <v>-119.2289104117699</v>
+        <v>-141.5972671174482</v>
       </c>
       <c r="O98">
-        <v>-32.19180581117788</v>
+        <v>-38.231262121711</v>
       </c>
       <c r="P98">
-        <v>-87.03710460059202</v>
+        <v>-103.3660049957371</v>
       </c>
       <c r="Q98">
-        <v>732.1628953994078</v>
+        <v>715.8339950042626</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.7784575337704089</v>
+        <v>1.022676711693879</v>
       </c>
       <c r="T98">
-        <v>13.41888002970316</v>
+        <v>17.89184003960422</v>
       </c>
       <c r="U98">
         <v>0.1269811058765187</v>
       </c>
       <c r="V98">
-        <v>0.2550086747566942</v>
+        <v>0.2523797193468313</v>
       </c>
       <c r="W98">
-        <v>0.09459982234780821</v>
+        <v>0.09493365001305265</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.9444765731729413</v>
+        <v>0.9347397012845604</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9375,22 +9375,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1227659418634774</v>
+        <v>0.1235777529222426</v>
       </c>
       <c r="C99">
-        <v>-8166.735830784028</v>
+        <v>-8416.37343122882</v>
       </c>
       <c r="D99">
-        <v>7040.199169215972</v>
+        <v>6966.716568771179</v>
       </c>
       <c r="E99">
-        <v>7420.735000000001</v>
+        <v>7596.889999999999</v>
       </c>
       <c r="F99">
-        <v>17087.035</v>
+        <v>17263.19</v>
       </c>
       <c r="G99">
         <v>1880.1</v>
@@ -9411,37 +9411,37 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M99">
-        <v>2169.730600450781</v>
+        <v>2192.098957156459</v>
       </c>
       <c r="N99">
-        <v>-141.5972671174482</v>
+        <v>-163.965623823126</v>
       </c>
       <c r="O99">
-        <v>-38.231262121711</v>
+        <v>-44.27071843224401</v>
       </c>
       <c r="P99">
-        <v>-103.3660049957371</v>
+        <v>-119.6949053908819</v>
       </c>
       <c r="Q99">
-        <v>715.8339950042626</v>
+        <v>699.5050946091179</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.022676711693879</v>
+        <v>1.511115067540818</v>
       </c>
       <c r="T99">
-        <v>17.89184003960422</v>
+        <v>26.83776005940632</v>
       </c>
       <c r="U99">
         <v>0.1269811058765187</v>
       </c>
       <c r="V99">
-        <v>0.2523797193468313</v>
+        <v>0.2498044160881902</v>
       </c>
       <c r="W99">
-        <v>0.09493365001305265</v>
+        <v>0.0952606648688023</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.9347397012845604</v>
+        <v>0.9252015410673712</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9457,22 +9457,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1235777529222426</v>
+        <v>0.1243895639810078</v>
       </c>
       <c r="C100">
-        <v>-8416.37343122882</v>
+        <v>-8664.492916935578</v>
       </c>
       <c r="D100">
-        <v>6966.716568771179</v>
+        <v>6894.752083064423</v>
       </c>
       <c r="E100">
-        <v>7596.889999999999</v>
+        <v>7773.045000000002</v>
       </c>
       <c r="F100">
-        <v>17263.19</v>
+        <v>17439.345</v>
       </c>
       <c r="G100">
         <v>1880.1</v>
@@ -9493,37 +9493,37 @@
         <v>2028.133333333333</v>
       </c>
       <c r="M100">
-        <v>2192.098957156459</v>
+        <v>2214.467313862138</v>
       </c>
       <c r="N100">
-        <v>-163.965623823126</v>
+        <v>-186.3339805288047</v>
       </c>
       <c r="O100">
-        <v>-44.27071843224401</v>
+        <v>-50.31017474277726</v>
       </c>
       <c r="P100">
-        <v>-119.6949053908819</v>
+        <v>-136.0238057860274</v>
       </c>
       <c r="Q100">
-        <v>699.5050946091179</v>
+        <v>683.1761942139724</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.511115067540818</v>
+        <v>2.976430135081636</v>
       </c>
       <c r="T100">
-        <v>26.83776005940632</v>
+        <v>53.67552011881265</v>
       </c>
       <c r="U100">
         <v>0.1269811058765187</v>
       </c>
       <c r="V100">
-        <v>0.2498044160881902</v>
+        <v>0.2472811391580064</v>
       </c>
       <c r="W100">
-        <v>0.0952606648688023</v>
+        <v>0.09558107336382976</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9531,91 +9531,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.9252015410673712</v>
+        <v>0.9158560709555793</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1243895639810078</v>
-      </c>
-      <c r="C101">
-        <v>-8664.492916935578</v>
-      </c>
-      <c r="D101">
-        <v>6894.752083064423</v>
-      </c>
-      <c r="E101">
-        <v>7773.045000000002</v>
-      </c>
-      <c r="F101">
-        <v>17439.345</v>
-      </c>
-      <c r="G101">
-        <v>1880.1</v>
-      </c>
-      <c r="H101">
-        <v>7949.2</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>2847.333333333333</v>
-      </c>
-      <c r="K101">
-        <v>819.1999999999998</v>
-      </c>
-      <c r="L101">
-        <v>2028.133333333333</v>
-      </c>
-      <c r="M101">
-        <v>2214.467313862138</v>
-      </c>
-      <c r="N101">
-        <v>-186.3339805288047</v>
-      </c>
-      <c r="O101">
-        <v>-50.31017474277726</v>
-      </c>
-      <c r="P101">
-        <v>-136.0238057860274</v>
-      </c>
-      <c r="Q101">
-        <v>683.1761942139724</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>2.976430135081636</v>
-      </c>
-      <c r="T101">
-        <v>53.67552011881265</v>
-      </c>
-      <c r="U101">
-        <v>0.1269811058765187</v>
-      </c>
-      <c r="V101">
-        <v>0.2472811391580064</v>
-      </c>
-      <c r="W101">
-        <v>0.09558107336382976</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>Caa/CCC</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.9158560709555793</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
